--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="472">
   <si>
     <t/>
   </si>
@@ -1292,15 +1292,6 @@
   </si>
   <si>
     <t>NISSIN CR.CRISPY 250</t>
-  </si>
-  <si>
-    <t>20071671</t>
-  </si>
-  <si>
-    <t>IDM CREAM CRACK 120G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20137760</t>
@@ -1828,7 +1819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5652,18 +5643,18 @@
         <v>424</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>429</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
@@ -5672,7 +5663,7 @@
         <v>424</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5680,19 +5671,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5709,10 +5700,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5720,19 +5711,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5740,19 +5731,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5760,19 +5751,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5780,19 +5771,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5800,19 +5791,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5820,19 +5811,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5849,10 +5840,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5860,19 +5851,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5880,19 +5871,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5900,19 +5891,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5920,19 +5911,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5940,19 +5931,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="E206" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5969,10 +5960,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5980,19 +5971,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6000,19 +5991,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6020,19 +6011,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6040,41 +6031,21 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>472</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F212" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="470">
   <si>
     <t/>
   </si>
@@ -434,12 +434,6 @@
   </si>
   <si>
     <t>14</t>
-  </si>
-  <si>
-    <t>20138463</t>
-  </si>
-  <si>
-    <t>NABATI WRPZ STRW 66G</t>
   </si>
   <si>
     <t>20137570</t>
@@ -1819,7 +1813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F211"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3083,7 +3077,7 @@
         <v>140</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3103,7 +3097,7 @@
         <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3123,7 +3117,7 @@
         <v>140</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3143,7 +3137,7 @@
         <v>140</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3163,7 +3157,7 @@
         <v>140</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3183,10 +3177,10 @@
         <v>140</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3200,30 +3194,30 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3240,10 +3234,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3260,13 +3254,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3280,10 +3274,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>24</v>
@@ -3300,13 +3294,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3320,10 +3314,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3340,10 +3334,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3360,10 +3354,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3371,19 +3365,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3400,10 +3394,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3420,10 +3414,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3440,10 +3434,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3460,10 +3454,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3480,10 +3474,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3500,10 +3494,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3520,10 +3514,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3540,10 +3534,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3560,10 +3554,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3571,19 +3565,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3600,10 +3594,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3620,10 +3614,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3640,10 +3634,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3660,10 +3654,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3680,33 +3674,33 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>209</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3720,13 +3714,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3740,30 +3734,30 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3780,10 +3774,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3800,10 +3794,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3820,10 +3814,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3831,19 +3825,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3860,10 +3854,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3880,10 +3874,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3900,10 +3894,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3911,19 +3905,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3940,10 +3934,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3960,10 +3954,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3980,10 +3974,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3991,19 +3985,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -4020,10 +4014,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4031,19 +4025,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4060,10 +4054,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4071,19 +4065,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4100,10 +4094,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4120,30 +4114,30 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>24</v>
@@ -4160,30 +4154,30 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4200,10 +4194,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4220,10 +4214,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4240,13 +4234,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4260,10 +4254,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>24</v>
@@ -4280,10 +4274,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>24</v>
@@ -4300,13 +4294,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4320,50 +4314,50 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>280</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>282</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4380,10 +4374,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4400,13 +4394,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4420,13 +4414,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4440,30 +4434,30 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4480,10 +4474,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4500,10 +4494,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4520,10 +4514,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4531,19 +4525,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4560,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4580,10 +4574,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4591,19 +4585,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4620,10 +4614,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4640,13 +4634,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4660,30 +4654,30 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4700,10 +4694,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4720,10 +4714,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4740,10 +4734,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4760,10 +4754,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4771,19 +4765,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4800,10 +4794,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4811,19 +4805,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4840,10 +4834,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4860,10 +4854,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4880,10 +4874,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4891,19 +4885,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4920,10 +4914,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4940,10 +4934,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4960,10 +4954,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4971,19 +4965,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -5000,10 +4994,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -5020,10 +5014,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5040,10 +5034,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5051,19 +5045,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="E162" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5080,13 +5074,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5100,10 +5094,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>24</v>
@@ -5120,13 +5114,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5140,10 +5134,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5160,10 +5154,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5180,10 +5174,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5200,10 +5194,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5220,53 +5214,53 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>381</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>383</v>
+        <v>18</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5280,13 +5274,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5300,13 +5294,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>18</v>
+        <v>381</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5320,13 +5314,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5340,30 +5334,30 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>383</v>
+        <v>18</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>18</v>
@@ -5380,10 +5374,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>18</v>
@@ -5400,10 +5394,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>18</v>
@@ -5420,30 +5414,30 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5460,10 +5454,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5480,10 +5474,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5500,10 +5494,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5511,19 +5505,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5540,13 +5534,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5560,13 +5554,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5580,10 +5574,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5591,19 +5585,19 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="E189" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5620,10 +5614,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5640,10 +5634,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5660,10 +5654,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5671,19 +5665,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5700,10 +5694,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5720,10 +5714,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5740,10 +5734,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5760,10 +5754,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5780,10 +5774,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5800,10 +5794,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5811,19 +5805,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5840,10 +5834,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5860,10 +5854,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5880,10 +5874,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5900,10 +5894,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5920,10 +5914,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5931,19 +5925,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5960,10 +5954,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5980,10 +5974,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6000,10 +5994,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6020,32 +6014,12 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F211" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -97,7 +97,7 @@
     <t>10007336</t>
   </si>
   <si>
-    <t>TANGO WFR STRAW 133G</t>
+    <t>TANGO WFR STRAW 124G</t>
   </si>
   <si>
     <t>20063092</t>
@@ -115,13 +115,13 @@
     <t>10004541</t>
   </si>
   <si>
-    <t>TANGO WFR VNLA 133G</t>
+    <t>TANGO WFR VNLA 124G</t>
   </si>
   <si>
     <t>10004540</t>
   </si>
   <si>
-    <t>TANGO WFR CHOCO 133G</t>
+    <t>TANGO WFR CHOCO 124G</t>
   </si>
   <si>
     <t>20133247</t>
@@ -280,13 +280,13 @@
     <t>20083487</t>
   </si>
   <si>
-    <t>TANGO WFR CHOCO 99G</t>
+    <t>TANGO WFR CHOCO 95G</t>
   </si>
   <si>
     <t>20083488</t>
   </si>
   <si>
-    <t>TANGO WFR VANL 99G</t>
+    <t>TANGO WFR VANL 95G</t>
   </si>
   <si>
     <t>20138099</t>
@@ -403,7 +403,7 @@
     <t>20128683</t>
   </si>
   <si>
-    <t>TANGO WFLE CHO HZL75</t>
+    <t>TANGO WFLE CHO HZL63</t>
   </si>
   <si>
     <t>20027448</t>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="474">
   <si>
     <t/>
   </si>
@@ -574,288 +574,294 @@
     <t>POCKY CRSHD DRK.CH25</t>
   </si>
   <si>
+    <t>20142267</t>
+  </si>
+  <si>
+    <t>POCKY PASION FRUIT38</t>
+  </si>
+  <si>
+    <t>20142268</t>
+  </si>
+  <si>
+    <t>GLICO PJOY TIRAMIS30</t>
+  </si>
+  <si>
+    <t>20090169</t>
+  </si>
+  <si>
+    <t>GERY KR.BRS ASN 10'S</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20141391</t>
+  </si>
+  <si>
+    <t>MONDE SNACK CHEESE50</t>
+  </si>
+  <si>
+    <t>10000461</t>
+  </si>
+  <si>
+    <t>MONDE SERENA GOLD 50</t>
+  </si>
+  <si>
+    <t>20099687</t>
+  </si>
+  <si>
+    <t>MONDE SPCY TOMAT 50G</t>
+  </si>
+  <si>
+    <t>10000562</t>
+  </si>
+  <si>
+    <t>MONDE EGG DROPS 110G</t>
+  </si>
+  <si>
+    <t>10002258</t>
+  </si>
+  <si>
+    <t>MONDE BISC PBIS 190G</t>
+  </si>
+  <si>
+    <t>20085046</t>
+  </si>
+  <si>
+    <t>JULIES PNUT BTR 82.5</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20057475</t>
+  </si>
+  <si>
+    <t>SERENA TOGO CKLT 128</t>
+  </si>
+  <si>
+    <t>20095021</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CKLT 76G</t>
+  </si>
+  <si>
+    <t>20129409</t>
+  </si>
+  <si>
+    <t>NEXTAR NOIR CHO 144</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20122285</t>
+  </si>
+  <si>
+    <t>NEXTAR NOIR C&amp;C 144</t>
+  </si>
+  <si>
+    <t>20137569</t>
+  </si>
+  <si>
+    <t>BISKUAT GOLD.STR105G</t>
+  </si>
+  <si>
+    <t>20137568</t>
+  </si>
+  <si>
+    <t>BISKUAT GOLD.VNL105G</t>
+  </si>
+  <si>
+    <t>20131802</t>
+  </si>
+  <si>
+    <t>IMPERIAL BLUBERRY108</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20139973</t>
+  </si>
+  <si>
+    <t>IMPERIAL STRW&amp;CH 100</t>
+  </si>
+  <si>
+    <t>20139951</t>
+  </si>
+  <si>
+    <t>KOKOLA BLCK CKLT 110</t>
+  </si>
+  <si>
+    <t>20140011</t>
+  </si>
+  <si>
+    <t>MILO BISC. CHOCO 96G</t>
+  </si>
+  <si>
+    <t>20106305</t>
+  </si>
+  <si>
+    <t>OREO RED VELVET 105G</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20091225</t>
+  </si>
+  <si>
+    <t>OVLTNE CHO BISC 104G</t>
+  </si>
+  <si>
+    <t>20134970</t>
+  </si>
+  <si>
+    <t>MILO SANDW ORIG 104G</t>
+  </si>
+  <si>
+    <t>20134969</t>
+  </si>
+  <si>
+    <t>MILO SANDW MILK 104G</t>
+  </si>
+  <si>
+    <t>20074990</t>
+  </si>
+  <si>
+    <t>OREO DARK&amp;WHT 105G</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20024644</t>
+  </si>
+  <si>
+    <t>OREO STRAW CREM1105G</t>
+  </si>
+  <si>
+    <t>10016170</t>
+  </si>
+  <si>
+    <t>OREO CHOCO CRM 105G</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20030547</t>
+  </si>
+  <si>
+    <t>OREO ICE CRM BL 105G</t>
+  </si>
+  <si>
+    <t>10035165</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 105G</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20138464</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 147.2G</t>
+  </si>
+  <si>
+    <t>20139740</t>
+  </si>
+  <si>
+    <t>OREO BB MONSTR 110.4</t>
+  </si>
+  <si>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20015338</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CHSE 190</t>
+  </si>
+  <si>
+    <t>20139060</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE ORI 35G</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20139061</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE CKLT 35</t>
+  </si>
+  <si>
+    <t>20048790</t>
+  </si>
+  <si>
+    <t>OREO MINI CHOCO 58.4</t>
+  </si>
+  <si>
+    <t>20048791</t>
+  </si>
+  <si>
+    <t>OREO MINI VANLA 58.4</t>
+  </si>
+  <si>
+    <t>20076573</t>
+  </si>
+  <si>
+    <t>NEXTAR CHO.BRWNS 8'S</t>
+  </si>
+  <si>
+    <t>20071797</t>
+  </si>
+  <si>
+    <t>NEXTAR PINEAPPLE 8'S</t>
+  </si>
+  <si>
+    <t>20130555</t>
+  </si>
+  <si>
+    <t>NEXTAR RICHOCO 8'S</t>
+  </si>
+  <si>
+    <t>20122072</t>
+  </si>
+  <si>
+    <t>NUTELLA B-READY/F 22</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20071746</t>
+  </si>
+  <si>
+    <t>SPRSTAR TRPL.CHO 6'S</t>
+  </si>
+  <si>
     <t>10032077</t>
   </si>
   <si>
     <t>NSSIN LG.STK BISC 90</t>
   </si>
   <si>
-    <t>20071746</t>
-  </si>
-  <si>
-    <t>SPRSTAR TRPL.CHO 6'S</t>
-  </si>
-  <si>
-    <t>20090169</t>
-  </si>
-  <si>
-    <t>GERY KR.BRS ASN 10'S</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20141391</t>
-  </si>
-  <si>
-    <t>MONDE SNACK CHEESE50</t>
-  </si>
-  <si>
-    <t>10000461</t>
-  </si>
-  <si>
-    <t>MONDE SERENA GOLD 50</t>
-  </si>
-  <si>
-    <t>20099687</t>
-  </si>
-  <si>
-    <t>MONDE SPCY TOMAT 50G</t>
-  </si>
-  <si>
-    <t>10000562</t>
-  </si>
-  <si>
-    <t>MONDE EGG DROPS 110G</t>
-  </si>
-  <si>
-    <t>10002258</t>
-  </si>
-  <si>
-    <t>MONDE BISC PBIS 190G</t>
-  </si>
-  <si>
-    <t>20085046</t>
-  </si>
-  <si>
-    <t>JULIES PNUT BTR 82.5</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20057475</t>
-  </si>
-  <si>
-    <t>SERENA TOGO CKLT 128</t>
-  </si>
-  <si>
-    <t>20095021</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CKLT 76G</t>
-  </si>
-  <si>
-    <t>20129409</t>
-  </si>
-  <si>
-    <t>NEXTAR NOIR CHO 144</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20122285</t>
-  </si>
-  <si>
-    <t>NEXTAR NOIR C&amp;C 144</t>
-  </si>
-  <si>
-    <t>20137569</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.STR105G</t>
-  </si>
-  <si>
-    <t>20137568</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.VNL105G</t>
-  </si>
-  <si>
-    <t>20131802</t>
-  </si>
-  <si>
-    <t>IMPERIAL BLUBERRY108</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20139973</t>
-  </si>
-  <si>
-    <t>IMPERIAL STRW&amp;CH 100</t>
-  </si>
-  <si>
-    <t>20139951</t>
-  </si>
-  <si>
-    <t>KOKOLA BLCK CKLT 110</t>
-  </si>
-  <si>
-    <t>20140011</t>
-  </si>
-  <si>
-    <t>MILO BISC. CHOCO 96G</t>
-  </si>
-  <si>
-    <t>20106305</t>
-  </si>
-  <si>
-    <t>OREO RED VELVET 105G</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20091225</t>
-  </si>
-  <si>
-    <t>OVLTNE CHO BISC 104G</t>
-  </si>
-  <si>
-    <t>20134970</t>
-  </si>
-  <si>
-    <t>MILO SANDW ORIG 104G</t>
-  </si>
-  <si>
-    <t>20134969</t>
-  </si>
-  <si>
-    <t>MILO SANDW MILK 104G</t>
-  </si>
-  <si>
-    <t>20074990</t>
-  </si>
-  <si>
-    <t>OREO DARK&amp;WHT 105G</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20024644</t>
-  </si>
-  <si>
-    <t>OREO STRAW CREM1105G</t>
-  </si>
-  <si>
-    <t>10016170</t>
-  </si>
-  <si>
-    <t>OREO CHOCO CRM 105G</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20030547</t>
-  </si>
-  <si>
-    <t>OREO ICE CRM BL 105G</t>
-  </si>
-  <si>
-    <t>10035165</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 105G</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20138464</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 147.2G</t>
-  </si>
-  <si>
-    <t>20139740</t>
-  </si>
-  <si>
-    <t>OREO BB MONSTR 110.4</t>
-  </si>
-  <si>
-    <t>20015337</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW COKL 190</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20015338</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CHSE 190</t>
-  </si>
-  <si>
-    <t>20139060</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE ORI 35G</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20139061</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE CKLT 35</t>
-  </si>
-  <si>
-    <t>20048790</t>
-  </si>
-  <si>
-    <t>OREO MINI CHOCO 58.4</t>
-  </si>
-  <si>
-    <t>20048791</t>
-  </si>
-  <si>
-    <t>OREO MINI VANLA 58.4</t>
-  </si>
-  <si>
-    <t>20076573</t>
-  </si>
-  <si>
-    <t>NEXTAR CHO.BRWNS 8'S</t>
-  </si>
-  <si>
-    <t>20071797</t>
-  </si>
-  <si>
-    <t>NEXTAR PINEAPPLE 8'S</t>
-  </si>
-  <si>
-    <t>20130555</t>
-  </si>
-  <si>
-    <t>NEXTAR RICHOCO 8'S</t>
-  </si>
-  <si>
-    <t>20138465</t>
-  </si>
-  <si>
-    <t>NEXTAR STRAWBRY 90G</t>
-  </si>
-  <si>
-    <t>20122072</t>
-  </si>
-  <si>
-    <t>NUTELLA B-READY/F 22</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
     <t>20025592</t>
   </si>
   <si>
@@ -1246,15 +1252,21 @@
     <t>BISKUAT COKLAT121.6G</t>
   </si>
   <si>
+    <t>20133020</t>
+  </si>
+  <si>
+    <t>NISSIN CRACK.LMON200</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>20118424</t>
   </si>
   <si>
     <t>KG SALTCHEESE S&amp;S200</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>10001826</t>
   </si>
   <si>
@@ -1273,21 +1285,15 @@
     <t>NSIN BSC KLP IJO 280</t>
   </si>
   <si>
-    <t>20133020</t>
-  </si>
-  <si>
-    <t>NISSIN CRACK.LMON200</t>
+    <t>10000206</t>
+  </si>
+  <si>
+    <t>NISSIN CR.CRISPY 250</t>
   </si>
   <si>
     <t>41</t>
   </si>
   <si>
-    <t>10000206</t>
-  </si>
-  <si>
-    <t>NISSIN CR.CRISPY 250</t>
-  </si>
-  <si>
     <t>20137760</t>
   </si>
   <si>
@@ -1300,6 +1306,18 @@
     <t>BRIO POTATO BBQ 49G</t>
   </si>
   <si>
+    <t>20046434</t>
+  </si>
+  <si>
+    <t>BRIO POTATO BISC 56G</t>
+  </si>
+  <si>
+    <t>20142222</t>
+  </si>
+  <si>
+    <t>RITZ CRCKS KYA BUT91</t>
+  </si>
+  <si>
     <t>20095220</t>
   </si>
   <si>
@@ -1337,12 +1355,6 @@
   </si>
   <si>
     <t>RITZ CRCKRS CHSE 91G</t>
-  </si>
-  <si>
-    <t>20046434</t>
-  </si>
-  <si>
-    <t>BRIO POTATO BISC 56G</t>
   </si>
   <si>
     <t>20063359</t>
@@ -1813,7 +1825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3077,7 +3089,7 @@
         <v>140</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3097,7 +3109,7 @@
         <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3117,7 +3129,7 @@
         <v>140</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3137,7 +3149,7 @@
         <v>140</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3157,7 +3169,7 @@
         <v>140</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3177,7 +3189,7 @@
         <v>140</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>24</v>
@@ -3677,7 +3689,7 @@
         <v>206</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>207</v>
@@ -3697,7 +3709,7 @@
         <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3717,7 +3729,7 @@
         <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>18</v>
@@ -4300,15 +4312,15 @@
         <v>76</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>278</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4320,7 +4332,7 @@
         <v>79</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>280</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4334,10 +4346,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4345,19 +4357,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4374,10 +4386,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4394,13 +4406,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4414,13 +4426,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4434,30 +4446,30 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4474,10 +4486,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4494,10 +4506,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4514,10 +4526,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4525,19 +4537,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4554,10 +4566,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4574,10 +4586,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4585,19 +4597,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4614,10 +4626,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4634,13 +4646,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4654,30 +4666,30 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4694,10 +4706,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4714,10 +4726,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4734,10 +4746,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4754,10 +4766,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4765,19 +4777,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4794,10 +4806,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4805,19 +4817,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4834,10 +4846,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4854,10 +4866,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4874,10 +4886,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4885,19 +4897,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4914,10 +4926,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4934,10 +4946,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4954,10 +4966,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4965,19 +4977,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4994,10 +5006,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -5014,10 +5026,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5034,10 +5046,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5045,19 +5057,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5074,13 +5086,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5094,10 +5106,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>24</v>
@@ -5114,13 +5126,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5134,10 +5146,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5154,10 +5166,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5174,10 +5186,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5194,10 +5206,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5214,53 +5226,53 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>381</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F171" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5274,13 +5286,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5294,13 +5306,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>381</v>
+        <v>18</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5314,13 +5326,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5334,30 +5346,30 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>18</v>
+        <v>383</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>18</v>
@@ -5374,10 +5386,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>18</v>
@@ -5394,10 +5406,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>18</v>
@@ -5414,30 +5426,30 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5454,10 +5466,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5474,10 +5486,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5494,10 +5506,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5505,19 +5517,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5534,13 +5546,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5554,10 +5566,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5574,30 +5586,30 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5605,19 +5617,19 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="E190" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5634,10 +5646,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5654,10 +5666,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5665,19 +5677,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5685,19 +5697,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5705,19 +5717,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5734,10 +5746,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5754,10 +5766,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5774,10 +5786,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5794,10 +5806,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5805,19 +5817,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5825,19 +5837,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="E201" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5854,10 +5866,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5874,10 +5886,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5894,10 +5906,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5914,10 +5926,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5925,19 +5937,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5945,19 +5957,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5974,10 +5986,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5994,10 +6006,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6014,12 +6026,52 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E210" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F210" s="1" t="s">
+      <c r="F212" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -58,532 +58,808 @@
     <t>4</t>
   </si>
   <si>
+    <t>20025592</t>
+  </si>
+  <si>
+    <t>K/G WAFER CLASSIC350</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10036899</t>
+  </si>
+  <si>
+    <t>REGAL MARIE BARU 550</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20125628</t>
+  </si>
+  <si>
+    <t>NSSIN WFR CHO/LVA137</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20108817</t>
+  </si>
+  <si>
+    <t>K/G SLTCHS COMBO 175</t>
+  </si>
+  <si>
+    <t>10007336</t>
+  </si>
+  <si>
+    <t>TANGO WFR STRAW 124G</t>
+  </si>
+  <si>
+    <t>20063092</t>
+  </si>
+  <si>
+    <t>SELAMAT DBL CHOCO128</t>
+  </si>
+  <si>
+    <t>10016650</t>
+  </si>
+  <si>
+    <t>SELAMAT WF.CHOCO 128</t>
+  </si>
+  <si>
+    <t>10004541</t>
+  </si>
+  <si>
+    <t>TANGO WFR VNLA 124G</t>
+  </si>
+  <si>
+    <t>10004540</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOCO 124G</t>
+  </si>
+  <si>
+    <t>20133247</t>
+  </si>
+  <si>
+    <t>OREO SOFT CAKE 96G</t>
+  </si>
+  <si>
+    <t>20030358</t>
+  </si>
+  <si>
+    <t>MONDE GNJI MN PIE 50</t>
+  </si>
+  <si>
+    <t>10036942</t>
+  </si>
+  <si>
+    <t>MONDE S.PIE STRW 85G</t>
+  </si>
+  <si>
+    <t>10003324</t>
+  </si>
+  <si>
+    <t>MONDE GENJIE PIE 70G</t>
+  </si>
+  <si>
+    <t>20139391</t>
+  </si>
+  <si>
+    <t>NEXTAR CHOC PIE 6S</t>
+  </si>
+  <si>
+    <t>20140126</t>
+  </si>
+  <si>
+    <t>NEXTAR STRAWB CHS156</t>
+  </si>
+  <si>
+    <t>20083539</t>
+  </si>
+  <si>
+    <t>DELFI CUSTAS SC 6'S</t>
+  </si>
+  <si>
+    <t>20052630</t>
+  </si>
+  <si>
+    <t>LOTTE CHOCO PIE 156G</t>
+  </si>
+  <si>
+    <t>20096783</t>
+  </si>
+  <si>
+    <t>DELFI CHO.PIE DRK180</t>
+  </si>
+  <si>
+    <t>20136934</t>
+  </si>
+  <si>
+    <t>LOTTE C/PIE STRWB156</t>
+  </si>
+  <si>
+    <t>20052628</t>
+  </si>
+  <si>
+    <t>LOTTE CHOCO PIE 52G</t>
+  </si>
+  <si>
+    <t>20056645</t>
+  </si>
+  <si>
+    <t>NARAYA OAT CHOCO 90G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10008580</t>
+  </si>
+  <si>
+    <t>DELFI MINIS CHOCO 70</t>
+  </si>
+  <si>
+    <t>10008579</t>
+  </si>
+  <si>
+    <t>DELFI MINIS BLK.VN70</t>
+  </si>
+  <si>
+    <t>20132494</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS KJU33</t>
+  </si>
+  <si>
+    <t>20130152</t>
+  </si>
+  <si>
+    <t>LEMONILO BROWNIES 33</t>
+  </si>
+  <si>
+    <t>20137230</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS STR33</t>
+  </si>
+  <si>
+    <t>20137584</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHOCIP35</t>
+  </si>
+  <si>
+    <t>20137583</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHEESE35</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20139819</t>
+  </si>
+  <si>
+    <t>TANGO BROWNIS CR.35G</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20061189</t>
+  </si>
+  <si>
+    <t>NARAYA OAT CHOCO 90</t>
+  </si>
+  <si>
+    <t>20133506</t>
+  </si>
+  <si>
+    <t>DELFI KRICE SWET64.8</t>
+  </si>
+  <si>
+    <t>20133507</t>
+  </si>
+  <si>
+    <t>DELFI KRICE SWD 47.4</t>
+  </si>
+  <si>
+    <t>20102638</t>
+  </si>
+  <si>
+    <t>DEKA WFR BITE CHO 72</t>
+  </si>
+  <si>
+    <t>20083487</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOCO 95G</t>
+  </si>
+  <si>
+    <t>20083488</t>
+  </si>
+  <si>
+    <t>TANGO WFR VANL 95G</t>
+  </si>
+  <si>
+    <t>20138099</t>
+  </si>
+  <si>
+    <t>OVALTINE MB WFR 100G</t>
+  </si>
+  <si>
+    <t>20139081</t>
+  </si>
+  <si>
+    <t>REGAL CHO MARIE 64G</t>
+  </si>
+  <si>
+    <t>20130007</t>
+  </si>
+  <si>
+    <t>BETTER FUN BITES 10S</t>
+  </si>
+  <si>
+    <t>10000132</t>
+  </si>
+  <si>
+    <t>MONDE BT.COOKIES 454</t>
+  </si>
+  <si>
+    <t>10000734</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHOCO 570</t>
+  </si>
+  <si>
+    <t>20010655</t>
+  </si>
+  <si>
+    <t>TANGO WFER CHOCO 240</t>
+  </si>
+  <si>
+    <t>10000133</t>
+  </si>
+  <si>
+    <t>KHONG GUAN MN ASS650</t>
+  </si>
+  <si>
+    <t>10000360</t>
+  </si>
+  <si>
+    <t>KHONG GUAN RED 1600G</t>
+  </si>
+  <si>
+    <t>20129572</t>
+  </si>
+  <si>
+    <t>CHCLATOS WFR VNLA90</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20127761</t>
+  </si>
+  <si>
+    <t>CHCLATOS WFR CHO 90</t>
+  </si>
+  <si>
+    <t>10000175</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHO 110G</t>
+  </si>
+  <si>
+    <t>20109917</t>
+  </si>
+  <si>
+    <t>ROMA WFR CHO BLS97.6</t>
+  </si>
+  <si>
+    <t>20055311</t>
+  </si>
+  <si>
+    <t>NABATI RCHSE WFR 110</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20055312</t>
+  </si>
+  <si>
+    <t>NBATI RCHCO WFR C110</t>
+  </si>
+  <si>
+    <t>20138462</t>
+  </si>
+  <si>
+    <t>NABATI WFR STRAW 122</t>
+  </si>
+  <si>
+    <t>20069149</t>
+  </si>
+  <si>
+    <t>TANGO WFR LG VAN 100</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20138977</t>
+  </si>
+  <si>
+    <t>TANGO WFR LG CHES100</t>
+  </si>
+  <si>
+    <t>20128683</t>
+  </si>
+  <si>
+    <t>TANGO WFLE CHO HZL63</t>
+  </si>
+  <si>
+    <t>20027448</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOC 100G</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>10000726</t>
+  </si>
+  <si>
+    <t>ASTOR CHOCOLATE 150G</t>
+  </si>
+  <si>
+    <t>20139686</t>
+  </si>
+  <si>
+    <t>TANGO WFLE WAHH 67.5</t>
+  </si>
+  <si>
+    <t>20139392</t>
+  </si>
+  <si>
+    <t>BRINGZ LMIER BTR 100</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20137570</t>
+  </si>
+  <si>
+    <t>NABATI BIG RL CHS48G</t>
+  </si>
+  <si>
+    <t>20138461</t>
+  </si>
+  <si>
+    <t>NABATI ROLL STRAW 55</t>
+  </si>
+  <si>
+    <t>20138332</t>
+  </si>
+  <si>
+    <t>CHOCOLATOS RICH 54G</t>
+  </si>
+  <si>
+    <t>10036934</t>
+  </si>
+  <si>
+    <t>ASTOR CHOCOLATE 40G</t>
+  </si>
+  <si>
+    <t>20129863</t>
+  </si>
+  <si>
+    <t>NYAM2 SMILEY CKL 45G</t>
+  </si>
+  <si>
+    <t>20099762</t>
+  </si>
+  <si>
+    <t>NYAM2 POPSTIX CHO 48</t>
+  </si>
+  <si>
+    <t>20138261</t>
+  </si>
+  <si>
+    <t>POCKY BLUEBERRY 38G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20141134</t>
+  </si>
+  <si>
+    <t>POCKY STRAW YOGRT 38</t>
+  </si>
+  <si>
+    <t>20065180</t>
+  </si>
+  <si>
+    <t>GLICO PEJOY CHO 30G</t>
+  </si>
+  <si>
+    <t>20039648</t>
+  </si>
+  <si>
+    <t>LOTTE PEPERO ALMND32</t>
+  </si>
+  <si>
+    <t>20060710</t>
+  </si>
+  <si>
+    <t>LOTTE PEPERO WHT.C32</t>
+  </si>
+  <si>
+    <t>10038704</t>
+  </si>
+  <si>
+    <t>MEIJI H/PANDA CHOC42</t>
+  </si>
+  <si>
+    <t>10004490</t>
+  </si>
+  <si>
+    <t>HELLO PANDA STRW 42G</t>
+  </si>
+  <si>
+    <t>20134559</t>
+  </si>
+  <si>
+    <t>HLO PANDA DB.CHO 42G</t>
+  </si>
+  <si>
+    <t>10000213</t>
+  </si>
+  <si>
+    <t>GLICO POCKY CHO 47GR</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>10036916</t>
+  </si>
+  <si>
+    <t>GLICO POCKY.STRAW 45</t>
+  </si>
+  <si>
+    <t>20086168</t>
+  </si>
+  <si>
+    <t>GLCO POCKY COOK&amp;CR40</t>
+  </si>
+  <si>
+    <t>20138741</t>
+  </si>
+  <si>
+    <t>GLICO POCKY MILK 39G</t>
+  </si>
+  <si>
+    <t>20138740</t>
+  </si>
+  <si>
+    <t>POCKY MILK CHOCO 39G</t>
+  </si>
+  <si>
+    <t>20062839</t>
+  </si>
+  <si>
+    <t>GLCO POCKY MTCHA 33G</t>
+  </si>
+  <si>
+    <t>20057865</t>
+  </si>
+  <si>
+    <t>GLCO POCKY DOU.CHO47</t>
+  </si>
+  <si>
+    <t>20134839</t>
+  </si>
+  <si>
+    <t>POCKY CRSHD DRK.CH25</t>
+  </si>
+  <si>
+    <t>20142268</t>
+  </si>
+  <si>
+    <t>GLICO PJOY TIRAMIS30</t>
+  </si>
+  <si>
+    <t>20142267</t>
+  </si>
+  <si>
+    <t>POCKY PASION FRUIT38</t>
+  </si>
+  <si>
     <t>10006131</t>
   </si>
   <si>
     <t>AIM ROASTED CORN 180</t>
   </si>
   <si>
-    <t>5</t>
+    <t>17</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>10036899</t>
-  </si>
-  <si>
-    <t>REGAL MARIE BARU 550</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20125628</t>
-  </si>
-  <si>
-    <t>NSSIN WFR CHO/LVA137</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20108817</t>
-  </si>
-  <si>
-    <t>K/G SLTCHS COMBO 175</t>
-  </si>
-  <si>
-    <t>10007336</t>
-  </si>
-  <si>
-    <t>TANGO WFR STRAW 124G</t>
-  </si>
-  <si>
-    <t>20063092</t>
-  </si>
-  <si>
-    <t>SELAMAT DBL CHOCO128</t>
-  </si>
-  <si>
-    <t>10016650</t>
-  </si>
-  <si>
-    <t>SELAMAT WF.CHOCO 128</t>
-  </si>
-  <si>
-    <t>10004541</t>
-  </si>
-  <si>
-    <t>TANGO WFR VNLA 124G</t>
-  </si>
-  <si>
-    <t>10004540</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOCO 124G</t>
-  </si>
-  <si>
-    <t>20133247</t>
-  </si>
-  <si>
-    <t>OREO SOFT CAKE 96G</t>
-  </si>
-  <si>
-    <t>20030358</t>
-  </si>
-  <si>
-    <t>MONDE GNJI MN PIE 50</t>
-  </si>
-  <si>
-    <t>10036942</t>
-  </si>
-  <si>
-    <t>MONDE S.PIE STRW 85G</t>
-  </si>
-  <si>
-    <t>10003324</t>
-  </si>
-  <si>
-    <t>MONDE GENJIE PIE 70G</t>
-  </si>
-  <si>
-    <t>20139391</t>
-  </si>
-  <si>
-    <t>NEXTAR CHOC PIE 6S</t>
-  </si>
-  <si>
-    <t>20140126</t>
-  </si>
-  <si>
-    <t>NEXTAR STRAWB CHS156</t>
-  </si>
-  <si>
-    <t>20083539</t>
-  </si>
-  <si>
-    <t>DELFI CUSTAS SC 6'S</t>
-  </si>
-  <si>
-    <t>20052630</t>
-  </si>
-  <si>
-    <t>LOTTE CHOCO PIE 156G</t>
-  </si>
-  <si>
-    <t>20096783</t>
-  </si>
-  <si>
-    <t>DELFI CHO.PIE DRK180</t>
-  </si>
-  <si>
-    <t>20136934</t>
-  </si>
-  <si>
-    <t>LOTTE C/PIE STRWB156</t>
-  </si>
-  <si>
-    <t>20052628</t>
-  </si>
-  <si>
-    <t>LOTTE CHOCO PIE 52G</t>
-  </si>
-  <si>
-    <t>20056645</t>
-  </si>
-  <si>
-    <t>NARAYA OAT CHOCO 90G</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10008580</t>
-  </si>
-  <si>
-    <t>DELFI MINIS CHOCO 70</t>
-  </si>
-  <si>
-    <t>10008579</t>
-  </si>
-  <si>
-    <t>DELFI MINIS BLK.VN70</t>
-  </si>
-  <si>
-    <t>20132494</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS KJU33</t>
-  </si>
-  <si>
-    <t>20130152</t>
-  </si>
-  <si>
-    <t>LEMONILO BROWNIES 33</t>
-  </si>
-  <si>
-    <t>20137230</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS STR33</t>
-  </si>
-  <si>
-    <t>20137584</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHOCIP35</t>
-  </si>
-  <si>
-    <t>20137583</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHEESE35</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20139819</t>
-  </si>
-  <si>
-    <t>TANGO BROWNIS CR.35G</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20061189</t>
-  </si>
-  <si>
-    <t>NARAYA OAT CHOCO 90</t>
-  </si>
-  <si>
-    <t>20133506</t>
-  </si>
-  <si>
-    <t>DELFI KRICE SWET64.8</t>
-  </si>
-  <si>
-    <t>20133507</t>
-  </si>
-  <si>
-    <t>DELFI KRICE SWD 47.4</t>
-  </si>
-  <si>
-    <t>20102638</t>
-  </si>
-  <si>
-    <t>DEKA WFR BITE CHO 72</t>
-  </si>
-  <si>
-    <t>20083487</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOCO 95G</t>
-  </si>
-  <si>
-    <t>20083488</t>
-  </si>
-  <si>
-    <t>TANGO WFR VANL 95G</t>
-  </si>
-  <si>
-    <t>20138099</t>
-  </si>
-  <si>
-    <t>OVALTINE MB WFR 100G</t>
-  </si>
-  <si>
-    <t>20139081</t>
-  </si>
-  <si>
-    <t>REGAL CHO MARIE 64G</t>
-  </si>
-  <si>
-    <t>20130007</t>
-  </si>
-  <si>
-    <t>BETTER FUN BITES 10S</t>
-  </si>
-  <si>
-    <t>10000132</t>
-  </si>
-  <si>
-    <t>MONDE BT.COOKIES 454</t>
-  </si>
-  <si>
-    <t>10000734</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHOCO 570</t>
-  </si>
-  <si>
-    <t>20010655</t>
-  </si>
-  <si>
-    <t>TANGO WFER CHOCO 240</t>
-  </si>
-  <si>
-    <t>10000133</t>
-  </si>
-  <si>
-    <t>KHONG GUAN MN ASS650</t>
-  </si>
-  <si>
-    <t>10000360</t>
-  </si>
-  <si>
-    <t>KHONG GUAN RED 1600G</t>
-  </si>
-  <si>
-    <t>20129572</t>
-  </si>
-  <si>
-    <t>CHCLATOS WFR VNLA90</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20127761</t>
-  </si>
-  <si>
-    <t>CHCLATOS WFR CHO 90</t>
-  </si>
-  <si>
-    <t>10000175</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHO 110G</t>
-  </si>
-  <si>
-    <t>20109917</t>
-  </si>
-  <si>
-    <t>ROMA WFR CHO BLS97.6</t>
-  </si>
-  <si>
-    <t>20055311</t>
-  </si>
-  <si>
-    <t>NABATI RCHSE WFR 110</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20055312</t>
-  </si>
-  <si>
-    <t>NBATI RCHCO WFR C110</t>
-  </si>
-  <si>
-    <t>20138462</t>
-  </si>
-  <si>
-    <t>NABATI WFR STRAW 122</t>
-  </si>
-  <si>
-    <t>20069149</t>
-  </si>
-  <si>
-    <t>TANGO WFR LG VAN 100</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20138977</t>
-  </si>
-  <si>
-    <t>TANGO WFR LG CHES100</t>
-  </si>
-  <si>
-    <t>20128683</t>
-  </si>
-  <si>
-    <t>TANGO WFLE CHO HZL63</t>
-  </si>
-  <si>
-    <t>20027448</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOC 100G</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10000726</t>
-  </si>
-  <si>
-    <t>ASTOR CHOCOLATE 150G</t>
-  </si>
-  <si>
-    <t>20139686</t>
-  </si>
-  <si>
-    <t>TANGO WFLE WAHH 67.5</t>
-  </si>
-  <si>
-    <t>20139392</t>
-  </si>
-  <si>
-    <t>BRINGZ LMIER BTR 100</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20137570</t>
-  </si>
-  <si>
-    <t>NABATI BIG RL CHS48G</t>
-  </si>
-  <si>
-    <t>20138461</t>
-  </si>
-  <si>
-    <t>NABATI ROLL STRAW 55</t>
-  </si>
-  <si>
-    <t>20138332</t>
-  </si>
-  <si>
-    <t>CHOCOLATOS RICH 54G</t>
-  </si>
-  <si>
-    <t>10036934</t>
-  </si>
-  <si>
-    <t>ASTOR CHOCOLATE 40G</t>
-  </si>
-  <si>
-    <t>20129863</t>
-  </si>
-  <si>
-    <t>NYAM2 SMILEY CKL 45G</t>
-  </si>
-  <si>
-    <t>20099762</t>
-  </si>
-  <si>
-    <t>NYAM2 POPSTIX CHO 48</t>
-  </si>
-  <si>
-    <t>20138261</t>
-  </si>
-  <si>
-    <t>POCKY BLUEBERRY 38G</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20141134</t>
-  </si>
-  <si>
-    <t>POCKY STRAW YOGRT 38</t>
-  </si>
-  <si>
-    <t>20065180</t>
-  </si>
-  <si>
-    <t>GLICO PEJOY CHO 30G</t>
-  </si>
-  <si>
-    <t>20039648</t>
-  </si>
-  <si>
-    <t>LOTTE PEPERO ALMND32</t>
-  </si>
-  <si>
-    <t>20060710</t>
-  </si>
-  <si>
-    <t>LOTTE PEPERO WHT.C32</t>
-  </si>
-  <si>
-    <t>10038704</t>
-  </si>
-  <si>
-    <t>MEIJI H/PANDA CHOC42</t>
-  </si>
-  <si>
-    <t>10004490</t>
-  </si>
-  <si>
-    <t>HELLO PANDA STRW 42G</t>
-  </si>
-  <si>
-    <t>20134559</t>
-  </si>
-  <si>
-    <t>HLO PANDA DB.CHO 42G</t>
-  </si>
-  <si>
-    <t>10000213</t>
-  </si>
-  <si>
-    <t>GLICO POCKY CHO 47GR</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>10036916</t>
-  </si>
-  <si>
-    <t>GLICO POCKY.STRAW 45</t>
-  </si>
-  <si>
-    <t>20086168</t>
-  </si>
-  <si>
-    <t>GLCO POCKY COOK&amp;CR40</t>
-  </si>
-  <si>
-    <t>20138741</t>
-  </si>
-  <si>
-    <t>GLICO POCKY MILK 39G</t>
-  </si>
-  <si>
-    <t>20138740</t>
-  </si>
-  <si>
-    <t>POCKY MILK CHOCO 39G</t>
-  </si>
-  <si>
-    <t>20062839</t>
-  </si>
-  <si>
-    <t>GLCO POCKY MTCHA 33G</t>
-  </si>
-  <si>
-    <t>20057865</t>
-  </si>
-  <si>
-    <t>GLCO POCKY DOU.CHO47</t>
-  </si>
-  <si>
-    <t>20134839</t>
-  </si>
-  <si>
-    <t>POCKY CRSHD DRK.CH25</t>
-  </si>
-  <si>
-    <t>20142267</t>
-  </si>
-  <si>
-    <t>POCKY PASION FRUIT38</t>
-  </si>
-  <si>
-    <t>20142268</t>
-  </si>
-  <si>
-    <t>GLICO PJOY TIRAMIS30</t>
+    <t>10000461</t>
+  </si>
+  <si>
+    <t>MONDE SERENA GOLD 50</t>
+  </si>
+  <si>
+    <t>20099687</t>
+  </si>
+  <si>
+    <t>MONDE SPCY TOMAT 50G</t>
+  </si>
+  <si>
+    <t>10000562</t>
+  </si>
+  <si>
+    <t>MONDE EGG DROPS 110G</t>
+  </si>
+  <si>
+    <t>10002258</t>
+  </si>
+  <si>
+    <t>MONDE BISC PBIS 190G</t>
+  </si>
+  <si>
+    <t>20141391</t>
+  </si>
+  <si>
+    <t>MONDE SNACK CHEESE50</t>
+  </si>
+  <si>
+    <t>20085046</t>
+  </si>
+  <si>
+    <t>JULIES PNUT BTR 82.5</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20057475</t>
+  </si>
+  <si>
+    <t>SERENA TOGO CKLT 128</t>
+  </si>
+  <si>
+    <t>20095021</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CKLT 76G</t>
+  </si>
+  <si>
+    <t>20129409</t>
+  </si>
+  <si>
+    <t>NEXTAR NOIR CHO 144</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20122285</t>
+  </si>
+  <si>
+    <t>NEXTAR NOIR C&amp;C 144</t>
+  </si>
+  <si>
+    <t>20137569</t>
+  </si>
+  <si>
+    <t>BISKUAT GOLD.STR105G</t>
+  </si>
+  <si>
+    <t>20137568</t>
+  </si>
+  <si>
+    <t>BISKUAT GOLD.VNL105G</t>
+  </si>
+  <si>
+    <t>20131802</t>
+  </si>
+  <si>
+    <t>IMPERIAL BLUBERRY108</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20139973</t>
+  </si>
+  <si>
+    <t>IMPERIAL STRW&amp;CH 100</t>
+  </si>
+  <si>
+    <t>20139951</t>
+  </si>
+  <si>
+    <t>KOKOLA BLCK CKLT 110</t>
+  </si>
+  <si>
+    <t>20091225</t>
+  </si>
+  <si>
+    <t>OVLTNE CHO BISC 104G</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20134970</t>
+  </si>
+  <si>
+    <t>MILO SANDW ORIG 104G</t>
+  </si>
+  <si>
+    <t>20134969</t>
+  </si>
+  <si>
+    <t>MILO SANDW MILK 104G</t>
+  </si>
+  <si>
+    <t>20140011</t>
+  </si>
+  <si>
+    <t>MILO BISC. CHOCO 96G</t>
+  </si>
+  <si>
+    <t>20074990</t>
+  </si>
+  <si>
+    <t>OREO DARK&amp;WHT 105G</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20024644</t>
+  </si>
+  <si>
+    <t>OREO STRAW CREM1105G</t>
+  </si>
+  <si>
+    <t>20106305</t>
+  </si>
+  <si>
+    <t>OREO RED VELVET 105G</t>
+  </si>
+  <si>
+    <t>10016170</t>
+  </si>
+  <si>
+    <t>OREO CHOCO CRM 105G</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20030547</t>
+  </si>
+  <si>
+    <t>OREO ICE CRM BL 105G</t>
+  </si>
+  <si>
+    <t>10035165</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 105G</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20138464</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 147.2G</t>
+  </si>
+  <si>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20015338</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CHSE 190</t>
+  </si>
+  <si>
+    <t>20140253</t>
+  </si>
+  <si>
+    <t>OREO BB MONSTR 220.8</t>
+  </si>
+  <si>
+    <t>20139060</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE ORI 35G</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20139061</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE CKLT 35</t>
+  </si>
+  <si>
+    <t>20048790</t>
+  </si>
+  <si>
+    <t>OREO MINI CHOCO 58.4</t>
+  </si>
+  <si>
+    <t>20048791</t>
+  </si>
+  <si>
+    <t>OREO MINI VANLA 58.4</t>
+  </si>
+  <si>
+    <t>20076573</t>
+  </si>
+  <si>
+    <t>NEXTAR CHO.BRWNS 8'S</t>
+  </si>
+  <si>
+    <t>20071797</t>
+  </si>
+  <si>
+    <t>NEXTAR PINEAPPLE 8'S</t>
+  </si>
+  <si>
+    <t>20130555</t>
+  </si>
+  <si>
+    <t>NEXTAR RICHOCO 8'S</t>
+  </si>
+  <si>
+    <t>20071746</t>
+  </si>
+  <si>
+    <t>SPRSTAR TRPL.CHO 6'S</t>
+  </si>
+  <si>
+    <t>10032077</t>
+  </si>
+  <si>
+    <t>NSSIN LG.STK BISC 90</t>
+  </si>
+  <si>
+    <t>20122072</t>
+  </si>
+  <si>
+    <t>NUTELLA B-READY/F 22</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
   </si>
   <si>
     <t>20090169</t>
@@ -592,282 +868,6 @@
     <t>GERY KR.BRS ASN 10'S</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20141391</t>
-  </si>
-  <si>
-    <t>MONDE SNACK CHEESE50</t>
-  </si>
-  <si>
-    <t>10000461</t>
-  </si>
-  <si>
-    <t>MONDE SERENA GOLD 50</t>
-  </si>
-  <si>
-    <t>20099687</t>
-  </si>
-  <si>
-    <t>MONDE SPCY TOMAT 50G</t>
-  </si>
-  <si>
-    <t>10000562</t>
-  </si>
-  <si>
-    <t>MONDE EGG DROPS 110G</t>
-  </si>
-  <si>
-    <t>10002258</t>
-  </si>
-  <si>
-    <t>MONDE BISC PBIS 190G</t>
-  </si>
-  <si>
-    <t>20085046</t>
-  </si>
-  <si>
-    <t>JULIES PNUT BTR 82.5</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20057475</t>
-  </si>
-  <si>
-    <t>SERENA TOGO CKLT 128</t>
-  </si>
-  <si>
-    <t>20095021</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CKLT 76G</t>
-  </si>
-  <si>
-    <t>20129409</t>
-  </si>
-  <si>
-    <t>NEXTAR NOIR CHO 144</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20122285</t>
-  </si>
-  <si>
-    <t>NEXTAR NOIR C&amp;C 144</t>
-  </si>
-  <si>
-    <t>20137569</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.STR105G</t>
-  </si>
-  <si>
-    <t>20137568</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.VNL105G</t>
-  </si>
-  <si>
-    <t>20131802</t>
-  </si>
-  <si>
-    <t>IMPERIAL BLUBERRY108</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20139973</t>
-  </si>
-  <si>
-    <t>IMPERIAL STRW&amp;CH 100</t>
-  </si>
-  <si>
-    <t>20139951</t>
-  </si>
-  <si>
-    <t>KOKOLA BLCK CKLT 110</t>
-  </si>
-  <si>
-    <t>20140011</t>
-  </si>
-  <si>
-    <t>MILO BISC. CHOCO 96G</t>
-  </si>
-  <si>
-    <t>20106305</t>
-  </si>
-  <si>
-    <t>OREO RED VELVET 105G</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20091225</t>
-  </si>
-  <si>
-    <t>OVLTNE CHO BISC 104G</t>
-  </si>
-  <si>
-    <t>20134970</t>
-  </si>
-  <si>
-    <t>MILO SANDW ORIG 104G</t>
-  </si>
-  <si>
-    <t>20134969</t>
-  </si>
-  <si>
-    <t>MILO SANDW MILK 104G</t>
-  </si>
-  <si>
-    <t>20074990</t>
-  </si>
-  <si>
-    <t>OREO DARK&amp;WHT 105G</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20024644</t>
-  </si>
-  <si>
-    <t>OREO STRAW CREM1105G</t>
-  </si>
-  <si>
-    <t>10016170</t>
-  </si>
-  <si>
-    <t>OREO CHOCO CRM 105G</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20030547</t>
-  </si>
-  <si>
-    <t>OREO ICE CRM BL 105G</t>
-  </si>
-  <si>
-    <t>10035165</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 105G</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20138464</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 147.2G</t>
-  </si>
-  <si>
-    <t>20139740</t>
-  </si>
-  <si>
-    <t>OREO BB MONSTR 110.4</t>
-  </si>
-  <si>
-    <t>20015337</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW COKL 190</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20015338</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CHSE 190</t>
-  </si>
-  <si>
-    <t>20139060</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE ORI 35G</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20139061</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE CKLT 35</t>
-  </si>
-  <si>
-    <t>20048790</t>
-  </si>
-  <si>
-    <t>OREO MINI CHOCO 58.4</t>
-  </si>
-  <si>
-    <t>20048791</t>
-  </si>
-  <si>
-    <t>OREO MINI VANLA 58.4</t>
-  </si>
-  <si>
-    <t>20076573</t>
-  </si>
-  <si>
-    <t>NEXTAR CHO.BRWNS 8'S</t>
-  </si>
-  <si>
-    <t>20071797</t>
-  </si>
-  <si>
-    <t>NEXTAR PINEAPPLE 8'S</t>
-  </si>
-  <si>
-    <t>20130555</t>
-  </si>
-  <si>
-    <t>NEXTAR RICHOCO 8'S</t>
-  </si>
-  <si>
-    <t>20122072</t>
-  </si>
-  <si>
-    <t>NUTELLA B-READY/F 22</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20071746</t>
-  </si>
-  <si>
-    <t>SPRSTAR TRPL.CHO 6'S</t>
-  </si>
-  <si>
-    <t>10032077</t>
-  </si>
-  <si>
-    <t>NSSIN LG.STK BISC 90</t>
-  </si>
-  <si>
-    <t>20025592</t>
-  </si>
-  <si>
-    <t>K/G WAFER CLASSIC350</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
@@ -883,45 +883,45 @@
     <t>K/G CRACKERS CRM 350</t>
   </si>
   <si>
+    <t>20126401</t>
+  </si>
+  <si>
+    <t>KOKOLA KKS VANLA 218</t>
+  </si>
+  <si>
+    <t>20013332</t>
+  </si>
+  <si>
+    <t>K/G SALTCH CMBO10X17</t>
+  </si>
+  <si>
+    <t>20008887</t>
+  </si>
+  <si>
+    <t>MONDE SERENA EGG 168</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>10036931</t>
+  </si>
+  <si>
+    <t>MONDE BT.COOKIES 150</t>
+  </si>
+  <si>
+    <t>20135148</t>
+  </si>
+  <si>
+    <t>MONDE SHRTBRD MTG115</t>
+  </si>
+  <si>
     <t>10038628</t>
   </si>
   <si>
     <t>HATARI BIS.PEANUT225</t>
   </si>
   <si>
-    <t>20126401</t>
-  </si>
-  <si>
-    <t>KOKOLA KKS VANLA 218</t>
-  </si>
-  <si>
-    <t>20008887</t>
-  </si>
-  <si>
-    <t>MONDE SERENA EGG 168</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>10036931</t>
-  </si>
-  <si>
-    <t>MONDE BT.COOKIES 150</t>
-  </si>
-  <si>
-    <t>20135148</t>
-  </si>
-  <si>
-    <t>MONDE SHRTBRD MTG115</t>
-  </si>
-  <si>
-    <t>20013332</t>
-  </si>
-  <si>
-    <t>K/G SALTCH CMBO10X17</t>
-  </si>
-  <si>
     <t>10033424</t>
   </si>
   <si>
@@ -997,27 +997,27 @@
     <t>NISSIN CHOCO SOES100</t>
   </si>
   <si>
+    <t>20111641</t>
+  </si>
+  <si>
+    <t>BETTER VANILLA 100G</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20063488</t>
+  </si>
+  <si>
+    <t>ROMA ARDEN CHOCO 72G</t>
+  </si>
+  <si>
     <t>10002246</t>
   </si>
   <si>
     <t>NISSIN LEMONIA 130GR</t>
   </si>
   <si>
-    <t>20111641</t>
-  </si>
-  <si>
-    <t>BETTER VANILLA 100G</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20063488</t>
-  </si>
-  <si>
-    <t>ROMA ARDEN CHOCO 72G</t>
-  </si>
-  <si>
     <t>20033519</t>
   </si>
   <si>
@@ -1345,16 +1345,16 @@
     <t>RITZ CRCKRS CHOC 91G</t>
   </si>
   <si>
+    <t>20134983</t>
+  </si>
+  <si>
+    <t>RITZ CRCKRS CHSE 91G</t>
+  </si>
+  <si>
     <t>20141506</t>
   </si>
   <si>
     <t>RITZ CRACKER ORI 100</t>
-  </si>
-  <si>
-    <t>20134983</t>
-  </si>
-  <si>
-    <t>RITZ CRCKRS CHSE 91G</t>
   </si>
   <si>
     <t>20063359</t>
@@ -1952,15 +1952,15 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -1969,7 +1969,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -1977,10 +1977,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -1992,15 +1992,15 @@
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -2177,10 +2177,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2257,16 +2257,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>4</v>
@@ -2277,16 +2277,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>8</v>
@@ -2297,16 +2297,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>11</v>
@@ -2317,16 +2317,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>14</v>
@@ -2337,36 +2337,36 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>8</v>
@@ -2377,16 +2377,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>11</v>
@@ -2397,16 +2397,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>14</v>
@@ -2417,16 +2417,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>17</v>
@@ -2437,19 +2437,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2457,19 +2457,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2477,19 +2477,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2497,19 +2497,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2517,36 +2517,36 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>8</v>
@@ -2557,16 +2557,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>11</v>
@@ -2577,16 +2577,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>14</v>
@@ -2597,16 +2597,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>17</v>
@@ -2617,19 +2617,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2637,19 +2637,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2657,19 +2657,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2677,19 +2677,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2697,16 +2697,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>4</v>
@@ -2717,16 +2717,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>8</v>
@@ -2737,16 +2737,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>11</v>
@@ -2757,16 +2757,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>14</v>
@@ -2777,16 +2777,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>17</v>
@@ -2797,16 +2797,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>4</v>
@@ -2817,16 +2817,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>8</v>
@@ -2837,16 +2837,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>11</v>
@@ -2857,16 +2857,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>14</v>
@@ -2877,56 +2877,56 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>11</v>
@@ -2937,16 +2937,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>4</v>
@@ -2957,16 +2957,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>8</v>
@@ -2977,16 +2977,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>11</v>
@@ -2997,16 +2997,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>4</v>
@@ -3017,16 +3017,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>8</v>
@@ -3037,16 +3037,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>11</v>
@@ -3057,16 +3057,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>4</v>
@@ -3077,19 +3077,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3097,19 +3097,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3117,19 +3117,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3137,19 +3137,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3157,19 +3157,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3177,36 +3177,36 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>4</v>
@@ -3217,16 +3217,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
@@ -3237,16 +3237,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>11</v>
@@ -3257,59 +3257,59 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3317,19 +3317,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3337,19 +3337,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3357,16 +3357,16 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>4</v>
@@ -3377,16 +3377,16 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>8</v>
@@ -3397,16 +3397,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>11</v>
@@ -3417,16 +3417,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>14</v>
@@ -3437,16 +3437,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>17</v>
@@ -3457,19 +3457,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3477,19 +3477,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3497,19 +3497,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3517,19 +3517,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3537,19 +3537,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3557,22 +3557,22 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3586,7 +3586,7 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>8</v>
@@ -3606,7 +3606,7 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>11</v>
@@ -3626,7 +3626,7 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>14</v>
@@ -3646,7 +3646,7 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>17</v>
@@ -3666,10 +3666,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3732,7 +3732,7 @@
         <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3886,10 +3886,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3897,19 +3897,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3926,10 +3926,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3946,10 +3946,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3966,10 +3966,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3977,19 +3977,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -4006,10 +4006,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -4106,33 +4106,33 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4146,13 +4146,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4252,7 +4252,7 @@
         <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4269,10 +4269,10 @@
         <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4289,10 +4289,10 @@
         <v>263</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4309,18 +4309,18 @@
         <v>263</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>278</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4329,7 +4329,7 @@
         <v>263</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4349,10 +4349,10 @@
         <v>263</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>282</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4432,7 +4432,7 @@
         <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4452,7 +4452,7 @@
         <v>17</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4532,7 +4532,7 @@
         <v>14</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4672,7 +4672,7 @@
         <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4766,10 +4766,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4777,19 +4777,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4806,10 +4806,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -5112,7 +5112,7 @@
         <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5132,7 +5132,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5169,7 +5169,7 @@
         <v>364</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5189,7 +5189,7 @@
         <v>364</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5209,7 +5209,7 @@
         <v>364</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5229,7 +5229,7 @@
         <v>364</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5249,7 +5249,7 @@
         <v>364</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>383</v>
@@ -5272,7 +5272,7 @@
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5312,7 +5312,7 @@
         <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5372,7 +5372,7 @@
         <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5392,7 +5392,7 @@
         <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5412,7 +5412,7 @@
         <v>11</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5432,7 +5432,7 @@
         <v>14</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5592,7 +5592,7 @@
         <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>18</v>
+        <v>193</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5829,7 +5829,7 @@
         <v>437</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5949,7 +5949,7 @@
         <v>450</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -6069,7 +6069,7 @@
         <v>463</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="476">
   <si>
     <t/>
   </si>
@@ -773,6 +773,12 @@
   </si>
   <si>
     <t>OREO ORIGINAL 147.2G</t>
+  </si>
+  <si>
+    <t>20142591</t>
+  </si>
+  <si>
+    <t>OREO SNDW HOTTEOK105</t>
   </si>
   <si>
     <t>20015337</t>
@@ -1825,7 +1831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F213"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4106,30 +4112,30 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -4146,13 +4152,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4166,10 +4172,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4177,19 +4183,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4206,10 +4212,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4226,10 +4232,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4246,13 +4252,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4266,10 +4272,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>23</v>
@@ -4286,10 +4292,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>23</v>
@@ -4306,13 +4312,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4326,10 +4332,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4346,50 +4352,50 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>282</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4406,10 +4412,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4426,13 +4432,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4446,13 +4452,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4466,10 +4472,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4477,19 +4483,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4506,10 +4512,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4526,13 +4532,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4546,30 +4552,30 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4586,10 +4592,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4606,10 +4612,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4617,19 +4623,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4646,10 +4652,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4666,13 +4672,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4686,30 +4692,30 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4726,10 +4732,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4746,10 +4752,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4766,10 +4772,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4777,19 +4783,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4806,10 +4812,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4826,10 +4832,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4837,19 +4843,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4866,10 +4872,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4886,10 +4892,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4906,10 +4912,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4917,19 +4923,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4946,10 +4952,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4966,10 +4972,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4986,10 +4992,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4997,19 +5003,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -5026,10 +5032,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5046,10 +5052,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5066,10 +5072,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5077,19 +5083,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5106,13 +5112,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5126,10 +5132,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>23</v>
@@ -5146,13 +5152,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5166,10 +5172,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5186,10 +5192,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5206,10 +5212,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5226,10 +5232,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5246,53 +5252,53 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>383</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5306,13 +5312,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5326,13 +5332,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>383</v>
+        <v>193</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5346,13 +5352,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5366,30 +5372,30 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>193</v>
+        <v>385</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>193</v>
@@ -5406,10 +5412,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>193</v>
@@ -5426,10 +5432,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>193</v>
@@ -5446,30 +5452,30 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5486,10 +5492,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5506,10 +5512,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5526,10 +5532,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5537,19 +5543,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5566,10 +5572,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5586,13 +5592,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5606,13 +5612,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5626,10 +5632,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5637,19 +5643,19 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="E191" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5666,10 +5672,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5686,10 +5692,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5706,10 +5712,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5726,10 +5732,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5737,19 +5743,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5766,10 +5772,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5786,10 +5792,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5806,10 +5812,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5826,10 +5832,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5846,10 +5852,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5857,19 +5863,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5886,10 +5892,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5906,10 +5912,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5926,10 +5932,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5946,10 +5952,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5966,10 +5972,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5977,19 +5983,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6006,10 +6012,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6026,10 +6032,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6046,10 +6052,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6066,12 +6072,32 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E212" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E213" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F212" s="1" t="s">
+      <c r="F213" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="474">
   <si>
     <t/>
   </si>
@@ -448,7 +448,7 @@
     <t>20138332</t>
   </si>
   <si>
-    <t>CHOCOLATOS RICH 54G</t>
+    <t>CHCLTOS RICH CHOC54G</t>
   </si>
   <si>
     <t>10036934</t>
@@ -794,12 +794,6 @@
   </si>
   <si>
     <t>LEXUS SANDW CHSE 190</t>
-  </si>
-  <si>
-    <t>20140253</t>
-  </si>
-  <si>
-    <t>OREO BB MONSTR 220.8</t>
   </si>
   <si>
     <t>20139060</t>
@@ -1831,7 +1825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F213"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4172,10 +4166,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4183,19 +4177,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4212,10 +4206,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4232,10 +4226,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4252,13 +4246,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4272,10 +4266,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>23</v>
@@ -4292,10 +4286,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>23</v>
@@ -4312,13 +4306,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4332,10 +4326,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4352,50 +4346,50 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>282</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>284</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4412,10 +4406,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4432,13 +4426,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4452,13 +4446,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4472,10 +4466,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4483,19 +4477,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4512,10 +4506,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4532,13 +4526,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4552,30 +4546,30 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4592,10 +4586,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4612,10 +4606,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4623,19 +4617,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4652,10 +4646,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4672,13 +4666,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4692,30 +4686,30 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4732,10 +4726,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4752,10 +4746,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4772,10 +4766,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4783,19 +4777,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4812,10 +4806,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4832,10 +4826,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4843,19 +4837,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4872,10 +4866,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4892,10 +4886,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4912,10 +4906,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4923,19 +4917,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4952,10 +4946,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4972,10 +4966,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4992,10 +4986,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -5003,19 +4997,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -5032,10 +5026,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5052,10 +5046,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5072,10 +5066,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5083,19 +5077,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5112,13 +5106,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5132,10 +5126,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>23</v>
@@ -5152,13 +5146,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5172,10 +5166,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5192,10 +5186,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5212,10 +5206,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5232,10 +5226,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5252,53 +5246,53 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>383</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>385</v>
+        <v>193</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5312,13 +5306,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5332,13 +5326,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>193</v>
+        <v>383</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5352,13 +5346,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5372,30 +5366,30 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>385</v>
+        <v>193</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>193</v>
@@ -5412,10 +5406,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>193</v>
@@ -5432,10 +5426,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>193</v>
@@ -5452,30 +5446,30 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5492,10 +5486,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5512,10 +5506,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5532,10 +5526,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5543,19 +5537,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5572,10 +5566,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5592,13 +5586,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5612,13 +5606,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5632,10 +5626,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5643,19 +5637,19 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5672,10 +5666,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5692,10 +5686,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5712,10 +5706,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5732,10 +5726,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5743,19 +5737,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5772,10 +5766,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5792,10 +5786,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5812,10 +5806,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5832,10 +5826,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5852,10 +5846,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5863,19 +5857,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5892,10 +5886,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5912,10 +5906,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5932,10 +5926,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5952,10 +5946,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5972,10 +5966,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5983,19 +5977,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6012,10 +6006,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6032,10 +6026,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6052,10 +6046,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6072,32 +6066,12 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F213" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,24 +11,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="482">
   <si>
     <t/>
   </si>
   <si>
+    <t>20142669</t>
+  </si>
+  <si>
+    <t>KTST BGLN GT BUTER45</t>
+  </si>
+  <si>
+    <t>BIS05D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142670</t>
+  </si>
+  <si>
+    <t>KTST BGLN GT CHESE45</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>20106173</t>
   </si>
   <si>
     <t>KR.TOAST BGLN CHS 78</t>
   </si>
   <si>
-    <t>BIS05D</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
+    <t>3</t>
   </si>
   <si>
     <t>20106172</t>
@@ -37,7 +55,7 @@
     <t>KR.TOAST BGLN BTR 72</t>
   </si>
   <si>
-    <t>2</t>
+    <t>4</t>
   </si>
   <si>
     <t>20130350</t>
@@ -46,7 +64,7 @@
     <t>POCKY CHOCOLATE 154</t>
   </si>
   <si>
-    <t>3</t>
+    <t>5</t>
   </si>
   <si>
     <t>20019529</t>
@@ -55,7 +73,7 @@
     <t>NISSIN HEXA CRAK 225</t>
   </si>
   <si>
-    <t>4</t>
+    <t>6</t>
   </si>
   <si>
     <t>20025592</t>
@@ -64,7 +82,7 @@
     <t>K/G WAFER CLASSIC350</t>
   </si>
   <si>
-    <t>5</t>
+    <t>7</t>
   </si>
   <si>
     <t>10036899</t>
@@ -73,7 +91,7 @@
     <t>REGAL MARIE BARU 550</t>
   </si>
   <si>
-    <t>6</t>
+    <t>8</t>
   </si>
   <si>
     <t>20125628</t>
@@ -193,9 +211,6 @@
     <t>NARAYA OAT CHOCO 90G</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>10008580</t>
   </si>
   <si>
@@ -220,6 +235,12 @@
     <t>LEMONILO BROWNIES 33</t>
   </si>
   <si>
+    <t>20142678</t>
+  </si>
+  <si>
+    <t>LMNILO LMN CHESSE 33</t>
+  </si>
+  <si>
     <t>20137230</t>
   </si>
   <si>
@@ -238,7 +259,7 @@
     <t>IDM BROWNIS CHEESE35</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>20139819</t>
@@ -247,7 +268,7 @@
     <t>TANGO BROWNIS CR.35G</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>20061189</t>
@@ -340,9 +361,6 @@
     <t>CHCLATOS WFR VNLA90</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>20127761</t>
   </si>
   <si>
@@ -929,6 +947,12 @@
   </si>
   <si>
     <t>29</t>
+  </si>
+  <si>
+    <t>20142677</t>
+  </si>
+  <si>
+    <t>MONDE BRBON GNDM 140</t>
   </si>
   <si>
     <t>10003144</t>
@@ -1825,7 +1849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F216"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1986,13 +2010,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2006,10 +2030,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -2017,10 +2041,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -2029,27 +2053,27 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -2057,19 +2081,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -2077,10 +2101,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -2089,7 +2113,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -2097,10 +2121,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -2109,7 +2133,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -2117,19 +2141,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -2137,19 +2161,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -2157,10 +2181,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -2169,7 +2193,7 @@
         <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -2177,10 +2201,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -2189,7 +2213,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -2197,19 +2221,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -2217,19 +2241,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -2237,10 +2261,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2249,7 +2273,7 @@
         <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -2257,19 +2281,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -2277,19 +2301,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2297,10 +2321,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -2309,7 +2333,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2317,10 +2341,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -2329,7 +2353,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2337,39 +2361,39 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2377,39 +2401,39 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2417,19 +2441,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2437,19 +2461,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2457,19 +2481,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2477,19 +2501,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2506,10 +2530,10 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2517,39 +2541,39 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2566,10 +2590,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2577,39 +2601,39 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2617,19 +2641,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2637,19 +2661,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2657,19 +2681,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2677,19 +2701,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2697,19 +2721,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2717,19 +2741,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2737,19 +2761,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2757,19 +2781,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2777,19 +2801,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2797,19 +2821,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2826,10 +2850,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2846,10 +2870,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2866,10 +2890,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2886,50 +2910,50 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2937,56 +2961,56 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>11</v>
@@ -2997,16 +3021,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>4</v>
@@ -3017,16 +3041,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>8</v>
@@ -3037,16 +3061,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>11</v>
@@ -3057,16 +3081,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>4</v>
@@ -3077,16 +3101,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>8</v>
@@ -3097,16 +3121,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>11</v>
@@ -3117,19 +3141,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="E65" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3146,10 +3170,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3166,10 +3190,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3186,13 +3210,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3206,10 +3230,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3217,19 +3241,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3237,42 +3261,42 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3286,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3306,10 +3330,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3326,13 +3350,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3346,13 +3370,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3366,10 +3390,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3377,19 +3401,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3397,19 +3421,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3417,19 +3441,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3446,10 +3470,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3466,10 +3490,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3486,10 +3510,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3506,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3526,10 +3550,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3546,10 +3570,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3566,30 +3590,30 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3597,19 +3621,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3617,22 +3641,22 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="E90" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3646,10 +3670,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3666,10 +3690,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3686,30 +3710,30 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>207</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3717,56 +3741,56 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>213</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
@@ -3777,39 +3801,39 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3826,10 +3850,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3837,19 +3861,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3857,19 +3881,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3877,16 +3901,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>4</v>
@@ -3897,16 +3921,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>8</v>
@@ -3917,16 +3941,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>11</v>
@@ -3937,19 +3961,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3966,10 +3990,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3977,19 +4001,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3997,19 +4021,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -4017,16 +4041,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>4</v>
@@ -4037,16 +4061,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>8</v>
@@ -4057,19 +4081,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4077,19 +4101,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4097,19 +4121,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4117,59 +4141,59 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4177,59 +4201,59 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4246,13 +4270,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4266,13 +4290,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4286,13 +4310,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4306,13 +4330,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4326,13 +4350,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4346,30 +4370,30 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>282</v>
+        <v>29</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4377,19 +4401,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4397,42 +4421,42 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4446,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4466,10 +4490,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4477,39 +4501,39 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4517,22 +4541,22 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4546,10 +4570,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4557,19 +4581,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4577,36 +4601,36 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>4</v>
@@ -4617,16 +4641,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>8</v>
@@ -4637,16 +4661,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>11</v>
@@ -4657,36 +4681,36 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>4</v>
@@ -4697,16 +4721,16 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>8</v>
@@ -4717,16 +4741,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>11</v>
@@ -4737,36 +4761,36 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>4</v>
@@ -4777,16 +4801,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>8</v>
@@ -4797,16 +4821,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>11</v>
@@ -4817,19 +4841,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4837,19 +4861,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4857,19 +4881,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4877,19 +4901,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4897,16 +4921,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>4</v>
@@ -4917,16 +4941,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>8</v>
@@ -4937,16 +4961,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>11</v>
@@ -4957,16 +4981,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>14</v>
@@ -4977,16 +5001,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>355</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>4</v>
@@ -4997,16 +5021,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>8</v>
@@ -5017,16 +5041,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>11</v>
@@ -5037,16 +5061,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>14</v>
@@ -5057,16 +5081,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>4</v>
@@ -5077,16 +5101,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>8</v>
@@ -5097,59 +5121,59 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5166,10 +5190,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5186,13 +5210,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5206,13 +5230,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5226,10 +5250,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5246,50 +5270,50 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>383</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5297,62 +5321,62 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F175" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F175" s="1" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>383</v>
+        <v>199</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5366,167 +5390,167 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>193</v>
+        <v>391</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>193</v>
+        <v>391</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>4</v>
@@ -5537,16 +5561,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>8</v>
@@ -5557,16 +5581,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>11</v>
@@ -5577,39 +5601,39 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="E189" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5626,10 +5650,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5637,19 +5661,19 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5657,39 +5681,39 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5697,19 +5721,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="E194" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5726,10 +5750,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5737,19 +5761,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5757,19 +5781,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5777,19 +5801,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5797,19 +5821,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="E199" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5826,10 +5850,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5846,10 +5870,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5857,19 +5881,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5877,19 +5901,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5897,19 +5921,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5917,19 +5941,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5946,10 +5970,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5966,10 +5990,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5977,19 +6001,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5997,19 +6021,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6017,19 +6041,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6037,19 +6061,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="C211" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="E211" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6066,12 +6090,92 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E212" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E216" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F212" s="1" t="s">
+      <c r="F216" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="472">
   <si>
     <t/>
   </si>
@@ -40,153 +40,135 @@
     <t>2</t>
   </si>
   <si>
-    <t>20106173</t>
-  </si>
-  <si>
-    <t>KR.TOAST BGLN CHS 78</t>
+    <t>20130350</t>
+  </si>
+  <si>
+    <t>POCKY CHOCOLATE 154</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20025592</t>
+  </si>
+  <si>
+    <t>K/G WAFER CLASSIC350</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10036899</t>
+  </si>
+  <si>
+    <t>REGAL MARIE BARU 550</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20125628</t>
+  </si>
+  <si>
+    <t>NSSIN WFR CHO/LVA137</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20108817</t>
+  </si>
+  <si>
+    <t>K/G SLTCHS COMBO 175</t>
+  </si>
+  <si>
+    <t>10007336</t>
+  </si>
+  <si>
+    <t>TANGO WFR STRAW 124G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20106172</t>
-  </si>
-  <si>
-    <t>KR.TOAST BGLN BTR 72</t>
+    <t>20063092</t>
+  </si>
+  <si>
+    <t>SELAMAT DBL CHOCO128</t>
+  </si>
+  <si>
+    <t>10016650</t>
+  </si>
+  <si>
+    <t>SELAMAT WF.CHOCO 128</t>
+  </si>
+  <si>
+    <t>10004541</t>
+  </si>
+  <si>
+    <t>TANGO WFR VNLA 124G</t>
+  </si>
+  <si>
+    <t>10004540</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOCO 124G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20130350</t>
-  </si>
-  <si>
-    <t>POCKY CHOCOLATE 154</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20019529</t>
-  </si>
-  <si>
-    <t>NISSIN HEXA CRAK 225</t>
+    <t>20133247</t>
+  </si>
+  <si>
+    <t>OREO SOFT CAKE 96G</t>
+  </si>
+  <si>
+    <t>20030358</t>
+  </si>
+  <si>
+    <t>MONDE GNJI MN PIE 50</t>
+  </si>
+  <si>
+    <t>10036942</t>
+  </si>
+  <si>
+    <t>MONDE S.PIE STRW 85G</t>
+  </si>
+  <si>
+    <t>10003324</t>
+  </si>
+  <si>
+    <t>MONDE GENJIE PIE 70G</t>
+  </si>
+  <si>
+    <t>20139391</t>
+  </si>
+  <si>
+    <t>NEXTAR CHOC PIE 6S</t>
+  </si>
+  <si>
+    <t>20140126</t>
+  </si>
+  <si>
+    <t>NEXTAR STRAWB CHS144</t>
+  </si>
+  <si>
+    <t>20083539</t>
+  </si>
+  <si>
+    <t>DELFI CUSTAS SC 6'S</t>
+  </si>
+  <si>
+    <t>20052630</t>
+  </si>
+  <si>
+    <t>LOTTE CHOCO PIE 156G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20025592</t>
-  </si>
-  <si>
-    <t>K/G WAFER CLASSIC350</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10036899</t>
-  </si>
-  <si>
-    <t>REGAL MARIE BARU 550</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20125628</t>
-  </si>
-  <si>
-    <t>NSSIN WFR CHO/LVA137</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20108817</t>
-  </si>
-  <si>
-    <t>K/G SLTCHS COMBO 175</t>
-  </si>
-  <si>
-    <t>10007336</t>
-  </si>
-  <si>
-    <t>TANGO WFR STRAW 124G</t>
-  </si>
-  <si>
-    <t>20063092</t>
-  </si>
-  <si>
-    <t>SELAMAT DBL CHOCO128</t>
-  </si>
-  <si>
-    <t>10016650</t>
-  </si>
-  <si>
-    <t>SELAMAT WF.CHOCO 128</t>
-  </si>
-  <si>
-    <t>10004541</t>
-  </si>
-  <si>
-    <t>TANGO WFR VNLA 124G</t>
-  </si>
-  <si>
-    <t>10004540</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOCO 124G</t>
-  </si>
-  <si>
-    <t>20133247</t>
-  </si>
-  <si>
-    <t>OREO SOFT CAKE 96G</t>
-  </si>
-  <si>
-    <t>20030358</t>
-  </si>
-  <si>
-    <t>MONDE GNJI MN PIE 50</t>
-  </si>
-  <si>
-    <t>10036942</t>
-  </si>
-  <si>
-    <t>MONDE S.PIE STRW 85G</t>
-  </si>
-  <si>
-    <t>10003324</t>
-  </si>
-  <si>
-    <t>MONDE GENJIE PIE 70G</t>
-  </si>
-  <si>
-    <t>20139391</t>
-  </si>
-  <si>
-    <t>NEXTAR CHOC PIE 6S</t>
-  </si>
-  <si>
-    <t>20140126</t>
-  </si>
-  <si>
-    <t>NEXTAR STRAWB CHS156</t>
-  </si>
-  <si>
-    <t>20083539</t>
-  </si>
-  <si>
-    <t>DELFI CUSTAS SC 6'S</t>
-  </si>
-  <si>
-    <t>20052630</t>
-  </si>
-  <si>
-    <t>LOTTE CHOCO PIE 156G</t>
-  </si>
-  <si>
     <t>20096783</t>
   </si>
   <si>
@@ -211,624 +193,618 @@
     <t>NARAYA OAT CHOCO 90G</t>
   </si>
   <si>
+    <t>20132494</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS KJU33</t>
+  </si>
+  <si>
+    <t>20130152</t>
+  </si>
+  <si>
+    <t>LEMONILO BROWNIES 33</t>
+  </si>
+  <si>
+    <t>20142678</t>
+  </si>
+  <si>
+    <t>LMNILO LMN CHESSE 33</t>
+  </si>
+  <si>
+    <t>20137230</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS STR33</t>
+  </si>
+  <si>
+    <t>20137584</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHOCIP35</t>
+  </si>
+  <si>
+    <t>20137583</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHEESE35</t>
+  </si>
+  <si>
+    <t>20139819</t>
+  </si>
+  <si>
+    <t>TANGO BROWNIS CR.35G</t>
+  </si>
+  <si>
+    <t>20061189</t>
+  </si>
+  <si>
+    <t>NARAYA OAT CHOCO 90</t>
+  </si>
+  <si>
+    <t>20133506</t>
+  </si>
+  <si>
+    <t>DELFI KRICE SWET64.8</t>
+  </si>
+  <si>
+    <t>20133507</t>
+  </si>
+  <si>
+    <t>DELFI KRICE SWD 47.4</t>
+  </si>
+  <si>
+    <t>20102638</t>
+  </si>
+  <si>
+    <t>DEKA WFR BITE CHO 72</t>
+  </si>
+  <si>
+    <t>20083487</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOCO 95G</t>
+  </si>
+  <si>
+    <t>20083488</t>
+  </si>
+  <si>
+    <t>TANGO WFR VANL 95G</t>
+  </si>
+  <si>
+    <t>20138099</t>
+  </si>
+  <si>
+    <t>OVALTINE MB WFR 100G</t>
+  </si>
+  <si>
+    <t>20139081</t>
+  </si>
+  <si>
+    <t>REGAL CHO MARIE 64G</t>
+  </si>
+  <si>
+    <t>20130007</t>
+  </si>
+  <si>
+    <t>BETTER FUN BITES 10S</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10000132</t>
+  </si>
+  <si>
+    <t>MONDE BT.COOKIES 454</t>
+  </si>
+  <si>
+    <t>10000734</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHOCO 570</t>
+  </si>
+  <si>
+    <t>20010655</t>
+  </si>
+  <si>
+    <t>TANGO WFER CHOCO 240</t>
+  </si>
+  <si>
+    <t>10000133</t>
+  </si>
+  <si>
+    <t>KHONG GUAN MN ASS650</t>
+  </si>
+  <si>
+    <t>10000360</t>
+  </si>
+  <si>
+    <t>KHONG GUAN RED 1600G</t>
+  </si>
+  <si>
+    <t>20129572</t>
+  </si>
+  <si>
+    <t>CHCLATOS WFR VNLA90</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20127761</t>
+  </si>
+  <si>
+    <t>CHCLATOS WFR CHO 90</t>
+  </si>
+  <si>
+    <t>10000175</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHO 110G</t>
+  </si>
+  <si>
+    <t>20109917</t>
+  </si>
+  <si>
+    <t>ROMA WFR CHO BLS97.6</t>
+  </si>
+  <si>
+    <t>20055311</t>
+  </si>
+  <si>
+    <t>NABATI RCHSE WFR 110</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20055312</t>
+  </si>
+  <si>
+    <t>NBATI RCHCO WFR C110</t>
+  </si>
+  <si>
+    <t>20138462</t>
+  </si>
+  <si>
+    <t>NABATI WFR STRAW 122</t>
+  </si>
+  <si>
+    <t>20069149</t>
+  </si>
+  <si>
+    <t>TANGO WFR LG VAN 100</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20138977</t>
+  </si>
+  <si>
+    <t>TANGO WFR LG CHES100</t>
+  </si>
+  <si>
+    <t>20128683</t>
+  </si>
+  <si>
+    <t>TANGO WFLE CHO HZL63</t>
+  </si>
+  <si>
+    <t>20027448</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOC 100G</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>10000726</t>
+  </si>
+  <si>
+    <t>ASTOR CHOCOLATE 150G</t>
+  </si>
+  <si>
+    <t>20139686</t>
+  </si>
+  <si>
+    <t>TANGO WFLE WAHH 67.5</t>
+  </si>
+  <si>
+    <t>20139392</t>
+  </si>
+  <si>
+    <t>BRINGZ LMIER BTR 100</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20137570</t>
+  </si>
+  <si>
+    <t>NABATI BIG RL CHS48G</t>
+  </si>
+  <si>
+    <t>20138461</t>
+  </si>
+  <si>
+    <t>NABATI ROLL STRAW 55</t>
+  </si>
+  <si>
+    <t>20142903</t>
+  </si>
+  <si>
+    <t>CHCLTOS RCH DUBAI 54</t>
+  </si>
+  <si>
+    <t>20142904</t>
+  </si>
+  <si>
+    <t>CHCLTOS RCH MTCHA 54</t>
+  </si>
+  <si>
+    <t>10036934</t>
+  </si>
+  <si>
+    <t>ASTOR CHOCOLATE 40G</t>
+  </si>
+  <si>
+    <t>20139060</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE ORI 35G</t>
+  </si>
+  <si>
+    <t>20139061</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE CKLT 35</t>
+  </si>
+  <si>
+    <t>20138261</t>
+  </si>
+  <si>
+    <t>POCKY BLUEBERRY 38G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20141134</t>
+  </si>
+  <si>
+    <t>POCKY STRAW YOGRT 38</t>
+  </si>
+  <si>
+    <t>20065180</t>
+  </si>
+  <si>
+    <t>GLICO PEJOY CHO 30G</t>
+  </si>
+  <si>
+    <t>20039648</t>
+  </si>
+  <si>
+    <t>LOTTE PEPERO ALMND32</t>
+  </si>
+  <si>
+    <t>20060710</t>
+  </si>
+  <si>
+    <t>LOTTE PEPERO WHT.C32</t>
+  </si>
+  <si>
+    <t>10038704</t>
+  </si>
+  <si>
+    <t>MEIJI H/PANDA CHOC42</t>
+  </si>
+  <si>
+    <t>10004490</t>
+  </si>
+  <si>
+    <t>HELLO PANDA STRW 42G</t>
+  </si>
+  <si>
+    <t>20134559</t>
+  </si>
+  <si>
+    <t>HLO PANDA DB.CHO 42G</t>
+  </si>
+  <si>
+    <t>20129863</t>
+  </si>
+  <si>
+    <t>NYAM2 SMILEY CKL 45G</t>
+  </si>
+  <si>
+    <t>20099762</t>
+  </si>
+  <si>
+    <t>NYAM2 POPSTIX CHO 48</t>
+  </si>
+  <si>
+    <t>10000213</t>
+  </si>
+  <si>
+    <t>GLICO POCKY CHO 47GR</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>10036916</t>
+  </si>
+  <si>
+    <t>GLICO POCKY.STRAW 45</t>
+  </si>
+  <si>
+    <t>20086168</t>
+  </si>
+  <si>
+    <t>GLCO POCKY COOK&amp;CR40</t>
+  </si>
+  <si>
+    <t>20138741</t>
+  </si>
+  <si>
+    <t>GLICO POCKY MILK 39G</t>
+  </si>
+  <si>
+    <t>20138740</t>
+  </si>
+  <si>
+    <t>POCKY MILK CHOCO 39G</t>
+  </si>
+  <si>
+    <t>20062839</t>
+  </si>
+  <si>
+    <t>GLCO POCKY MTCHA 33G</t>
+  </si>
+  <si>
+    <t>20057865</t>
+  </si>
+  <si>
+    <t>GLCO POCKY DOU.CHO47</t>
+  </si>
+  <si>
+    <t>20134839</t>
+  </si>
+  <si>
+    <t>POCKY CRSHD DRK.CH25</t>
+  </si>
+  <si>
+    <t>20142268</t>
+  </si>
+  <si>
+    <t>GLICO PJOY TIRAMIS30</t>
+  </si>
+  <si>
+    <t>20142267</t>
+  </si>
+  <si>
+    <t>POCKY PASION FRUIT38</t>
+  </si>
+  <si>
+    <t>10006131</t>
+  </si>
+  <si>
+    <t>AIM ROASTED CORN 180</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10000461</t>
+  </si>
+  <si>
+    <t>MONDE SERENA GOLD 50</t>
+  </si>
+  <si>
+    <t>20099687</t>
+  </si>
+  <si>
+    <t>MONDE SPCY TOMAT 50G</t>
+  </si>
+  <si>
+    <t>10000562</t>
+  </si>
+  <si>
+    <t>MONDE EGG DROPS 110G</t>
+  </si>
+  <si>
+    <t>10002258</t>
+  </si>
+  <si>
+    <t>MONDE BISC PBIS 190G</t>
+  </si>
+  <si>
+    <t>20141391</t>
+  </si>
+  <si>
+    <t>MONDE SNACK CHEESE50</t>
+  </si>
+  <si>
+    <t>20085046</t>
+  </si>
+  <si>
+    <t>JULIES PNUT BTR 82.5</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20057475</t>
+  </si>
+  <si>
+    <t>SERENA TOGO CKLT 128</t>
+  </si>
+  <si>
+    <t>20095021</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CKLT 76G</t>
+  </si>
+  <si>
+    <t>20137569</t>
+  </si>
+  <si>
+    <t>BISKUAT GOLD.STR105G</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20137568</t>
+  </si>
+  <si>
+    <t>BISKUAT GOLD.VNL105G</t>
+  </si>
+  <si>
+    <t>20131802</t>
+  </si>
+  <si>
+    <t>IMPERIAL BLUBERRY108</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20139973</t>
+  </si>
+  <si>
+    <t>IMPERIAL STRW&amp;CH 100</t>
+  </si>
+  <si>
+    <t>20139951</t>
+  </si>
+  <si>
+    <t>KOKOLA BLCK CKLT 110</t>
+  </si>
+  <si>
+    <t>20091225</t>
+  </si>
+  <si>
+    <t>OVLTNE CHO BISC 104G</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20134970</t>
+  </si>
+  <si>
+    <t>MILO SANDW ORIG 96G</t>
+  </si>
+  <si>
+    <t>20134969</t>
+  </si>
+  <si>
+    <t>MILO SANDW MILK 96G</t>
+  </si>
+  <si>
+    <t>20140011</t>
+  </si>
+  <si>
+    <t>MILO BISC. CHOCO 96G</t>
+  </si>
+  <si>
+    <t>20074990</t>
+  </si>
+  <si>
+    <t>OREO DARK&amp;WHT 105G</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20024644</t>
+  </si>
+  <si>
+    <t>OREO STRAW CREM1105G</t>
+  </si>
+  <si>
+    <t>20106305</t>
+  </si>
+  <si>
+    <t>OREO RED VELVET 105G</t>
+  </si>
+  <si>
+    <t>10016170</t>
+  </si>
+  <si>
+    <t>OREO CHOCO CRM 105G</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20030547</t>
+  </si>
+  <si>
+    <t>OREO ICE CRM BL 105G</t>
+  </si>
+  <si>
+    <t>10035165</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 105G</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20138464</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 147.2G</t>
+  </si>
+  <si>
+    <t>20142591</t>
+  </si>
+  <si>
+    <t>OREO SNDW HOTTEOK105</t>
+  </si>
+  <si>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20015338</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CHSE 190</t>
+  </si>
+  <si>
+    <t>10008579</t>
+  </si>
+  <si>
+    <t>DELFI MINIS BLK.VN70</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
     <t>10008580</t>
   </si>
   <si>
     <t>DELFI MINIS CHOCO 70</t>
   </si>
   <si>
-    <t>10008579</t>
-  </si>
-  <si>
-    <t>DELFI MINIS BLK.VN70</t>
-  </si>
-  <si>
-    <t>20132494</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS KJU33</t>
-  </si>
-  <si>
-    <t>20130152</t>
-  </si>
-  <si>
-    <t>LEMONILO BROWNIES 33</t>
-  </si>
-  <si>
-    <t>20142678</t>
-  </si>
-  <si>
-    <t>LMNILO LMN CHESSE 33</t>
-  </si>
-  <si>
-    <t>20137230</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS STR33</t>
-  </si>
-  <si>
-    <t>20137584</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHOCIP35</t>
-  </si>
-  <si>
-    <t>20137583</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHEESE35</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20139819</t>
-  </si>
-  <si>
-    <t>TANGO BROWNIS CR.35G</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20061189</t>
-  </si>
-  <si>
-    <t>NARAYA OAT CHOCO 90</t>
-  </si>
-  <si>
-    <t>20133506</t>
-  </si>
-  <si>
-    <t>DELFI KRICE SWET64.8</t>
-  </si>
-  <si>
-    <t>20133507</t>
-  </si>
-  <si>
-    <t>DELFI KRICE SWD 47.4</t>
-  </si>
-  <si>
-    <t>20102638</t>
-  </si>
-  <si>
-    <t>DEKA WFR BITE CHO 72</t>
-  </si>
-  <si>
-    <t>20083487</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOCO 95G</t>
-  </si>
-  <si>
-    <t>20083488</t>
-  </si>
-  <si>
-    <t>TANGO WFR VANL 95G</t>
-  </si>
-  <si>
-    <t>20138099</t>
-  </si>
-  <si>
-    <t>OVALTINE MB WFR 100G</t>
-  </si>
-  <si>
-    <t>20139081</t>
-  </si>
-  <si>
-    <t>REGAL CHO MARIE 64G</t>
-  </si>
-  <si>
-    <t>20130007</t>
-  </si>
-  <si>
-    <t>BETTER FUN BITES 10S</t>
-  </si>
-  <si>
-    <t>10000132</t>
-  </si>
-  <si>
-    <t>MONDE BT.COOKIES 454</t>
-  </si>
-  <si>
-    <t>10000734</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHOCO 570</t>
-  </si>
-  <si>
-    <t>20010655</t>
-  </si>
-  <si>
-    <t>TANGO WFER CHOCO 240</t>
-  </si>
-  <si>
-    <t>10000133</t>
-  </si>
-  <si>
-    <t>KHONG GUAN MN ASS650</t>
-  </si>
-  <si>
-    <t>10000360</t>
-  </si>
-  <si>
-    <t>KHONG GUAN RED 1600G</t>
-  </si>
-  <si>
-    <t>20129572</t>
-  </si>
-  <si>
-    <t>CHCLATOS WFR VNLA90</t>
-  </si>
-  <si>
-    <t>20127761</t>
-  </si>
-  <si>
-    <t>CHCLATOS WFR CHO 90</t>
-  </si>
-  <si>
-    <t>10000175</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHO 110G</t>
-  </si>
-  <si>
-    <t>20109917</t>
-  </si>
-  <si>
-    <t>ROMA WFR CHO BLS97.6</t>
-  </si>
-  <si>
-    <t>20055311</t>
-  </si>
-  <si>
-    <t>NABATI RCHSE WFR 110</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20055312</t>
-  </si>
-  <si>
-    <t>NBATI RCHCO WFR C110</t>
-  </si>
-  <si>
-    <t>20138462</t>
-  </si>
-  <si>
-    <t>NABATI WFR STRAW 122</t>
-  </si>
-  <si>
-    <t>20069149</t>
-  </si>
-  <si>
-    <t>TANGO WFR LG VAN 100</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20138977</t>
-  </si>
-  <si>
-    <t>TANGO WFR LG CHES100</t>
-  </si>
-  <si>
-    <t>20128683</t>
-  </si>
-  <si>
-    <t>TANGO WFLE CHO HZL63</t>
-  </si>
-  <si>
-    <t>20027448</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOC 100G</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10000726</t>
-  </si>
-  <si>
-    <t>ASTOR CHOCOLATE 150G</t>
-  </si>
-  <si>
-    <t>20139686</t>
-  </si>
-  <si>
-    <t>TANGO WFLE WAHH 67.5</t>
-  </si>
-  <si>
-    <t>20139392</t>
-  </si>
-  <si>
-    <t>BRINGZ LMIER BTR 100</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20137570</t>
-  </si>
-  <si>
-    <t>NABATI BIG RL CHS48G</t>
-  </si>
-  <si>
-    <t>20138461</t>
-  </si>
-  <si>
-    <t>NABATI ROLL STRAW 55</t>
-  </si>
-  <si>
-    <t>20138332</t>
-  </si>
-  <si>
-    <t>CHCLTOS RICH CHOC54G</t>
-  </si>
-  <si>
-    <t>10036934</t>
-  </si>
-  <si>
-    <t>ASTOR CHOCOLATE 40G</t>
-  </si>
-  <si>
-    <t>20129863</t>
-  </si>
-  <si>
-    <t>NYAM2 SMILEY CKL 45G</t>
-  </si>
-  <si>
-    <t>20099762</t>
-  </si>
-  <si>
-    <t>NYAM2 POPSTIX CHO 48</t>
-  </si>
-  <si>
-    <t>20138261</t>
-  </si>
-  <si>
-    <t>POCKY BLUEBERRY 38G</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20141134</t>
-  </si>
-  <si>
-    <t>POCKY STRAW YOGRT 38</t>
-  </si>
-  <si>
-    <t>20065180</t>
-  </si>
-  <si>
-    <t>GLICO PEJOY CHO 30G</t>
-  </si>
-  <si>
-    <t>20039648</t>
-  </si>
-  <si>
-    <t>LOTTE PEPERO ALMND32</t>
-  </si>
-  <si>
-    <t>20060710</t>
-  </si>
-  <si>
-    <t>LOTTE PEPERO WHT.C32</t>
-  </si>
-  <si>
-    <t>10038704</t>
-  </si>
-  <si>
-    <t>MEIJI H/PANDA CHOC42</t>
-  </si>
-  <si>
-    <t>10004490</t>
-  </si>
-  <si>
-    <t>HELLO PANDA STRW 42G</t>
-  </si>
-  <si>
-    <t>20134559</t>
-  </si>
-  <si>
-    <t>HLO PANDA DB.CHO 42G</t>
-  </si>
-  <si>
-    <t>10000213</t>
-  </si>
-  <si>
-    <t>GLICO POCKY CHO 47GR</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>10036916</t>
-  </si>
-  <si>
-    <t>GLICO POCKY.STRAW 45</t>
-  </si>
-  <si>
-    <t>20086168</t>
-  </si>
-  <si>
-    <t>GLCO POCKY COOK&amp;CR40</t>
-  </si>
-  <si>
-    <t>20138741</t>
-  </si>
-  <si>
-    <t>GLICO POCKY MILK 39G</t>
-  </si>
-  <si>
-    <t>20138740</t>
-  </si>
-  <si>
-    <t>POCKY MILK CHOCO 39G</t>
-  </si>
-  <si>
-    <t>20062839</t>
-  </si>
-  <si>
-    <t>GLCO POCKY MTCHA 33G</t>
-  </si>
-  <si>
-    <t>20057865</t>
-  </si>
-  <si>
-    <t>GLCO POCKY DOU.CHO47</t>
-  </si>
-  <si>
-    <t>20134839</t>
-  </si>
-  <si>
-    <t>POCKY CRSHD DRK.CH25</t>
-  </si>
-  <si>
-    <t>20142268</t>
-  </si>
-  <si>
-    <t>GLICO PJOY TIRAMIS30</t>
-  </si>
-  <si>
-    <t>20142267</t>
-  </si>
-  <si>
-    <t>POCKY PASION FRUIT38</t>
-  </si>
-  <si>
-    <t>10006131</t>
-  </si>
-  <si>
-    <t>AIM ROASTED CORN 180</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10000461</t>
-  </si>
-  <si>
-    <t>MONDE SERENA GOLD 50</t>
-  </si>
-  <si>
-    <t>20099687</t>
-  </si>
-  <si>
-    <t>MONDE SPCY TOMAT 50G</t>
-  </si>
-  <si>
-    <t>10000562</t>
-  </si>
-  <si>
-    <t>MONDE EGG DROPS 110G</t>
-  </si>
-  <si>
-    <t>10002258</t>
-  </si>
-  <si>
-    <t>MONDE BISC PBIS 190G</t>
-  </si>
-  <si>
-    <t>20141391</t>
-  </si>
-  <si>
-    <t>MONDE SNACK CHEESE50</t>
-  </si>
-  <si>
-    <t>20085046</t>
-  </si>
-  <si>
-    <t>JULIES PNUT BTR 82.5</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20057475</t>
-  </si>
-  <si>
-    <t>SERENA TOGO CKLT 128</t>
-  </si>
-  <si>
-    <t>20095021</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CKLT 76G</t>
-  </si>
-  <si>
-    <t>20129409</t>
-  </si>
-  <si>
-    <t>NEXTAR NOIR CHO 144</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20122285</t>
-  </si>
-  <si>
-    <t>NEXTAR NOIR C&amp;C 144</t>
-  </si>
-  <si>
-    <t>20137569</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.STR105G</t>
-  </si>
-  <si>
-    <t>20137568</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.VNL105G</t>
-  </si>
-  <si>
-    <t>20131802</t>
-  </si>
-  <si>
-    <t>IMPERIAL BLUBERRY108</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20139973</t>
-  </si>
-  <si>
-    <t>IMPERIAL STRW&amp;CH 100</t>
-  </si>
-  <si>
-    <t>20139951</t>
-  </si>
-  <si>
-    <t>KOKOLA BLCK CKLT 110</t>
-  </si>
-  <si>
-    <t>20091225</t>
-  </si>
-  <si>
-    <t>OVLTNE CHO BISC 104G</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20134970</t>
-  </si>
-  <si>
-    <t>MILO SANDW ORIG 104G</t>
-  </si>
-  <si>
-    <t>20134969</t>
-  </si>
-  <si>
-    <t>MILO SANDW MILK 104G</t>
-  </si>
-  <si>
-    <t>20140011</t>
-  </si>
-  <si>
-    <t>MILO BISC. CHOCO 96G</t>
-  </si>
-  <si>
-    <t>20074990</t>
-  </si>
-  <si>
-    <t>OREO DARK&amp;WHT 105G</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20024644</t>
-  </si>
-  <si>
-    <t>OREO STRAW CREM1105G</t>
-  </si>
-  <si>
-    <t>20106305</t>
-  </si>
-  <si>
-    <t>OREO RED VELVET 105G</t>
-  </si>
-  <si>
-    <t>10016170</t>
-  </si>
-  <si>
-    <t>OREO CHOCO CRM 105G</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20030547</t>
-  </si>
-  <si>
-    <t>OREO ICE CRM BL 105G</t>
-  </si>
-  <si>
-    <t>10035165</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 105G</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20138464</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 147.2G</t>
-  </si>
-  <si>
-    <t>20142591</t>
-  </si>
-  <si>
-    <t>OREO SNDW HOTTEOK105</t>
-  </si>
-  <si>
-    <t>20015337</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW COKL 190</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20015338</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CHSE 190</t>
-  </si>
-  <si>
-    <t>20139060</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE ORI 35G</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20139061</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE CKLT 35</t>
-  </si>
-  <si>
     <t>20048790</t>
   </si>
   <si>
@@ -880,21 +856,15 @@
     <t>RT,(E-14H)</t>
   </si>
   <si>
-    <t>20090169</t>
-  </si>
-  <si>
-    <t>GERY KR.BRS ASN 10'S</t>
+    <t>10000731</t>
+  </si>
+  <si>
+    <t>KHONG GUAN BISC 300G</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>10000731</t>
-  </si>
-  <si>
-    <t>KHONG GUAN BISC 300G</t>
-  </si>
-  <si>
     <t>10036921</t>
   </si>
   <si>
@@ -1021,6 +991,12 @@
     <t>NISSIN CHOCO SOES100</t>
   </si>
   <si>
+    <t>20142902</t>
+  </si>
+  <si>
+    <t>DILAN CKIES CHOCP 69</t>
+  </si>
+  <si>
     <t>20111641</t>
   </si>
   <si>
@@ -1072,7 +1048,7 @@
     <t>20025741</t>
   </si>
   <si>
-    <t>ROMA SARI GANDUM 149</t>
+    <t>ROMA SR GANDUM 149 G</t>
   </si>
   <si>
     <t>34</t>
@@ -1099,7 +1075,7 @@
     <t>20045132</t>
   </si>
   <si>
-    <t>ROMA GNDM SAND. 108G</t>
+    <t>ROMA GNDM SAND 108 G</t>
   </si>
   <si>
     <t>35</t>
@@ -1108,7 +1084,7 @@
     <t>20052934</t>
   </si>
   <si>
-    <t>ROMA GNDM/S PNUT 108</t>
+    <t>ROMA GNDM PNUT 108 G</t>
   </si>
   <si>
     <t>10031595</t>
@@ -1249,21 +1225,15 @@
     <t>REGAL MARIE 120GR</t>
   </si>
   <si>
-    <t>20136761</t>
-  </si>
-  <si>
-    <t>ROMA MARI GOLD 110G</t>
+    <t>20091350</t>
+  </si>
+  <si>
+    <t>ROMA MARIE GOLD 220G</t>
   </si>
   <si>
     <t>39</t>
   </si>
   <si>
-    <t>20091350</t>
-  </si>
-  <si>
-    <t>ROMA MARIE GOLD 220G</t>
-  </si>
-  <si>
     <t>20014537</t>
   </si>
   <si>
@@ -1276,15 +1246,27 @@
     <t>BISKUAT COKLAT121.6G</t>
   </si>
   <si>
+    <t>20053216</t>
+  </si>
+  <si>
+    <t>NSIN BSC KLP IJO 280</t>
+  </si>
+  <si>
+    <t>10000206</t>
+  </si>
+  <si>
+    <t>NISSIN CR.CRISPY 250</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>20133020</t>
   </si>
   <si>
     <t>NISSIN CRACK.LMON200</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>20118424</t>
   </si>
   <si>
@@ -1303,16 +1285,10 @@
     <t>AIM CRACK CRISPY 150</t>
   </si>
   <si>
-    <t>20053216</t>
-  </si>
-  <si>
-    <t>NSIN BSC KLP IJO 280</t>
-  </si>
-  <si>
-    <t>10000206</t>
-  </si>
-  <si>
-    <t>NISSIN CR.CRISPY 250</t>
+    <t>20142807</t>
+  </si>
+  <si>
+    <t>GERY BISC.KNTG BBQ55</t>
   </si>
   <si>
     <t>41</t>
@@ -1355,12 +1331,6 @@
   </si>
   <si>
     <t>GERY MLKS SLT COK100</t>
-  </si>
-  <si>
-    <t>20130454</t>
-  </si>
-  <si>
-    <t>DILAN SANDW COK.VN80</t>
   </si>
   <si>
     <t>20134984</t>
@@ -1849,7 +1819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F216"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1990,13 +1960,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2010,10 +1980,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -2021,19 +1991,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -2041,36 +2011,36 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>8</v>
@@ -2081,19 +2051,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -2101,19 +2071,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -2121,19 +2091,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -2141,19 +2111,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -2161,19 +2131,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -2181,19 +2151,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -2201,19 +2171,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -2221,19 +2191,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -2241,19 +2211,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -2261,16 +2231,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>4</v>
@@ -2290,7 +2260,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>8</v>
@@ -2310,10 +2280,10 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2330,10 +2300,10 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2350,13 +2320,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2370,10 +2340,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2390,10 +2360,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2410,13 +2380,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2430,10 +2400,10 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2450,10 +2420,10 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2470,7 +2440,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>14</v>
@@ -2490,7 +2460,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>17</v>
@@ -2510,13 +2480,13 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2530,10 +2500,10 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2550,10 +2520,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2570,10 +2540,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2581,19 +2551,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2601,39 +2571,39 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2641,19 +2611,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2661,19 +2631,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2681,19 +2651,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2701,19 +2671,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2721,19 +2691,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2741,19 +2711,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2761,19 +2731,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2781,16 +2751,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>4</v>
@@ -2810,7 +2780,7 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>8</v>
@@ -2830,10 +2800,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2850,10 +2820,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2870,50 +2840,50 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2921,19 +2891,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2941,19 +2911,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2961,59 +2931,59 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3021,19 +2991,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3041,19 +3011,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3061,19 +3031,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3081,19 +3051,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3101,19 +3071,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3121,19 +3091,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3141,19 +3111,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3170,10 +3140,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3190,10 +3160,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3210,10 +3180,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3221,19 +3191,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3241,19 +3211,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3261,42 +3231,42 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3310,10 +3280,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3330,10 +3300,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3350,13 +3320,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3370,13 +3340,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3390,13 +3360,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3410,10 +3380,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3421,19 +3391,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3441,19 +3411,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3470,10 +3440,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3490,7 +3460,7 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>11</v>
@@ -3510,10 +3480,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3530,10 +3500,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3550,10 +3520,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3570,10 +3540,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3590,10 +3560,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3610,30 +3580,30 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>195</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3641,22 +3611,22 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>199</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3670,10 +3640,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3690,7 +3660,7 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>11</v>
@@ -3710,10 +3680,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3730,30 +3700,30 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3761,22 +3731,22 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3790,10 +3760,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3801,36 +3771,36 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>199</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>4</v>
@@ -3841,16 +3811,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>8</v>
@@ -3861,19 +3831,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3881,19 +3851,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3901,19 +3871,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3921,19 +3891,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3941,19 +3911,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3961,16 +3931,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>4</v>
@@ -3981,16 +3951,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>8</v>
@@ -4001,19 +3971,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -4021,19 +3991,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -4041,19 +4011,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4061,19 +4031,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4081,19 +4051,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4101,19 +4071,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4121,59 +4091,59 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4181,19 +4151,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4201,62 +4171,62 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4270,13 +4240,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4290,13 +4260,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4310,10 +4280,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4330,13 +4300,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4350,50 +4320,50 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>29</v>
+        <v>280</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B127" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4401,56 +4371,56 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>288</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>4</v>
@@ -4461,16 +4431,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>8</v>
@@ -4481,19 +4451,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4501,39 +4471,39 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4541,19 +4511,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4561,19 +4531,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4581,19 +4551,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4601,39 +4571,39 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>199</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4641,19 +4611,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4661,39 +4631,39 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4701,19 +4671,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B143" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4721,19 +4691,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4741,19 +4711,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4761,36 +4731,36 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>4</v>
@@ -4801,16 +4771,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>8</v>
@@ -4821,19 +4791,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4841,19 +4811,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4861,19 +4831,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4881,19 +4851,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4901,19 +4871,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4921,16 +4891,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>4</v>
@@ -4941,16 +4911,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>8</v>
@@ -4961,19 +4931,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4981,19 +4951,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -5001,16 +4971,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>4</v>
@@ -5021,16 +4991,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>8</v>
@@ -5041,19 +5011,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5061,19 +5031,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5081,16 +5051,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>4</v>
@@ -5101,16 +5071,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>8</v>
@@ -5121,59 +5091,59 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5190,10 +5160,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5210,13 +5180,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5230,13 +5200,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5250,10 +5220,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5270,50 +5240,50 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>383</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>195</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B173" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5321,62 +5291,62 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>195</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>199</v>
+        <v>383</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5390,167 +5360,167 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>195</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>391</v>
+        <v>195</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>391</v>
+        <v>195</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>199</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>199</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>199</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>199</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>4</v>
@@ -5561,16 +5531,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>8</v>
@@ -5581,19 +5551,19 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5601,19 +5571,19 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5621,22 +5591,22 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>195</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5650,10 +5620,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5661,19 +5631,19 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="E191" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5681,39 +5651,39 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>199</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5721,19 +5691,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5750,10 +5720,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5761,19 +5731,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="E196" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5781,19 +5751,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5801,19 +5771,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5821,19 +5791,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5850,10 +5820,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5861,19 +5831,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="E201" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5881,19 +5851,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5901,19 +5871,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5921,19 +5891,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5941,19 +5911,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5970,10 +5940,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5981,19 +5951,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -6001,19 +5971,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6021,19 +5991,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6041,19 +6011,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6061,121 +6031,21 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F212" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F213" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F214" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F215" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="E216" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F216" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -1048,7 +1048,7 @@
     <t>20025741</t>
   </si>
   <si>
-    <t>ROMA SR GANDUM 149 G</t>
+    <t>ROMA SARI GANDUM 149</t>
   </si>
   <si>
     <t>34</t>
@@ -1075,7 +1075,7 @@
     <t>20045132</t>
   </si>
   <si>
-    <t>ROMA GNDM SAND 108 G</t>
+    <t>ROMA GNDM SAND. 108G</t>
   </si>
   <si>
     <t>35</t>
@@ -1084,7 +1084,7 @@
     <t>20052934</t>
   </si>
   <si>
-    <t>ROMA GNDM PNUT 108 G</t>
+    <t>ROMA GNDM/S PNUT 108</t>
   </si>
   <si>
     <t>10031595</t>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,234 +11,831 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="476">
   <si>
     <t/>
   </si>
   <si>
+    <t>20130350</t>
+  </si>
+  <si>
+    <t>POCKY CHOCOLATE 154</t>
+  </si>
+  <si>
+    <t>BIS05D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20025592</t>
+  </si>
+  <si>
+    <t>K/G WAFER CLASSIC350</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10036899</t>
+  </si>
+  <si>
+    <t>REGAL MARIE BARU 550</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20125628</t>
+  </si>
+  <si>
+    <t>NSSIN WFR CHO/LVA137</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20108817</t>
+  </si>
+  <si>
+    <t>K/G SLTCHS COMBO 175</t>
+  </si>
+  <si>
+    <t>20142944</t>
+  </si>
+  <si>
+    <t>IDM CHOCO WAFER 120</t>
+  </si>
+  <si>
+    <t>20128683</t>
+  </si>
+  <si>
+    <t>TANGO WFLE CHO HZL63</t>
+  </si>
+  <si>
+    <t>20063092</t>
+  </si>
+  <si>
+    <t>SELAMAT DBL CHOCO128</t>
+  </si>
+  <si>
+    <t>10016650</t>
+  </si>
+  <si>
+    <t>SELAMAT WF.CHOCO 128</t>
+  </si>
+  <si>
+    <t>10004541</t>
+  </si>
+  <si>
+    <t>TANGO WFR VNLA 124G</t>
+  </si>
+  <si>
+    <t>10004540</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOCO 124G</t>
+  </si>
+  <si>
+    <t>20133247</t>
+  </si>
+  <si>
+    <t>OREO SOFT CAKE 96G</t>
+  </si>
+  <si>
+    <t>20030358</t>
+  </si>
+  <si>
+    <t>MONDE GNJI MN PIE 50</t>
+  </si>
+  <si>
+    <t>10036942</t>
+  </si>
+  <si>
+    <t>MONDE S.PIE STRW 85G</t>
+  </si>
+  <si>
+    <t>10003324</t>
+  </si>
+  <si>
+    <t>MONDE GENJIE PIE 70G</t>
+  </si>
+  <si>
+    <t>20139391</t>
+  </si>
+  <si>
+    <t>NEXTAR CHOC PIE 6S</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20140126</t>
+  </si>
+  <si>
+    <t>NEXTAR STRAWB CHS144</t>
+  </si>
+  <si>
+    <t>20083539</t>
+  </si>
+  <si>
+    <t>DELFI CUSTAS SC 6'S</t>
+  </si>
+  <si>
+    <t>20052630</t>
+  </si>
+  <si>
+    <t>LOTTE CHOCO PIE 156G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20096783</t>
+  </si>
+  <si>
+    <t>DELFI CHO.PIE DRK180</t>
+  </si>
+  <si>
+    <t>20136934</t>
+  </si>
+  <si>
+    <t>LOTTE C/PIE STRWB156</t>
+  </si>
+  <si>
+    <t>20052628</t>
+  </si>
+  <si>
+    <t>LOTTE CHOCO PIE 52G</t>
+  </si>
+  <si>
+    <t>20132494</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS KJU33</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20130152</t>
+  </si>
+  <si>
+    <t>LEMONILO BROWNIES 33</t>
+  </si>
+  <si>
+    <t>20142678</t>
+  </si>
+  <si>
+    <t>LMNILO LMN CHESSE 33</t>
+  </si>
+  <si>
+    <t>20137230</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS STR33</t>
+  </si>
+  <si>
+    <t>20137584</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHOCIP35</t>
+  </si>
+  <si>
+    <t>20137583</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHEESE35</t>
+  </si>
+  <si>
+    <t>20139819</t>
+  </si>
+  <si>
+    <t>TANGO BROWNIS CR.35G</t>
+  </si>
+  <si>
+    <t>20061189</t>
+  </si>
+  <si>
+    <t>NARAYA OAT CHOCO 90</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20056645</t>
+  </si>
+  <si>
+    <t>NARAYA OAT CHOCO 90G</t>
+  </si>
+  <si>
+    <t>20102638</t>
+  </si>
+  <si>
+    <t>DEKA WFR BITE CHO 72</t>
+  </si>
+  <si>
+    <t>20083487</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOCO 95G</t>
+  </si>
+  <si>
+    <t>20083488</t>
+  </si>
+  <si>
+    <t>TANGO WFR VANL 95G</t>
+  </si>
+  <si>
+    <t>20138099</t>
+  </si>
+  <si>
+    <t>OVALTINE MB WFR 100G</t>
+  </si>
+  <si>
+    <t>20139081</t>
+  </si>
+  <si>
+    <t>REGAL CHO MARIE 64G</t>
+  </si>
+  <si>
+    <t>20130007</t>
+  </si>
+  <si>
+    <t>BETTER FUN BITES 10S</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10000132</t>
+  </si>
+  <si>
+    <t>MONDE BT.COOKIES 454</t>
+  </si>
+  <si>
+    <t>10000734</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHOCO 570</t>
+  </si>
+  <si>
+    <t>20010655</t>
+  </si>
+  <si>
+    <t>TANGO WFER CHOCO 240</t>
+  </si>
+  <si>
+    <t>10000133</t>
+  </si>
+  <si>
+    <t>KHONG GUAN MN ASS650</t>
+  </si>
+  <si>
+    <t>10000360</t>
+  </si>
+  <si>
+    <t>KHONG GUAN RED 1600G</t>
+  </si>
+  <si>
+    <t>20129572</t>
+  </si>
+  <si>
+    <t>CHCLATOS WFR VNLA90</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20127761</t>
+  </si>
+  <si>
+    <t>CHCLATOS WFR CHO 90</t>
+  </si>
+  <si>
+    <t>10000175</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHO 110G</t>
+  </si>
+  <si>
+    <t>20109917</t>
+  </si>
+  <si>
+    <t>ROMA WFR CHO BLS97.6</t>
+  </si>
+  <si>
+    <t>20069149</t>
+  </si>
+  <si>
+    <t>TANGO WFR LG VAN 100</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>10007336</t>
+  </si>
+  <si>
+    <t>TANGO WFR STRAW 124G</t>
+  </si>
+  <si>
+    <t>20138977</t>
+  </si>
+  <si>
+    <t>TANGO WFR LG CHES100</t>
+  </si>
+  <si>
+    <t>20071746</t>
+  </si>
+  <si>
+    <t>SPRSTAR TRPL.CHO 6'S</t>
+  </si>
+  <si>
+    <t>20027448</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOC 100G</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20055311</t>
+  </si>
+  <si>
+    <t>NABATI RCHSE WFR 110</t>
+  </si>
+  <si>
+    <t>20055312</t>
+  </si>
+  <si>
+    <t>NBATI RCHCO WFR C110</t>
+  </si>
+  <si>
+    <t>20138462</t>
+  </si>
+  <si>
+    <t>NABATI WFR STRAW 122</t>
+  </si>
+  <si>
+    <t>10000726</t>
+  </si>
+  <si>
+    <t>ASTOR CHOCOLATE 150G</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20139061</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE CKLT 35</t>
+  </si>
+  <si>
+    <t>20139060</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE ORI 35G</t>
+  </si>
+  <si>
+    <t>20139686</t>
+  </si>
+  <si>
+    <t>TANGO WFLE WAHH 67.5</t>
+  </si>
+  <si>
+    <t>20139392</t>
+  </si>
+  <si>
+    <t>BRINGZ LMIER BTR 100</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20137570</t>
+  </si>
+  <si>
+    <t>NABATI BIG RL CHS48G</t>
+  </si>
+  <si>
+    <t>20138461</t>
+  </si>
+  <si>
+    <t>NABATI ROLL STRAW 55</t>
+  </si>
+  <si>
+    <t>20142903</t>
+  </si>
+  <si>
+    <t>CHCLTOS RCH DUBAI 54</t>
+  </si>
+  <si>
+    <t>20142904</t>
+  </si>
+  <si>
+    <t>CHCLTOS RCH MTCHA 54</t>
+  </si>
+  <si>
+    <t>10036934</t>
+  </si>
+  <si>
+    <t>ASTOR CHOCOLATE 40G</t>
+  </si>
+  <si>
+    <t>20138261</t>
+  </si>
+  <si>
+    <t>POCKY BLUEBERRY 38G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20141134</t>
+  </si>
+  <si>
+    <t>POCKY STRAW YOGRT 38</t>
+  </si>
+  <si>
+    <t>20065180</t>
+  </si>
+  <si>
+    <t>GLICO PEJOY CHO 30G</t>
+  </si>
+  <si>
+    <t>20039648</t>
+  </si>
+  <si>
+    <t>LOTTE PEPERO ALMND32</t>
+  </si>
+  <si>
+    <t>20060710</t>
+  </si>
+  <si>
+    <t>LOTTE PEPERO WHT.C32</t>
+  </si>
+  <si>
+    <t>10038704</t>
+  </si>
+  <si>
+    <t>MEIJI H/PANDA CHOC42</t>
+  </si>
+  <si>
+    <t>10004490</t>
+  </si>
+  <si>
+    <t>HELLO PANDA STRW 42G</t>
+  </si>
+  <si>
+    <t>20134559</t>
+  </si>
+  <si>
+    <t>HLO PANDA DB.CHO 42G</t>
+  </si>
+  <si>
+    <t>20129863</t>
+  </si>
+  <si>
+    <t>NYAM2 SMILEY CKL 45G</t>
+  </si>
+  <si>
+    <t>20099762</t>
+  </si>
+  <si>
+    <t>NYAM2 POPSTIX CHO 48</t>
+  </si>
+  <si>
+    <t>10000213</t>
+  </si>
+  <si>
+    <t>GLICO POCKY CHO 47GR</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>10036916</t>
+  </si>
+  <si>
+    <t>GLICO POCKY.STRAW 45</t>
+  </si>
+  <si>
+    <t>20086168</t>
+  </si>
+  <si>
+    <t>GLCO POCKY COOK&amp;CR40</t>
+  </si>
+  <si>
+    <t>20138741</t>
+  </si>
+  <si>
+    <t>GLICO POCKY MILK 39G</t>
+  </si>
+  <si>
+    <t>20138740</t>
+  </si>
+  <si>
+    <t>POCKY MILK CHOCO 39G</t>
+  </si>
+  <si>
+    <t>20062839</t>
+  </si>
+  <si>
+    <t>GLCO POCKY MTCHA 33G</t>
+  </si>
+  <si>
+    <t>20057865</t>
+  </si>
+  <si>
+    <t>GLCO POCKY DOU.CHO47</t>
+  </si>
+  <si>
+    <t>20134839</t>
+  </si>
+  <si>
+    <t>POCKY CRSHD DRK.CH25</t>
+  </si>
+  <si>
+    <t>20142268</t>
+  </si>
+  <si>
+    <t>GLICO PJOY TIRAMIS30</t>
+  </si>
+  <si>
+    <t>20142267</t>
+  </si>
+  <si>
+    <t>POCKY PASION FRUIT38</t>
+  </si>
+  <si>
+    <t>10006131</t>
+  </si>
+  <si>
+    <t>AIM ROASTED CORN 180</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10000461</t>
+  </si>
+  <si>
+    <t>MONDE SERENA GOLD 50</t>
+  </si>
+  <si>
+    <t>20099687</t>
+  </si>
+  <si>
+    <t>MONDE SPCY TOMAT 50G</t>
+  </si>
+  <si>
+    <t>10000562</t>
+  </si>
+  <si>
+    <t>MONDE EGG DROPS 110G</t>
+  </si>
+  <si>
+    <t>10002258</t>
+  </si>
+  <si>
+    <t>MONDE BISC PBIS 190G</t>
+  </si>
+  <si>
+    <t>20141391</t>
+  </si>
+  <si>
+    <t>MONDE SNACK CHEESE50</t>
+  </si>
+  <si>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20015338</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CHSE 190</t>
+  </si>
+  <si>
+    <t>20095021</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CKLT 76G</t>
+  </si>
+  <si>
+    <t>20142943</t>
+  </si>
+  <si>
+    <t>IDM CHOCO CRACKR 100</t>
+  </si>
+  <si>
+    <t>20137569</t>
+  </si>
+  <si>
+    <t>BISKUAT GOLD.STR105G</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20137568</t>
+  </si>
+  <si>
+    <t>BISKUAT GOLD.VNL105G</t>
+  </si>
+  <si>
+    <t>20085046</t>
+  </si>
+  <si>
+    <t>JULIES PNUT BTR 82.5</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20057475</t>
+  </si>
+  <si>
+    <t>SERENA TOGO CKLT 128</t>
+  </si>
+  <si>
+    <t>20131802</t>
+  </si>
+  <si>
+    <t>IMPERIAL BLUBERRY108</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20139973</t>
+  </si>
+  <si>
+    <t>IMPERIAL STRW&amp;CH 100</t>
+  </si>
+  <si>
+    <t>20021257</t>
+  </si>
+  <si>
+    <t>U/BISC BONBON CHO200</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20008947</t>
+  </si>
+  <si>
+    <t>K/G MALKIS SPRCO 138</t>
+  </si>
+  <si>
+    <t>20091225</t>
+  </si>
+  <si>
+    <t>OVLTNE CHO BISC 104G</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20134970</t>
+  </si>
+  <si>
+    <t>MILO SANDW ORIG 96G</t>
+  </si>
+  <si>
+    <t>20134969</t>
+  </si>
+  <si>
+    <t>MILO SANDW MILK 96G</t>
+  </si>
+  <si>
+    <t>20140011</t>
+  </si>
+  <si>
+    <t>MILO BISC. CHOCO 96G</t>
+  </si>
+  <si>
+    <t>20030547</t>
+  </si>
+  <si>
+    <t>OREO ICE CRM BL 105G</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20074990</t>
+  </si>
+  <si>
+    <t>OREO DARK&amp;WHT 105G</t>
+  </si>
+  <si>
+    <t>20024644</t>
+  </si>
+  <si>
+    <t>OREO STRAW CREM1105G</t>
+  </si>
+  <si>
+    <t>20106305</t>
+  </si>
+  <si>
+    <t>OREO RED VELVET 105G</t>
+  </si>
+  <si>
+    <t>20139951</t>
+  </si>
+  <si>
+    <t>KOKOLA BLCK CKLT 110</t>
+  </si>
+  <si>
+    <t>10035165</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 105G</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20138464</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 147.2G</t>
+  </si>
+  <si>
+    <t>20142591</t>
+  </si>
+  <si>
+    <t>OREO SNDW HOTTEOK105</t>
+  </si>
+  <si>
+    <t>10016170</t>
+  </si>
+  <si>
+    <t>OREO CHOCO CRM 105G</t>
+  </si>
+  <si>
+    <t>20142670</t>
+  </si>
+  <si>
+    <t>KTST BGLN GT CHESE45</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>20142669</t>
   </si>
   <si>
     <t>KTST BGLN GT BUTER45</t>
   </si>
   <si>
-    <t>BIS05D</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20142670</t>
-  </si>
-  <si>
-    <t>KTST BGLN GT CHESE45</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20130350</t>
-  </si>
-  <si>
-    <t>POCKY CHOCOLATE 154</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20025592</t>
-  </si>
-  <si>
-    <t>K/G WAFER CLASSIC350</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10036899</t>
-  </si>
-  <si>
-    <t>REGAL MARIE BARU 550</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20125628</t>
-  </si>
-  <si>
-    <t>NSSIN WFR CHO/LVA137</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20108817</t>
-  </si>
-  <si>
-    <t>K/G SLTCHS COMBO 175</t>
-  </si>
-  <si>
-    <t>10007336</t>
-  </si>
-  <si>
-    <t>TANGO WFR STRAW 124G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20063092</t>
-  </si>
-  <si>
-    <t>SELAMAT DBL CHOCO128</t>
-  </si>
-  <si>
-    <t>10016650</t>
-  </si>
-  <si>
-    <t>SELAMAT WF.CHOCO 128</t>
-  </si>
-  <si>
-    <t>10004541</t>
-  </si>
-  <si>
-    <t>TANGO WFR VNLA 124G</t>
-  </si>
-  <si>
-    <t>10004540</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOCO 124G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20133247</t>
-  </si>
-  <si>
-    <t>OREO SOFT CAKE 96G</t>
-  </si>
-  <si>
-    <t>20030358</t>
-  </si>
-  <si>
-    <t>MONDE GNJI MN PIE 50</t>
-  </si>
-  <si>
-    <t>10036942</t>
-  </si>
-  <si>
-    <t>MONDE S.PIE STRW 85G</t>
-  </si>
-  <si>
-    <t>10003324</t>
-  </si>
-  <si>
-    <t>MONDE GENJIE PIE 70G</t>
-  </si>
-  <si>
-    <t>20139391</t>
-  </si>
-  <si>
-    <t>NEXTAR CHOC PIE 6S</t>
-  </si>
-  <si>
-    <t>20140126</t>
-  </si>
-  <si>
-    <t>NEXTAR STRAWB CHS144</t>
-  </si>
-  <si>
-    <t>20083539</t>
-  </si>
-  <si>
-    <t>DELFI CUSTAS SC 6'S</t>
-  </si>
-  <si>
-    <t>20052630</t>
-  </si>
-  <si>
-    <t>LOTTE CHOCO PIE 156G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20096783</t>
-  </si>
-  <si>
-    <t>DELFI CHO.PIE DRK180</t>
-  </si>
-  <si>
-    <t>20136934</t>
-  </si>
-  <si>
-    <t>LOTTE C/PIE STRWB156</t>
-  </si>
-  <si>
-    <t>20052628</t>
-  </si>
-  <si>
-    <t>LOTTE CHOCO PIE 52G</t>
-  </si>
-  <si>
-    <t>20056645</t>
-  </si>
-  <si>
-    <t>NARAYA OAT CHOCO 90G</t>
-  </si>
-  <si>
-    <t>20132494</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS KJU33</t>
-  </si>
-  <si>
-    <t>20130152</t>
-  </si>
-  <si>
-    <t>LEMONILO BROWNIES 33</t>
-  </si>
-  <si>
-    <t>20142678</t>
-  </si>
-  <si>
-    <t>LMNILO LMN CHESSE 33</t>
-  </si>
-  <si>
-    <t>20137230</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS STR33</t>
-  </si>
-  <si>
-    <t>20137584</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHOCIP35</t>
-  </si>
-  <si>
-    <t>20137583</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHEESE35</t>
-  </si>
-  <si>
-    <t>20139819</t>
-  </si>
-  <si>
-    <t>TANGO BROWNIS CR.35G</t>
-  </si>
-  <si>
-    <t>20061189</t>
-  </si>
-  <si>
-    <t>NARAYA OAT CHOCO 90</t>
+    <t>20048790</t>
+  </si>
+  <si>
+    <t>OREO MINI CHOCO 58.4</t>
+  </si>
+  <si>
+    <t>20048791</t>
+  </si>
+  <si>
+    <t>OREO MINI VANLA 58.4</t>
+  </si>
+  <si>
+    <t>20134691</t>
+  </si>
+  <si>
+    <t>TWB CRACKR RAINBOW57</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20133507</t>
+  </si>
+  <si>
+    <t>DELFI KRICE SWD 47.4</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
   <si>
     <t>20133506</t>
@@ -247,576 +844,18 @@
     <t>DELFI KRICE SWET64.8</t>
   </si>
   <si>
-    <t>20133507</t>
-  </si>
-  <si>
-    <t>DELFI KRICE SWD 47.4</t>
-  </si>
-  <si>
-    <t>20102638</t>
-  </si>
-  <si>
-    <t>DEKA WFR BITE CHO 72</t>
-  </si>
-  <si>
-    <t>20083487</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOCO 95G</t>
-  </si>
-  <si>
-    <t>20083488</t>
-  </si>
-  <si>
-    <t>TANGO WFR VANL 95G</t>
-  </si>
-  <si>
-    <t>20138099</t>
-  </si>
-  <si>
-    <t>OVALTINE MB WFR 100G</t>
-  </si>
-  <si>
-    <t>20139081</t>
-  </si>
-  <si>
-    <t>REGAL CHO MARIE 64G</t>
-  </si>
-  <si>
-    <t>20130007</t>
-  </si>
-  <si>
-    <t>BETTER FUN BITES 10S</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10000132</t>
-  </si>
-  <si>
-    <t>MONDE BT.COOKIES 454</t>
-  </si>
-  <si>
-    <t>10000734</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHOCO 570</t>
-  </si>
-  <si>
-    <t>20010655</t>
-  </si>
-  <si>
-    <t>TANGO WFER CHOCO 240</t>
-  </si>
-  <si>
-    <t>10000133</t>
-  </si>
-  <si>
-    <t>KHONG GUAN MN ASS650</t>
-  </si>
-  <si>
-    <t>10000360</t>
-  </si>
-  <si>
-    <t>KHONG GUAN RED 1600G</t>
-  </si>
-  <si>
-    <t>20129572</t>
-  </si>
-  <si>
-    <t>CHCLATOS WFR VNLA90</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20127761</t>
-  </si>
-  <si>
-    <t>CHCLATOS WFR CHO 90</t>
-  </si>
-  <si>
-    <t>10000175</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHO 110G</t>
-  </si>
-  <si>
-    <t>20109917</t>
-  </si>
-  <si>
-    <t>ROMA WFR CHO BLS97.6</t>
-  </si>
-  <si>
-    <t>20055311</t>
-  </si>
-  <si>
-    <t>NABATI RCHSE WFR 110</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20055312</t>
-  </si>
-  <si>
-    <t>NBATI RCHCO WFR C110</t>
-  </si>
-  <si>
-    <t>20138462</t>
-  </si>
-  <si>
-    <t>NABATI WFR STRAW 122</t>
-  </si>
-  <si>
-    <t>20069149</t>
-  </si>
-  <si>
-    <t>TANGO WFR LG VAN 100</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20138977</t>
-  </si>
-  <si>
-    <t>TANGO WFR LG CHES100</t>
-  </si>
-  <si>
-    <t>20128683</t>
-  </si>
-  <si>
-    <t>TANGO WFLE CHO HZL63</t>
-  </si>
-  <si>
-    <t>20027448</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOC 100G</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10000726</t>
-  </si>
-  <si>
-    <t>ASTOR CHOCOLATE 150G</t>
-  </si>
-  <si>
-    <t>20139686</t>
-  </si>
-  <si>
-    <t>TANGO WFLE WAHH 67.5</t>
-  </si>
-  <si>
-    <t>20139392</t>
-  </si>
-  <si>
-    <t>BRINGZ LMIER BTR 100</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20137570</t>
-  </si>
-  <si>
-    <t>NABATI BIG RL CHS48G</t>
-  </si>
-  <si>
-    <t>20138461</t>
-  </si>
-  <si>
-    <t>NABATI ROLL STRAW 55</t>
-  </si>
-  <si>
-    <t>20142903</t>
-  </si>
-  <si>
-    <t>CHCLTOS RCH DUBAI 54</t>
-  </si>
-  <si>
-    <t>20142904</t>
-  </si>
-  <si>
-    <t>CHCLTOS RCH MTCHA 54</t>
-  </si>
-  <si>
-    <t>10036934</t>
-  </si>
-  <si>
-    <t>ASTOR CHOCOLATE 40G</t>
-  </si>
-  <si>
-    <t>20139060</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE ORI 35G</t>
-  </si>
-  <si>
-    <t>20139061</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE CKLT 35</t>
-  </si>
-  <si>
-    <t>20138261</t>
-  </si>
-  <si>
-    <t>POCKY BLUEBERRY 38G</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20141134</t>
-  </si>
-  <si>
-    <t>POCKY STRAW YOGRT 38</t>
-  </si>
-  <si>
-    <t>20065180</t>
-  </si>
-  <si>
-    <t>GLICO PEJOY CHO 30G</t>
-  </si>
-  <si>
-    <t>20039648</t>
-  </si>
-  <si>
-    <t>LOTTE PEPERO ALMND32</t>
-  </si>
-  <si>
-    <t>20060710</t>
-  </si>
-  <si>
-    <t>LOTTE PEPERO WHT.C32</t>
-  </si>
-  <si>
-    <t>10038704</t>
-  </si>
-  <si>
-    <t>MEIJI H/PANDA CHOC42</t>
-  </si>
-  <si>
-    <t>10004490</t>
-  </si>
-  <si>
-    <t>HELLO PANDA STRW 42G</t>
-  </si>
-  <si>
-    <t>20134559</t>
-  </si>
-  <si>
-    <t>HLO PANDA DB.CHO 42G</t>
-  </si>
-  <si>
-    <t>20129863</t>
-  </si>
-  <si>
-    <t>NYAM2 SMILEY CKL 45G</t>
-  </si>
-  <si>
-    <t>20099762</t>
-  </si>
-  <si>
-    <t>NYAM2 POPSTIX CHO 48</t>
-  </si>
-  <si>
-    <t>10000213</t>
-  </si>
-  <si>
-    <t>GLICO POCKY CHO 47GR</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>10036916</t>
-  </si>
-  <si>
-    <t>GLICO POCKY.STRAW 45</t>
-  </si>
-  <si>
-    <t>20086168</t>
-  </si>
-  <si>
-    <t>GLCO POCKY COOK&amp;CR40</t>
-  </si>
-  <si>
-    <t>20138741</t>
-  </si>
-  <si>
-    <t>GLICO POCKY MILK 39G</t>
-  </si>
-  <si>
-    <t>20138740</t>
-  </si>
-  <si>
-    <t>POCKY MILK CHOCO 39G</t>
-  </si>
-  <si>
-    <t>20062839</t>
-  </si>
-  <si>
-    <t>GLCO POCKY MTCHA 33G</t>
-  </si>
-  <si>
-    <t>20057865</t>
-  </si>
-  <si>
-    <t>GLCO POCKY DOU.CHO47</t>
-  </si>
-  <si>
-    <t>20134839</t>
-  </si>
-  <si>
-    <t>POCKY CRSHD DRK.CH25</t>
-  </si>
-  <si>
-    <t>20142268</t>
-  </si>
-  <si>
-    <t>GLICO PJOY TIRAMIS30</t>
-  </si>
-  <si>
-    <t>20142267</t>
-  </si>
-  <si>
-    <t>POCKY PASION FRUIT38</t>
-  </si>
-  <si>
-    <t>10006131</t>
-  </si>
-  <si>
-    <t>AIM ROASTED CORN 180</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10000461</t>
-  </si>
-  <si>
-    <t>MONDE SERENA GOLD 50</t>
-  </si>
-  <si>
-    <t>20099687</t>
-  </si>
-  <si>
-    <t>MONDE SPCY TOMAT 50G</t>
-  </si>
-  <si>
-    <t>10000562</t>
-  </si>
-  <si>
-    <t>MONDE EGG DROPS 110G</t>
-  </si>
-  <si>
-    <t>10002258</t>
-  </si>
-  <si>
-    <t>MONDE BISC PBIS 190G</t>
-  </si>
-  <si>
-    <t>20141391</t>
-  </si>
-  <si>
-    <t>MONDE SNACK CHEESE50</t>
-  </si>
-  <si>
-    <t>20085046</t>
-  </si>
-  <si>
-    <t>JULIES PNUT BTR 82.5</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20057475</t>
-  </si>
-  <si>
-    <t>SERENA TOGO CKLT 128</t>
-  </si>
-  <si>
-    <t>20095021</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CKLT 76G</t>
-  </si>
-  <si>
-    <t>20137569</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.STR105G</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20137568</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.VNL105G</t>
-  </si>
-  <si>
-    <t>20131802</t>
-  </si>
-  <si>
-    <t>IMPERIAL BLUBERRY108</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20139973</t>
-  </si>
-  <si>
-    <t>IMPERIAL STRW&amp;CH 100</t>
-  </si>
-  <si>
-    <t>20139951</t>
-  </si>
-  <si>
-    <t>KOKOLA BLCK CKLT 110</t>
-  </si>
-  <si>
-    <t>20091225</t>
-  </si>
-  <si>
-    <t>OVLTNE CHO BISC 104G</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20134970</t>
-  </si>
-  <si>
-    <t>MILO SANDW ORIG 96G</t>
-  </si>
-  <si>
-    <t>20134969</t>
-  </si>
-  <si>
-    <t>MILO SANDW MILK 96G</t>
-  </si>
-  <si>
-    <t>20140011</t>
-  </si>
-  <si>
-    <t>MILO BISC. CHOCO 96G</t>
-  </si>
-  <si>
-    <t>20074990</t>
-  </si>
-  <si>
-    <t>OREO DARK&amp;WHT 105G</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20024644</t>
-  </si>
-  <si>
-    <t>OREO STRAW CREM1105G</t>
-  </si>
-  <si>
-    <t>20106305</t>
-  </si>
-  <si>
-    <t>OREO RED VELVET 105G</t>
-  </si>
-  <si>
-    <t>10016170</t>
-  </si>
-  <si>
-    <t>OREO CHOCO CRM 105G</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20030547</t>
-  </si>
-  <si>
-    <t>OREO ICE CRM BL 105G</t>
-  </si>
-  <si>
-    <t>10035165</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 105G</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20138464</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 147.2G</t>
-  </si>
-  <si>
-    <t>20142591</t>
-  </si>
-  <si>
-    <t>OREO SNDW HOTTEOK105</t>
-  </si>
-  <si>
-    <t>20015337</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW COKL 190</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20015338</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CHSE 190</t>
-  </si>
-  <si>
     <t>10008579</t>
   </si>
   <si>
     <t>DELFI MINIS BLK.VN70</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>10008580</t>
   </si>
   <si>
     <t>DELFI MINIS CHOCO 70</t>
   </si>
   <si>
-    <t>20048790</t>
-  </si>
-  <si>
-    <t>OREO MINI CHOCO 58.4</t>
-  </si>
-  <si>
-    <t>20048791</t>
-  </si>
-  <si>
-    <t>OREO MINI VANLA 58.4</t>
-  </si>
-  <si>
     <t>20076573</t>
   </si>
   <si>
@@ -835,12 +874,6 @@
     <t>NEXTAR RICHOCO 8'S</t>
   </si>
   <si>
-    <t>20071746</t>
-  </si>
-  <si>
-    <t>SPRSTAR TRPL.CHO 6'S</t>
-  </si>
-  <si>
     <t>10032077</t>
   </si>
   <si>
@@ -898,18 +931,18 @@
     <t>MONDE BT.COOKIES 150</t>
   </si>
   <si>
+    <t>10038628</t>
+  </si>
+  <si>
+    <t>HATARI BIS.PEANUT225</t>
+  </si>
+  <si>
     <t>20135148</t>
   </si>
   <si>
     <t>MONDE SHRTBRD MTG115</t>
   </si>
   <si>
-    <t>10038628</t>
-  </si>
-  <si>
-    <t>HATARI BIS.PEANUT225</t>
-  </si>
-  <si>
     <t>10033424</t>
   </si>
   <si>
@@ -1156,34 +1189,13 @@
     <t>NYAM2 STCK CHOBRY 25</t>
   </si>
   <si>
-    <t>20134691</t>
-  </si>
-  <si>
-    <t>TWB CRACKR RAINBOW57</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20021257</t>
-  </si>
-  <si>
-    <t>U/BISC BONBON CHO200</t>
+    <t>20020018</t>
+  </si>
+  <si>
+    <t>HATARI S.H.PUFF 245G</t>
   </si>
   <si>
     <t>37</t>
-  </si>
-  <si>
-    <t>20008947</t>
-  </si>
-  <si>
-    <t>K/G MALKIS SPRCO 138</t>
-  </si>
-  <si>
-    <t>20020018</t>
-  </si>
-  <si>
-    <t>HATARI S.H.PUFF 245G</t>
   </si>
   <si>
     <t>20122975</t>
@@ -1819,7 +1831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F211"/>
+  <dimension ref="A1:F213"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1920,30 +1932,30 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -1960,30 +1972,30 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -1991,10 +2003,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -2003,7 +2015,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -2011,19 +2023,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -2031,16 +2043,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>8</v>
@@ -2051,19 +2063,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -2071,19 +2083,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -2091,19 +2103,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -2111,16 +2123,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>8</v>
@@ -2131,19 +2143,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -2151,19 +2163,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -2171,19 +2183,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -2191,16 +2203,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
@@ -2211,19 +2223,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -2231,19 +2243,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -2251,16 +2263,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>8</v>
@@ -2271,19 +2283,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2291,19 +2303,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2311,36 +2323,36 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>8</v>
@@ -2351,19 +2363,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2371,19 +2383,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2391,19 +2403,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2411,19 +2423,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2431,22 +2443,22 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2460,13 +2472,13 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2480,13 +2492,13 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2500,10 +2512,10 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2520,10 +2532,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2540,10 +2552,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2560,10 +2572,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2580,10 +2592,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2591,19 +2603,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2611,19 +2623,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2631,19 +2643,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2660,10 +2672,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2680,10 +2692,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2700,10 +2712,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2711,19 +2723,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2731,19 +2743,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2751,19 +2763,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2780,10 +2792,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2791,19 +2803,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2811,19 +2823,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2831,22 +2843,22 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2860,53 +2872,53 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="E53" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2920,10 +2932,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2940,10 +2952,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2951,19 +2963,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2980,7 +2992,7 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>8</v>
@@ -3000,10 +3012,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3023,7 +3035,7 @@
         <v>135</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3043,7 +3055,7 @@
         <v>135</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3063,7 +3075,7 @@
         <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3083,7 +3095,7 @@
         <v>135</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3103,7 +3115,7 @@
         <v>135</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3123,7 +3135,7 @@
         <v>135</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3140,10 +3152,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3151,19 +3163,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3171,19 +3183,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3200,13 +3212,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3220,13 +3232,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3240,13 +3252,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3260,13 +3272,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3280,10 +3292,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3300,10 +3312,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3320,13 +3332,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3340,10 +3352,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3351,39 +3363,39 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3400,10 +3412,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3420,10 +3432,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3440,10 +3452,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3460,10 +3472,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3480,10 +3492,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3500,10 +3512,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3520,10 +3532,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3540,30 +3552,30 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3571,22 +3583,22 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>195</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3600,10 +3612,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3620,10 +3632,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3640,10 +3652,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3660,70 +3672,70 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3731,22 +3743,22 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>195</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3760,10 +3772,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3771,22 +3783,22 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3800,10 +3812,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3811,19 +3823,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3840,10 +3852,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3866,7 +3878,7 @@
         <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3883,7 +3895,7 @@
         <v>228</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3900,10 +3912,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3911,19 +3923,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3931,19 +3943,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3960,10 +3972,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3980,10 +3992,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3991,19 +4003,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -4020,7 +4032,7 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>8</v>
@@ -4040,10 +4052,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4051,19 +4063,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4071,19 +4083,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4100,50 +4112,50 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4151,19 +4163,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4171,19 +4183,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4191,19 +4203,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4211,42 +4223,42 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4260,30 +4272,30 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4291,19 +4303,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4311,22 +4323,22 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>280</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4340,70 +4352,70 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4411,39 +4423,39 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4460,10 +4472,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4480,13 +4492,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>195</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4500,10 +4512,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4511,19 +4523,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4540,10 +4552,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4560,13 +4572,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4580,10 +4592,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4591,19 +4603,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4620,10 +4632,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4640,13 +4652,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4660,10 +4672,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4671,19 +4683,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4700,10 +4712,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4720,10 +4732,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4740,13 +4752,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4783,7 +4795,7 @@
         <v>330</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4803,7 +4815,7 @@
         <v>330</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4820,10 +4832,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4831,19 +4843,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4851,19 +4863,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4880,10 +4892,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4900,10 +4912,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4911,19 +4923,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4940,10 +4952,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4960,10 +4972,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4980,10 +4992,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4991,19 +5003,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -5020,10 +5032,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5040,10 +5052,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5060,10 +5072,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5071,19 +5083,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5100,13 +5112,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5120,13 +5132,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5140,7 +5152,7 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
@@ -5160,10 +5172,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5171,16 +5183,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>14</v>
@@ -5191,62 +5203,62 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>383</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5260,30 +5272,30 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>195</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5291,62 +5303,62 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>195</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>383</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>383</v>
+        <v>191</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5360,53 +5372,53 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>195</v>
+        <v>271</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>195</v>
+        <v>271</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5420,13 +5432,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5440,50 +5452,50 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E183" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5500,10 +5512,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5520,10 +5532,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5531,19 +5543,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5551,19 +5563,19 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5580,10 +5592,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5600,13 +5612,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>195</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5620,10 +5632,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5631,39 +5643,39 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="E192" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5680,10 +5692,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5700,10 +5712,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5720,10 +5732,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5731,19 +5743,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5751,19 +5763,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5780,10 +5792,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5800,10 +5812,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5820,10 +5832,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5831,19 +5843,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5851,19 +5863,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5880,10 +5892,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5900,10 +5912,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5920,10 +5932,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5940,10 +5952,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5951,19 +5963,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5971,19 +5983,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6000,10 +6012,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6020,10 +6032,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6040,12 +6052,52 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="F211" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F213" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="478">
   <si>
     <t/>
   </si>
@@ -340,22 +340,28 @@
     <t>11</t>
   </si>
   <si>
+    <t>20138977</t>
+  </si>
+  <si>
+    <t>TANGO WFR LG CHES100</t>
+  </si>
+  <si>
+    <t>20132881</t>
+  </si>
+  <si>
+    <t>TANGO WFR SSY STR100</t>
+  </si>
+  <si>
+    <t>20071746</t>
+  </si>
+  <si>
+    <t>SPRSTAR TRPL.CHO 6'S</t>
+  </si>
+  <si>
     <t>10007336</t>
   </si>
   <si>
     <t>TANGO WFR STRAW 124G</t>
-  </si>
-  <si>
-    <t>20138977</t>
-  </si>
-  <si>
-    <t>TANGO WFR LG CHES100</t>
-  </si>
-  <si>
-    <t>20071746</t>
-  </si>
-  <si>
-    <t>SPRSTAR TRPL.CHO 6'S</t>
   </si>
   <si>
     <t>20027448</t>
@@ -1831,7 +1837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F213"/>
+  <dimension ref="A1:F214"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2872,10 +2878,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2883,22 +2889,22 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="E53" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2912,10 +2918,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>15</v>
@@ -2932,13 +2938,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2952,10 +2958,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2963,19 +2969,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="E57" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2992,10 +2998,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3012,10 +3018,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3032,10 +3038,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3043,19 +3049,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3072,10 +3078,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3092,10 +3098,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3112,10 +3118,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3132,10 +3138,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3152,10 +3158,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3163,19 +3169,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3192,10 +3198,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3212,13 +3218,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3232,10 +3238,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>15</v>
@@ -3252,13 +3258,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3272,10 +3278,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3292,10 +3298,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3312,10 +3318,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3332,13 +3338,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3352,30 +3358,30 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3392,10 +3398,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3412,10 +3418,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3432,10 +3438,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3452,10 +3458,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3472,10 +3478,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3492,10 +3498,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3512,10 +3518,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3532,10 +3538,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3552,33 +3558,33 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="E87" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3592,10 +3598,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3612,10 +3618,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3632,10 +3638,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3652,10 +3658,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3672,30 +3678,30 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>15</v>
@@ -3712,13 +3718,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3732,13 +3738,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3752,10 +3758,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3763,19 +3769,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="E97" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3792,33 +3798,33 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>218</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3832,10 +3838,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3843,19 +3849,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3872,33 +3878,33 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3912,10 +3918,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3923,19 +3929,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3952,10 +3958,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3972,10 +3978,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3992,10 +3998,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -4003,19 +4009,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -4032,10 +4038,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4052,10 +4058,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4072,10 +4078,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4092,10 +4098,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4103,19 +4109,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4132,10 +4138,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4152,10 +4158,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4172,7 +4178,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>11</v>
@@ -4183,19 +4189,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4212,10 +4218,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4232,10 +4238,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4252,50 +4258,50 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>271</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="E123" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4312,10 +4318,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4332,10 +4338,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4352,13 +4358,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4372,10 +4378,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>15</v>
@@ -4392,10 +4398,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>15</v>
@@ -4412,13 +4418,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4432,50 +4438,50 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>291</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4492,13 +4498,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4512,13 +4518,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4532,10 +4538,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4543,19 +4549,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4572,13 +4578,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4592,13 +4598,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4612,10 +4618,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4623,19 +4629,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4652,10 +4658,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4672,10 +4678,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4692,10 +4698,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4703,19 +4709,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4732,10 +4738,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4752,13 +4758,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4772,30 +4778,30 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4812,10 +4818,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4832,10 +4838,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4852,10 +4858,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4872,10 +4878,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4883,19 +4889,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="E153" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4912,10 +4918,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4932,10 +4938,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4943,19 +4949,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4972,10 +4978,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4992,10 +4998,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -5012,10 +5018,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -5023,19 +5029,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5052,10 +5058,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5072,10 +5078,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5092,10 +5098,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5103,19 +5109,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5132,10 +5138,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5152,10 +5158,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5172,10 +5178,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5183,19 +5189,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E168" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5212,13 +5218,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5232,10 +5238,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>15</v>
@@ -5252,13 +5258,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5272,10 +5278,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5292,10 +5298,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5312,10 +5318,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5332,10 +5338,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5352,33 +5358,33 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>271</v>
+        <v>193</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5392,13 +5398,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5412,33 +5418,33 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5452,13 +5458,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5472,13 +5478,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -5492,30 +5498,30 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="E184" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5532,10 +5538,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5552,10 +5558,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5572,10 +5578,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5583,19 +5589,19 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5612,10 +5618,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5632,10 +5638,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5652,13 +5658,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5672,30 +5678,30 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5712,10 +5718,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5732,10 +5738,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5752,10 +5758,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5772,10 +5778,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5783,19 +5789,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5812,10 +5818,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5832,10 +5838,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5852,10 +5858,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5872,10 +5878,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5883,19 +5889,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="E203" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5912,10 +5918,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5932,10 +5938,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5952,10 +5958,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5972,10 +5978,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5992,10 +5998,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6003,19 +6009,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B209" s="1" t="s">
+      <c r="C209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="E209" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6032,10 +6038,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6052,10 +6058,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6072,10 +6078,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6092,12 +6098,32 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E213" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="E214" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F213" s="1" t="s">
+      <c r="F214" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="493">
   <si>
     <t/>
   </si>
@@ -253,6 +253,12 @@
     <t>TANGO WFR VANL 95G</t>
   </si>
   <si>
+    <t>20143337</t>
+  </si>
+  <si>
+    <t>TANGO WFLE CHO HZL70</t>
+  </si>
+  <si>
     <t>20138099</t>
   </si>
   <si>
@@ -376,13 +382,13 @@
     <t>20055311</t>
   </si>
   <si>
-    <t>NABATI RCHSE WFR 110</t>
+    <t>NABATI RCHSE WFR 100</t>
   </si>
   <si>
     <t>20055312</t>
   </si>
   <si>
-    <t>NBATI RCHCO WFR C110</t>
+    <t>NBTI RCHCO WFR CK100</t>
   </si>
   <si>
     <t>20138462</t>
@@ -520,15 +526,21 @@
     <t>NYAM2 POPSTIX CHO 48</t>
   </si>
   <si>
+    <t>20134875</t>
+  </si>
+  <si>
+    <t>CHOKI2 STIK CHOCO48G</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>10000213</t>
   </si>
   <si>
     <t>GLICO POCKY CHO 47GR</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>10036916</t>
   </si>
   <si>
@@ -697,6 +709,12 @@
     <t>IMPERIAL STRW&amp;CH 100</t>
   </si>
   <si>
+    <t>20125056</t>
+  </si>
+  <si>
+    <t>UNIBIS MRING TART120</t>
+  </si>
+  <si>
     <t>20021257</t>
   </si>
   <si>
@@ -835,6 +853,24 @@
     <t>RT,(E-1.5B)</t>
   </si>
   <si>
+    <t>20143289</t>
+  </si>
+  <si>
+    <t>NSN COOKIES KLPN 60G</t>
+  </si>
+  <si>
+    <t>20143285</t>
+  </si>
+  <si>
+    <t>MONDE SHRTBRD BISC70</t>
+  </si>
+  <si>
+    <t>20143290</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHCLAVA 5</t>
+  </si>
+  <si>
     <t>20133507</t>
   </si>
   <si>
@@ -1202,6 +1238,15 @@
   </si>
   <si>
     <t>37</t>
+  </si>
+  <si>
+    <t>20020089</t>
+  </si>
+  <si>
+    <t>UNIBIS S.H.PUFF 247G</t>
+  </si>
+  <si>
+    <t>,(E-4B)</t>
   </si>
   <si>
     <t>20122975</t>
@@ -1837,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F214"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2561,7 +2606,7 @@
         <v>71</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2581,7 +2626,7 @@
         <v>71</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2601,7 +2646,7 @@
         <v>71</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2609,19 +2654,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2638,10 +2683,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2658,10 +2703,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2678,10 +2723,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2698,10 +2743,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2718,10 +2763,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2729,19 +2774,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2758,10 +2803,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2778,10 +2823,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2798,10 +2843,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2809,19 +2854,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2838,10 +2883,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2858,10 +2903,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2878,10 +2923,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2898,10 +2943,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2909,22 +2954,22 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2938,10 +2983,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>15</v>
@@ -2958,13 +3003,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2978,10 +3023,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2989,19 +3034,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3018,10 +3063,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3038,10 +3083,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3058,10 +3103,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3069,19 +3114,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3098,10 +3143,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3118,10 +3163,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3138,10 +3183,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3158,10 +3203,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3178,10 +3223,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3189,19 +3234,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3218,10 +3263,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3238,13 +3283,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,10 +3303,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>15</v>
@@ -3278,13 +3323,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,10 +3343,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3318,10 +3363,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3338,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3358,13 +3403,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3378,30 +3423,30 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3418,10 +3463,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3438,10 +3483,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3458,10 +3503,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3478,10 +3523,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3498,10 +3543,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3518,10 +3563,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3538,10 +3583,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3558,10 +3603,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3578,30 +3623,30 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3609,22 +3654,22 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="E89" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3638,10 +3683,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3658,10 +3703,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3678,10 +3723,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3698,53 +3743,53 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3758,13 +3803,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3778,30 +3823,30 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3809,39 +3854,39 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>220</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3849,39 +3894,39 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3889,36 +3934,36 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>14</v>
@@ -3929,19 +3974,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3949,39 +3994,39 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3989,19 +4034,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -4018,10 +4063,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -4029,19 +4074,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4049,19 +4094,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4069,19 +4114,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4098,10 +4143,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4118,10 +4163,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4129,19 +4174,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4149,19 +4194,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4169,19 +4214,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4198,10 +4243,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4209,19 +4254,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4229,19 +4274,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4249,19 +4294,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4278,30 +4323,30 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4309,19 +4354,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4329,39 +4374,39 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4369,62 +4414,62 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4438,10 +4483,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4458,30 +4503,30 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>293</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4489,39 +4534,39 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>15</v>
@@ -4529,39 +4574,39 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4569,59 +4614,59 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4629,39 +4674,39 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4669,19 +4714,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4689,19 +4734,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4709,39 +4754,39 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4749,19 +4794,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4769,39 +4814,39 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4809,19 +4854,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4829,19 +4874,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4849,19 +4894,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4869,19 +4914,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4889,39 +4934,39 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4929,19 +4974,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4949,19 +4994,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4969,19 +5014,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4989,19 +5034,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -5009,19 +5054,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -5029,19 +5074,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5049,19 +5094,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5069,19 +5114,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5089,19 +5134,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5109,19 +5154,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5129,19 +5174,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5149,19 +5194,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5169,19 +5214,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5189,19 +5234,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5209,19 +5254,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5229,59 +5274,59 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5289,19 +5334,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5309,19 +5354,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5338,10 +5383,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5358,13 +5403,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5378,213 +5423,213 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="E183" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>279</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>279</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5598,70 +5643,70 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="E191" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5678,13 +5723,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5698,10 +5743,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5709,19 +5754,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5729,19 +5774,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5758,10 +5803,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5778,10 +5823,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5798,10 +5843,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5809,39 +5854,39 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5858,10 +5903,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5878,10 +5923,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5898,10 +5943,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5909,19 +5954,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5929,19 +5974,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5958,10 +6003,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5978,10 +6023,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5998,10 +6043,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6018,10 +6063,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6029,19 +6074,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="C210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="E210" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6058,10 +6103,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6078,10 +6123,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6098,10 +6143,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6118,12 +6163,152 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E214" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E215" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F214" s="1" t="s">
+      <c r="F215" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F221" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -19,7 +19,7 @@
     <t>20130350</t>
   </si>
   <si>
-    <t>POCKY CHOCOLATE 154</t>
+    <t>POCKY CHOCOLATE 140</t>
   </si>
   <si>
     <t>BIS05D</t>
@@ -178,7 +178,7 @@
     <t>20132494</t>
   </si>
   <si>
-    <t>LEMONILO BRWNS KJU33</t>
+    <t>LEMONILO BRWNS KJU32</t>
   </si>
   <si>
     <t>7</t>
@@ -187,19 +187,19 @@
     <t>20130152</t>
   </si>
   <si>
-    <t>LEMONILO BROWNIES 33</t>
+    <t>LEMONILO BROWNIES 32</t>
   </si>
   <si>
     <t>20142678</t>
   </si>
   <si>
-    <t>LMNILO LMN CHESSE 33</t>
+    <t>LMNILO LMN CHESSE 32</t>
   </si>
   <si>
     <t>20137230</t>
   </si>
   <si>
-    <t>LEMONILO BRWNS STR33</t>
+    <t>LEMONILO BRWNS STR32</t>
   </si>
   <si>
     <t>20137584</t>
@@ -334,7 +334,7 @@
     <t>20109917</t>
   </si>
   <si>
-    <t>ROMA WFR CHO BLS97.6</t>
+    <t>RMA WAFELO C/BLS97.6</t>
   </si>
   <si>
     <t>20069149</t>
@@ -538,13 +538,13 @@
     <t>10000213</t>
   </si>
   <si>
-    <t>GLICO POCKY CHO 47GR</t>
+    <t>GLICO POCKY CHO 40GR</t>
   </si>
   <si>
     <t>10036916</t>
   </si>
   <si>
-    <t>GLICO POCKY.STRAW 45</t>
+    <t>GLICO POCKY.STRAW39G</t>
   </si>
   <si>
     <t>20086168</t>
@@ -556,7 +556,7 @@
     <t>20138741</t>
   </si>
   <si>
-    <t>GLICO POCKY MILK 39G</t>
+    <t>GLICO POCKY MILK 40G</t>
   </si>
   <si>
     <t>20138740</t>
@@ -568,13 +568,13 @@
     <t>20062839</t>
   </si>
   <si>
-    <t>GLCO POCKY MTCHA 33G</t>
+    <t>GLCO POCKY MTCHA 35G</t>
   </si>
   <si>
     <t>20057865</t>
   </si>
   <si>
-    <t>GLCO POCKY DOU.CHO47</t>
+    <t>GLCO POCKY DOU.CHO39</t>
   </si>
   <si>
     <t>20134839</t>
@@ -1246,7 +1246,7 @@
     <t>UNIBIS S.H.PUFF 247G</t>
   </si>
   <si>
-    <t>,(E-4B)</t>
+    <t>RT,(E-4B)</t>
   </si>
   <si>
     <t>20122975</t>
@@ -1318,7 +1318,7 @@
     <t>10000206</t>
   </si>
   <si>
-    <t>NISSIN CR.CRISPY 250</t>
+    <t>NISSIN CR.CRISPY 225</t>
   </si>
   <si>
     <t>40</t>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="485">
   <si>
     <t/>
   </si>
@@ -364,12 +364,6 @@
     <t>SPRSTAR TRPL.CHO 6'S</t>
   </si>
   <si>
-    <t>10007336</t>
-  </si>
-  <si>
-    <t>TANGO WFR STRAW 124G</t>
-  </si>
-  <si>
     <t>20027448</t>
   </si>
   <si>
@@ -412,18 +406,6 @@
     <t>BISKUAT BITE CKLT 35</t>
   </si>
   <si>
-    <t>20139060</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE ORI 35G</t>
-  </si>
-  <si>
-    <t>20139686</t>
-  </si>
-  <si>
-    <t>TANGO WFLE WAHH 67.5</t>
-  </si>
-  <si>
     <t>20139392</t>
   </si>
   <si>
@@ -671,12 +653,6 @@
   </si>
   <si>
     <t>19</t>
-  </si>
-  <si>
-    <t>20137568</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.VNL105G</t>
   </si>
   <si>
     <t>20085046</t>
@@ -1882,7 +1858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F221"/>
+  <dimension ref="A1:F217"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2943,10 +2919,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2954,22 +2930,22 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2983,10 +2959,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>15</v>
@@ -3003,13 +2979,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3023,10 +2999,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -3034,19 +3010,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3063,10 +3039,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -3074,19 +3050,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3094,19 +3070,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3114,19 +3090,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3143,10 +3119,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3163,10 +3139,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3183,10 +3159,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3194,19 +3170,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3214,19 +3190,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3234,22 +3210,22 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3263,13 +3239,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3283,10 +3259,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3303,13 +3279,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3323,13 +3299,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3343,10 +3319,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3363,13 +3339,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3383,10 +3359,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3394,19 +3370,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3414,39 +3390,39 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3463,10 +3439,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3483,10 +3459,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3503,10 +3479,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3523,10 +3499,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3543,10 +3519,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3563,10 +3539,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3583,10 +3559,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3603,30 +3579,30 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3634,19 +3610,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3654,22 +3630,22 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3683,10 +3659,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3703,10 +3679,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3723,73 +3699,73 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3803,47 +3779,47 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>11</v>
@@ -3854,16 +3830,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>4</v>
@@ -3874,16 +3850,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>14</v>
@@ -3894,59 +3870,59 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>224</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3954,19 +3930,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3974,19 +3950,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3994,39 +3970,39 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -4034,16 +4010,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>4</v>
@@ -4054,16 +4030,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>14</v>
@@ -4074,16 +4050,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>8</v>
@@ -4094,16 +4070,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>11</v>
@@ -4114,19 +4090,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4143,10 +4119,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4154,19 +4130,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4174,19 +4150,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4194,19 +4170,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4214,16 +4190,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>4</v>
@@ -4234,16 +4210,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>14</v>
@@ -4254,16 +4230,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>8</v>
@@ -4274,16 +4250,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>11</v>
@@ -4294,39 +4270,39 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4334,19 +4310,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4354,19 +4330,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4374,39 +4350,39 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>279</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4414,19 +4390,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4434,19 +4410,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4454,22 +4430,22 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4483,13 +4459,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4503,13 +4479,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4523,10 +4499,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4543,107 +4519,107 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>15</v>
+        <v>297</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>305</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>4</v>
@@ -4654,16 +4630,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>14</v>
@@ -4674,36 +4650,36 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>15</v>
+        <v>191</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>11</v>
@@ -4714,16 +4690,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>4</v>
@@ -4734,16 +4710,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>14</v>
@@ -4754,36 +4730,36 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>11</v>
@@ -4794,16 +4770,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>4</v>
@@ -4814,16 +4790,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>14</v>
@@ -4834,16 +4810,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>8</v>
@@ -4854,36 +4830,36 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>4</v>
@@ -4894,16 +4870,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>14</v>
@@ -4914,16 +4890,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>8</v>
@@ -4934,39 +4910,39 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4983,10 +4959,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4994,19 +4970,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -5014,19 +4990,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -5034,19 +5010,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -5054,19 +5030,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -5074,19 +5050,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -5094,19 +5070,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5114,16 +5090,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>4</v>
@@ -5134,16 +5110,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>14</v>
@@ -5154,16 +5130,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>8</v>
@@ -5174,16 +5150,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>11</v>
@@ -5194,16 +5170,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>4</v>
@@ -5214,16 +5190,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>14</v>
@@ -5234,16 +5210,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>8</v>
@@ -5254,16 +5230,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>11</v>
@@ -5274,16 +5250,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>4</v>
@@ -5294,16 +5270,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>14</v>
@@ -5314,59 +5290,59 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5383,10 +5359,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5403,13 +5379,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5423,13 +5399,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5443,10 +5419,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5463,247 +5439,247 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>5</v>
+        <v>403</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>271</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B184" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="E184" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>411</v>
+        <v>191</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>4</v>
@@ -5714,16 +5690,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>14</v>
@@ -5734,16 +5710,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>8</v>
@@ -5754,16 +5730,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>11</v>
@@ -5774,22 +5750,22 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5803,10 +5779,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5814,19 +5790,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5834,19 +5810,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5854,39 +5830,39 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5903,10 +5879,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5914,19 +5890,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5934,16 +5910,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>11</v>
@@ -5954,16 +5930,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>40</v>
@@ -5974,19 +5950,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -6003,10 +5979,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -6014,19 +5990,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -6034,19 +6010,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6054,19 +6030,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6074,19 +6050,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6103,10 +6079,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6123,10 +6099,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6134,19 +6110,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6154,19 +6130,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6174,19 +6150,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6194,19 +6170,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6223,92 +6199,12 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F218" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F219" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F220" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F221" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -295,7 +295,7 @@
     <t>20010655</t>
   </si>
   <si>
-    <t>TANGO WFER CHOCO 240</t>
+    <t>TANGO WFER CHOCO 220</t>
   </si>
   <si>
     <t>10000133</t>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,54 +11,1341 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="487">
   <si>
     <t/>
   </si>
   <si>
+    <t>20025592</t>
+  </si>
+  <si>
+    <t>K/G WAFER CLASSIC350</t>
+  </si>
+  <si>
+    <t>BIS05D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20013332</t>
+  </si>
+  <si>
+    <t>K/G SALTCH CMBO10X17</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20125628</t>
+  </si>
+  <si>
+    <t>NSSIN WFR CHO/LVA137</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20142944</t>
+  </si>
+  <si>
+    <t>IDM CHOCO WAFER 120</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10000726</t>
+  </si>
+  <si>
+    <t>ASTOR CHOCOLATE 150G</t>
+  </si>
+  <si>
+    <t>20129572</t>
+  </si>
+  <si>
+    <t>CHCLATOS WFR VNLA90</t>
+  </si>
+  <si>
+    <t>20127761</t>
+  </si>
+  <si>
+    <t>CHCLATOS WFR CHO 90</t>
+  </si>
+  <si>
+    <t>10000175</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHO 110G</t>
+  </si>
+  <si>
+    <t>20063092</t>
+  </si>
+  <si>
+    <t>SELAMAT DBL CHOCO128</t>
+  </si>
+  <si>
+    <t>10016650</t>
+  </si>
+  <si>
+    <t>SELAMAT WF.CHOCO 128</t>
+  </si>
+  <si>
+    <t>10004541</t>
+  </si>
+  <si>
+    <t>TANGO WFR VNLA 124G</t>
+  </si>
+  <si>
+    <t>10004540</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOCO 124G</t>
+  </si>
+  <si>
+    <t>20138977</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHE 98 G</t>
+  </si>
+  <si>
+    <t>20132881</t>
+  </si>
+  <si>
+    <t>TANGO WFR S.ST 100 G</t>
+  </si>
+  <si>
+    <t>20138462</t>
+  </si>
+  <si>
+    <t>NABATI WFR STRAW 122</t>
+  </si>
+  <si>
+    <t>20109917</t>
+  </si>
+  <si>
+    <t>RMA WAFELO C/BLS97.6</t>
+  </si>
+  <si>
+    <t>20027448</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHO 100 G</t>
+  </si>
+  <si>
+    <t>20069149</t>
+  </si>
+  <si>
+    <t>TANGO WFR VM 100 G</t>
+  </si>
+  <si>
+    <t>20055312</t>
+  </si>
+  <si>
+    <t>NBTI RCHCO WFR CK100</t>
+  </si>
+  <si>
+    <t>20055311</t>
+  </si>
+  <si>
+    <t>NABATI RCHSE WFR 100</t>
+  </si>
+  <si>
+    <t>20134691</t>
+  </si>
+  <si>
+    <t>TWB CRACKR RAINBOW57</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20139392</t>
+  </si>
+  <si>
+    <t>BRINGZ LMIER BTR 100</t>
+  </si>
+  <si>
+    <t>20142670</t>
+  </si>
+  <si>
+    <t>KTST BGLN GT CHESE45</t>
+  </si>
+  <si>
+    <t>20142669</t>
+  </si>
+  <si>
+    <t>KTST BGLN GT BUTER45</t>
+  </si>
+  <si>
+    <t>20048790</t>
+  </si>
+  <si>
+    <t>OREO MINI CHOCO 58.4</t>
+  </si>
+  <si>
+    <t>20048791</t>
+  </si>
+  <si>
+    <t>OREO MINI VANLA 58.4</t>
+  </si>
+  <si>
+    <t>20137583</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHEESE35</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20143735</t>
+  </si>
+  <si>
+    <t>IDM BRWNS CRSPY MW35</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20132494</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS KJU32</t>
+  </si>
+  <si>
+    <t>20130152</t>
+  </si>
+  <si>
+    <t>LEMONILO BROWNIES 32</t>
+  </si>
+  <si>
+    <t>20142678</t>
+  </si>
+  <si>
+    <t>LMNILO LMN CHESSE 32</t>
+  </si>
+  <si>
+    <t>20137230</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS STR32</t>
+  </si>
+  <si>
+    <t>20139819</t>
+  </si>
+  <si>
+    <t>TANGO BROWNIS CR.35G</t>
+  </si>
+  <si>
+    <t>20137584</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHOCIP35</t>
+  </si>
+  <si>
+    <t>10000360</t>
+  </si>
+  <si>
+    <t>KHONG GUAN RED 1600G</t>
+  </si>
+  <si>
+    <t>10000133</t>
+  </si>
+  <si>
+    <t>KHONG GUAN MN ASS650</t>
+  </si>
+  <si>
+    <t>10000132</t>
+  </si>
+  <si>
+    <t>MONDE BT.COOKIES 454</t>
+  </si>
+  <si>
+    <t>20010655</t>
+  </si>
+  <si>
+    <t>TANGO WFER CHOCO 220</t>
+  </si>
+  <si>
+    <t>10000734</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHOCO 570</t>
+  </si>
+  <si>
+    <t>20128683</t>
+  </si>
+  <si>
+    <t>TANGO WFLE CHO HZL63</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10038628</t>
+  </si>
+  <si>
+    <t>HATARI BIS.PEANUT225</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20142943</t>
+  </si>
+  <si>
+    <t>IDM CHOCO CRACKR 100</t>
+  </si>
+  <si>
+    <t>20137569</t>
+  </si>
+  <si>
+    <t>BISKUAT GOLD.STR105G</t>
+  </si>
+  <si>
+    <t>20131802</t>
+  </si>
+  <si>
+    <t>IMPERIAL BLUBERRY108</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20139973</t>
+  </si>
+  <si>
+    <t>IMPERIAL STRW&amp;CH 100</t>
+  </si>
+  <si>
+    <t>20085046</t>
+  </si>
+  <si>
+    <t>JULIES PNUT BTR 82.5</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20057475</t>
+  </si>
+  <si>
+    <t>SERENA TOGO CKLT 128</t>
+  </si>
+  <si>
+    <t>20125056</t>
+  </si>
+  <si>
+    <t>UNIBIS MRING TART120</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>10003144</t>
+  </si>
+  <si>
+    <t>MONDE BOURBON CHO140</t>
+  </si>
+  <si>
+    <t>20142677</t>
+  </si>
+  <si>
+    <t>MONDE BRBON GNDM 140</t>
+  </si>
+  <si>
+    <t>20021257</t>
+  </si>
+  <si>
+    <t>U/BISC BONBON CHO200</t>
+  </si>
+  <si>
+    <t>20141506</t>
+  </si>
+  <si>
+    <t>RITZ CRACKER ORI 100</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20139951</t>
+  </si>
+  <si>
+    <t>KOKOLA BLCK CKLT 110</t>
+  </si>
+  <si>
+    <t>20008947</t>
+  </si>
+  <si>
+    <t>K/G MALKIS SPRCO 138</t>
+  </si>
+  <si>
+    <t>10036938</t>
+  </si>
+  <si>
+    <t>SRENA S.CAKE CHO 225</t>
+  </si>
+  <si>
+    <t>20095021</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CKLT 76G</t>
+  </si>
+  <si>
+    <t>20091225</t>
+  </si>
+  <si>
+    <t>OVLTNE CHO BISC 104G</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20134983</t>
+  </si>
+  <si>
+    <t>RITZ CRCKRS CHSE 91G</t>
+  </si>
+  <si>
+    <t>20134984</t>
+  </si>
+  <si>
+    <t>RITZ CRCKRS CHOC 91G</t>
+  </si>
+  <si>
+    <t>20142222</t>
+  </si>
+  <si>
+    <t>RITZ CRCKS KYA BUT91</t>
+  </si>
+  <si>
+    <t>20074990</t>
+  </si>
+  <si>
+    <t>OREO DARK&amp;WHT 105G</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20142591</t>
+  </si>
+  <si>
+    <t>OREO SNDW HOTTEOK105</t>
+  </si>
+  <si>
+    <t>20134970</t>
+  </si>
+  <si>
+    <t>MILO SANDW ORIG 96G</t>
+  </si>
+  <si>
+    <t>20134969</t>
+  </si>
+  <si>
+    <t>MILO SANDW MILK 96G</t>
+  </si>
+  <si>
+    <t>20140011</t>
+  </si>
+  <si>
+    <t>MILO BISC. CHOCO 96G</t>
+  </si>
+  <si>
+    <t>20030547</t>
+  </si>
+  <si>
+    <t>OREO ICE CRM BL 105G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>10016170</t>
+  </si>
+  <si>
+    <t>OREO CHOCO CRM 105G</t>
+  </si>
+  <si>
+    <t>20024644</t>
+  </si>
+  <si>
+    <t>OREO STRAW CREM1105G</t>
+  </si>
+  <si>
+    <t>20106305</t>
+  </si>
+  <si>
+    <t>OREO RED VELVET 105G</t>
+  </si>
+  <si>
+    <t>10035165</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 105G</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20138464</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 147.2G</t>
+  </si>
+  <si>
+    <t>20143289</t>
+  </si>
+  <si>
+    <t>NSN COOKIES KLPN 60G</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20143285</t>
+  </si>
+  <si>
+    <t>MONDE SHRTBRD BISC70</t>
+  </si>
+  <si>
+    <t>20076573</t>
+  </si>
+  <si>
+    <t>NEXTAR CHO.BRWNS 8'S</t>
+  </si>
+  <si>
+    <t>20071797</t>
+  </si>
+  <si>
+    <t>NEXTAR PINEAPPLE 8'S</t>
+  </si>
+  <si>
+    <t>20130555</t>
+  </si>
+  <si>
+    <t>NEXTAR RICHOCO 8'S</t>
+  </si>
+  <si>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
+  </si>
+  <si>
+    <t>20015338</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CHSE 190</t>
+  </si>
+  <si>
+    <t>10036899</t>
+  </si>
+  <si>
+    <t>REGAL MARIE BARU 550</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20056645</t>
+  </si>
+  <si>
+    <t>NARAYA OAT CHOCO 90G</t>
+  </si>
+  <si>
+    <t>20061189</t>
+  </si>
+  <si>
+    <t>NARAYA OAT CHOCO 90</t>
+  </si>
+  <si>
+    <t>20133507</t>
+  </si>
+  <si>
+    <t>DELFI KRICE SWD 47.4</t>
+  </si>
+  <si>
+    <t>20133506</t>
+  </si>
+  <si>
+    <t>DELFI KRICE SWET64.8</t>
+  </si>
+  <si>
+    <t>20139081</t>
+  </si>
+  <si>
+    <t>REGAL CHO MARIE 64G</t>
+  </si>
+  <si>
+    <t>20130007</t>
+  </si>
+  <si>
+    <t>BETTER FUN BITES 10S</t>
+  </si>
+  <si>
     <t>20130350</t>
   </si>
   <si>
     <t>POCKY CHOCOLATE 140</t>
   </si>
   <si>
-    <t>BIS05D</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20025592</t>
-  </si>
-  <si>
-    <t>K/G WAFER CLASSIC350</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10036899</t>
-  </si>
-  <si>
-    <t>REGAL MARIE BARU 550</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20125628</t>
-  </si>
-  <si>
-    <t>NSSIN WFR CHO/LVA137</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
+    <t>19</t>
+  </si>
+  <si>
+    <t>10003324</t>
+  </si>
+  <si>
+    <t>MONDE GENJIE PIE 70G</t>
+  </si>
+  <si>
+    <t>10036942</t>
+  </si>
+  <si>
+    <t>MONDE S.PIE STRW 85G</t>
+  </si>
+  <si>
+    <t>20030358</t>
+  </si>
+  <si>
+    <t>MONDE GNJI MN PIE 50</t>
+  </si>
+  <si>
+    <t>20096783</t>
+  </si>
+  <si>
+    <t>DELFI CHO.PIE DRK180</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20083539</t>
+  </si>
+  <si>
+    <t>DELFI CUSTAS SC 6'S</t>
+  </si>
+  <si>
+    <t>20025508</t>
+  </si>
+  <si>
+    <t>PIA 100 KCG HJ 138G</t>
+  </si>
+  <si>
+    <t>20025507</t>
+  </si>
+  <si>
+    <t>PIA 100 COKLAT 138G</t>
+  </si>
+  <si>
+    <t>20139391</t>
+  </si>
+  <si>
+    <t>NEXTAR CHOC PIE 6S</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20140126</t>
+  </si>
+  <si>
+    <t>NEXTAR STRAWB CHS144</t>
+  </si>
+  <si>
+    <t>20133247</t>
+  </si>
+  <si>
+    <t>OREO SOFT CAKE 96G</t>
+  </si>
+  <si>
+    <t>20052630</t>
+  </si>
+  <si>
+    <t>LOTTE CHOCO PIE 156G</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20136934</t>
+  </si>
+  <si>
+    <t>LOTTE C/PIE STRWB156</t>
+  </si>
+  <si>
+    <t>20052628</t>
+  </si>
+  <si>
+    <t>LOTTE CHOCO PIE 52G</t>
+  </si>
+  <si>
+    <t>20143290</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHCLAVA 5</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>10008579</t>
+  </si>
+  <si>
+    <t>DELFI MINIS BLK.VN70</t>
+  </si>
+  <si>
+    <t>10008580</t>
+  </si>
+  <si>
+    <t>DELFI MINIS CHOCO 70</t>
+  </si>
+  <si>
+    <t>20102638</t>
+  </si>
+  <si>
+    <t>DEKA WFR BITE CHO 72</t>
+  </si>
+  <si>
+    <t>20083487</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOCO 95G</t>
+  </si>
+  <si>
+    <t>20083488</t>
+  </si>
+  <si>
+    <t>TANGO WFR VANL 95G</t>
+  </si>
+  <si>
+    <t>20143337</t>
+  </si>
+  <si>
+    <t>TANGO WFLE CHO HZL70</t>
+  </si>
+  <si>
+    <t>20138099</t>
+  </si>
+  <si>
+    <t>OVALTINE MB WFR 100G</t>
+  </si>
+  <si>
+    <t>10036934</t>
+  </si>
+  <si>
+    <t>ASTOR CHOCOLATE 40G</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20137570</t>
+  </si>
+  <si>
+    <t>NABATI BIG RL CHS48G</t>
+  </si>
+  <si>
+    <t>20138461</t>
+  </si>
+  <si>
+    <t>NABATI ROLL STRAW 55</t>
+  </si>
+  <si>
+    <t>20142903</t>
+  </si>
+  <si>
+    <t>CHCLTOS RCH DUBAI 54</t>
+  </si>
+  <si>
+    <t>20142904</t>
+  </si>
+  <si>
+    <t>CHCLTOS RCH MTCHA 54</t>
+  </si>
+  <si>
+    <t>20139061</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE CKLT 35</t>
+  </si>
+  <si>
+    <t>20129863</t>
+  </si>
+  <si>
+    <t>NYAM2 SMILEY CKL 45G</t>
+  </si>
+  <si>
+    <t>20099762</t>
+  </si>
+  <si>
+    <t>NYAM2 POPSTIX CHO 48</t>
+  </si>
+  <si>
+    <t>20141134</t>
+  </si>
+  <si>
+    <t>POCKY STRAW YOGRT 38</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20138261</t>
+  </si>
+  <si>
+    <t>POCKY BLUEBERRY 38G</t>
+  </si>
+  <si>
+    <t>20142267</t>
+  </si>
+  <si>
+    <t>POCKY PASION FRUIT38</t>
+  </si>
+  <si>
+    <t>20142268</t>
+  </si>
+  <si>
+    <t>GLICO PJOY TIRAMIS30</t>
+  </si>
+  <si>
+    <t>20065180</t>
+  </si>
+  <si>
+    <t>GLICO PEJOY CHO 30G</t>
+  </si>
+  <si>
+    <t>20039648</t>
+  </si>
+  <si>
+    <t>LOTTE PEPERO ALMND32</t>
+  </si>
+  <si>
+    <t>20060710</t>
+  </si>
+  <si>
+    <t>LOTTE PEPERO WHT.C32</t>
+  </si>
+  <si>
+    <t>10038704</t>
+  </si>
+  <si>
+    <t>MEIJI H/PANDA CHOC42</t>
+  </si>
+  <si>
+    <t>10004490</t>
+  </si>
+  <si>
+    <t>HELLO PANDA STRW 42G</t>
+  </si>
+  <si>
+    <t>20134559</t>
+  </si>
+  <si>
+    <t>HLO PANDA DB.CHO 42G</t>
+  </si>
+  <si>
+    <t>20134875</t>
+  </si>
+  <si>
+    <t>CHOKI2 STIK CHOCO48G</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>10000213</t>
+  </si>
+  <si>
+    <t>GLICO POCKY CHO 40GR</t>
+  </si>
+  <si>
+    <t>10036916</t>
+  </si>
+  <si>
+    <t>GLICO POCKY.STRAW39G</t>
+  </si>
+  <si>
+    <t>20086168</t>
+  </si>
+  <si>
+    <t>GLCO POCKY COOK&amp;CR40</t>
+  </si>
+  <si>
+    <t>20062839</t>
+  </si>
+  <si>
+    <t>GLCO POCKY MTCHA 35G</t>
+  </si>
+  <si>
+    <t>20138741</t>
+  </si>
+  <si>
+    <t>GLICO POCKY MILK 40G</t>
+  </si>
+  <si>
+    <t>20057865</t>
+  </si>
+  <si>
+    <t>GLCO POCKY DOU.CHO39</t>
+  </si>
+  <si>
+    <t>20134839</t>
+  </si>
+  <si>
+    <t>POCKY CRSHD DRK.CH25</t>
+  </si>
+  <si>
+    <t>10032077</t>
+  </si>
+  <si>
+    <t>NSSIN LG.STK BISC 90</t>
+  </si>
+  <si>
+    <t>20071746</t>
+  </si>
+  <si>
+    <t>SPRSTAR TRPL.CHO 6'S</t>
+  </si>
+  <si>
+    <t>10000461</t>
+  </si>
+  <si>
+    <t>MONDE SERENA GOLD 50</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20141391</t>
+  </si>
+  <si>
+    <t>MONDE SNACK CHEESE50</t>
+  </si>
+  <si>
+    <t>20099687</t>
+  </si>
+  <si>
+    <t>MONDE SPCY TOMAT 50G</t>
+  </si>
+  <si>
+    <t>10006131</t>
+  </si>
+  <si>
+    <t>AIM ROASTED CORN 180</t>
+  </si>
+  <si>
+    <t>10000562</t>
+  </si>
+  <si>
+    <t>MONDE EGG DROPS 110G</t>
+  </si>
+  <si>
+    <t>10002258</t>
+  </si>
+  <si>
+    <t>MONDE BISC PBIS 190G</t>
+  </si>
+  <si>
+    <t>20008887</t>
+  </si>
+  <si>
+    <t>MONDE SERENA EGG 168</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>10036931</t>
+  </si>
+  <si>
+    <t>MONDE BT.COOKIES 150</t>
+  </si>
+  <si>
+    <t>20126401</t>
+  </si>
+  <si>
+    <t>KOKOLA KKS VANLA 218</t>
+  </si>
+  <si>
+    <t>10000731</t>
+  </si>
+  <si>
+    <t>KHONG GUAN BISC 300G</t>
+  </si>
+  <si>
+    <t>10036921</t>
+  </si>
+  <si>
+    <t>K/G CRACKERS CRM 350</t>
+  </si>
+  <si>
+    <t>20142902</t>
+  </si>
+  <si>
+    <t>DILAN CKIES CHOCP 69</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>10033424</t>
+  </si>
+  <si>
+    <t>NISSIN COCONUT 200GR</t>
+  </si>
+  <si>
+    <t>20062816</t>
+  </si>
+  <si>
+    <t>GT COOKIES RNBOW 72</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>10008554</t>
+  </si>
+  <si>
+    <t>G/T CHOCOCHP CLSC 72</t>
+  </si>
+  <si>
+    <t>10008550</t>
+  </si>
+  <si>
+    <t>G/T CHOCHP DB.CHO 72</t>
+  </si>
+  <si>
+    <t>20124895</t>
+  </si>
+  <si>
+    <t>G/T COKIES CHOCDIP71</t>
+  </si>
+  <si>
+    <t>20003910</t>
+  </si>
+  <si>
+    <t>NISSIN CHOCO SOES100</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20045139</t>
+  </si>
+  <si>
+    <t>NISSIN BLBRY SOES100</t>
+  </si>
+  <si>
+    <t>20098498</t>
+  </si>
+  <si>
+    <t>NISSIN CHESE SOES100</t>
+  </si>
+  <si>
+    <t>20098494</t>
+  </si>
+  <si>
+    <t>NISSIN COK.SG KJU110</t>
+  </si>
+  <si>
+    <t>20111641</t>
+  </si>
+  <si>
+    <t>BETTER VANILLA 100 G</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20063488</t>
+  </si>
+  <si>
+    <t>ROMA ARDEN CHOCO 72G</t>
+  </si>
+  <si>
+    <t>20122072</t>
+  </si>
+  <si>
+    <t>NUTELLA B-READY/F 22</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>10002246</t>
+  </si>
+  <si>
+    <t>NISSIN LEMONIA 130GR</t>
+  </si>
+  <si>
+    <t>20033519</t>
+  </si>
+  <si>
+    <t>SLAI O'LAI STRW 128G</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20097406</t>
+  </si>
+  <si>
+    <t>SLAI O'LAI BLUBR 128</t>
+  </si>
+  <si>
+    <t>20073409</t>
+  </si>
+  <si>
+    <t>ROMA SANDW CKLT 157G</t>
+  </si>
+  <si>
+    <t>20098059</t>
+  </si>
+  <si>
+    <t>ROMA SNDW PEANUT 157</t>
+  </si>
+  <si>
+    <t>20025741</t>
+  </si>
+  <si>
+    <t>ROMA SARI GANDUM 149</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20105102</t>
+  </si>
+  <si>
+    <t>ROMA KLP CRM 174 G</t>
+  </si>
+  <si>
+    <t>20113989</t>
+  </si>
+  <si>
+    <t>ROMA KLP C CKL 186 G</t>
+  </si>
+  <si>
+    <t>20109904</t>
+  </si>
+  <si>
+    <t>ROMA SANDW LMN 120G</t>
+  </si>
+  <si>
+    <t>10000310</t>
+  </si>
+  <si>
+    <t>ROMA SWT MALKIST 105</t>
+  </si>
+  <si>
+    <t>20045132</t>
+  </si>
+  <si>
+    <t>ROMA GNDM SAND. 108G</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20052934</t>
+  </si>
+  <si>
+    <t>ROMA GNDM/S PNUT 108</t>
+  </si>
+  <si>
+    <t>10031595</t>
+  </si>
+  <si>
+    <t>ROMA BISC.KELAPA 300</t>
+  </si>
+  <si>
+    <t>20113383</t>
+  </si>
+  <si>
+    <t>ROMA KLP FRS 6x23 G</t>
+  </si>
+  <si>
+    <t>20120798</t>
+  </si>
+  <si>
+    <t>CHO CHO JOY SPR 30G</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20124289</t>
+  </si>
+  <si>
+    <t>CHO CHO JOY JMB 40G</t>
+  </si>
+  <si>
+    <t>10034901</t>
+  </si>
+  <si>
+    <t>CHO-CHO WFR CRISPY33</t>
+  </si>
+  <si>
+    <t>10034899</t>
+  </si>
+  <si>
+    <t>CHO-CHO WFR STRAW 35</t>
+  </si>
+  <si>
+    <t>10003424</t>
+  </si>
+  <si>
+    <t>NYAM2 B/PUFF CHO 18G</t>
+  </si>
+  <si>
+    <t>10036887</t>
+  </si>
+  <si>
+    <t>NYAM2 STK S/CHO 22.5</t>
+  </si>
+  <si>
+    <t>10003404</t>
+  </si>
+  <si>
+    <t>NYAM2 STICK STRAW 25</t>
+  </si>
+  <si>
+    <t>10001365</t>
+  </si>
+  <si>
+    <t>NYAM2 STICK CHOCO 25</t>
+  </si>
+  <si>
+    <t>10017675</t>
+  </si>
+  <si>
+    <t>NYAM2 STCK CHOBRY 25</t>
+  </si>
+  <si>
+    <t>20020018</t>
+  </si>
+  <si>
+    <t>HATARI S.H.PUFF 245G</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20020089</t>
+  </si>
+  <si>
+    <t>UNIBIS S.H.PUFF 247G</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20122975</t>
+  </si>
+  <si>
+    <t>CHOCOLITO RC.CHO 38G</t>
+  </si>
+  <si>
+    <t>20130543</t>
+  </si>
+  <si>
+    <t>CHOCOLITO ORGNL 38G</t>
+  </si>
+  <si>
+    <t>20013662</t>
+  </si>
+  <si>
+    <t>BISKUAT COKLAT121.6G</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20014537</t>
+  </si>
+  <si>
+    <t>BISKUAT ORIGNAL121.6</t>
+  </si>
+  <si>
+    <t>20053216</t>
+  </si>
+  <si>
+    <t>NSIN BSC KLP IJO 280</t>
+  </si>
+  <si>
+    <t>20091350</t>
+  </si>
+  <si>
+    <t>ROMA MARIE GOLD 220G</t>
+  </si>
+  <si>
+    <t>10000104</t>
+  </si>
+  <si>
+    <t>REGAL MARIE 120GR</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>10000430</t>
+  </si>
+  <si>
+    <t>REGAL MARIE SPC. 230</t>
+  </si>
+  <si>
+    <t>10000103</t>
+  </si>
+  <si>
+    <t>REGAL MARIE 230GR</t>
+  </si>
+  <si>
+    <t>20020017</t>
+  </si>
+  <si>
+    <t>A.T.B MARIE SUSU 180</t>
+  </si>
+  <si>
+    <t>20137760</t>
+  </si>
+  <si>
+    <t>BRIO POTATO ORI 104G</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>20046434</t>
+  </si>
+  <si>
+    <t>BRIO POTATO BISC 56G</t>
+  </si>
+  <si>
+    <t>20139772</t>
+  </si>
+  <si>
+    <t>BRIO POTATO BBQ 49G</t>
+  </si>
+  <si>
+    <t>20142807</t>
+  </si>
+  <si>
+    <t>GERY BISC.KNTG BBQ55</t>
   </si>
   <si>
     <t>20108817</t>
@@ -67,1228 +1354,34 @@
     <t>K/G SLTCHS COMBO 175</t>
   </si>
   <si>
-    <t>20142944</t>
-  </si>
-  <si>
-    <t>IDM CHOCO WAFER 120</t>
-  </si>
-  <si>
-    <t>20128683</t>
-  </si>
-  <si>
-    <t>TANGO WFLE CHO HZL63</t>
-  </si>
-  <si>
-    <t>20063092</t>
-  </si>
-  <si>
-    <t>SELAMAT DBL CHOCO128</t>
-  </si>
-  <si>
-    <t>10016650</t>
-  </si>
-  <si>
-    <t>SELAMAT WF.CHOCO 128</t>
-  </si>
-  <si>
-    <t>10004541</t>
-  </si>
-  <si>
-    <t>TANGO WFR VNLA 124G</t>
-  </si>
-  <si>
-    <t>10004540</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOCO 124G</t>
-  </si>
-  <si>
-    <t>20133247</t>
-  </si>
-  <si>
-    <t>OREO SOFT CAKE 96G</t>
-  </si>
-  <si>
-    <t>20030358</t>
-  </si>
-  <si>
-    <t>MONDE GNJI MN PIE 50</t>
-  </si>
-  <si>
-    <t>10036942</t>
-  </si>
-  <si>
-    <t>MONDE S.PIE STRW 85G</t>
-  </si>
-  <si>
-    <t>10003324</t>
-  </si>
-  <si>
-    <t>MONDE GENJIE PIE 70G</t>
-  </si>
-  <si>
-    <t>20139391</t>
-  </si>
-  <si>
-    <t>NEXTAR CHOC PIE 6S</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20140126</t>
-  </si>
-  <si>
-    <t>NEXTAR STRAWB CHS144</t>
-  </si>
-  <si>
-    <t>20083539</t>
-  </si>
-  <si>
-    <t>DELFI CUSTAS SC 6'S</t>
-  </si>
-  <si>
-    <t>20052630</t>
-  </si>
-  <si>
-    <t>LOTTE CHOCO PIE 156G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20096783</t>
-  </si>
-  <si>
-    <t>DELFI CHO.PIE DRK180</t>
-  </si>
-  <si>
-    <t>20136934</t>
-  </si>
-  <si>
-    <t>LOTTE C/PIE STRWB156</t>
-  </si>
-  <si>
-    <t>20052628</t>
-  </si>
-  <si>
-    <t>LOTTE CHOCO PIE 52G</t>
-  </si>
-  <si>
-    <t>20132494</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS KJU32</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20130152</t>
-  </si>
-  <si>
-    <t>LEMONILO BROWNIES 32</t>
-  </si>
-  <si>
-    <t>20142678</t>
-  </si>
-  <si>
-    <t>LMNILO LMN CHESSE 32</t>
-  </si>
-  <si>
-    <t>20137230</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS STR32</t>
-  </si>
-  <si>
-    <t>20137584</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHOCIP35</t>
-  </si>
-  <si>
-    <t>20137583</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHEESE35</t>
-  </si>
-  <si>
-    <t>20139819</t>
-  </si>
-  <si>
-    <t>TANGO BROWNIS CR.35G</t>
-  </si>
-  <si>
-    <t>20061189</t>
-  </si>
-  <si>
-    <t>NARAYA OAT CHOCO 90</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20056645</t>
-  </si>
-  <si>
-    <t>NARAYA OAT CHOCO 90G</t>
-  </si>
-  <si>
-    <t>20102638</t>
-  </si>
-  <si>
-    <t>DEKA WFR BITE CHO 72</t>
-  </si>
-  <si>
-    <t>20083487</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOCO 95G</t>
-  </si>
-  <si>
-    <t>20083488</t>
-  </si>
-  <si>
-    <t>TANGO WFR VANL 95G</t>
-  </si>
-  <si>
-    <t>20143337</t>
-  </si>
-  <si>
-    <t>TANGO WFLE CHO HZL70</t>
-  </si>
-  <si>
-    <t>20138099</t>
-  </si>
-  <si>
-    <t>OVALTINE MB WFR 100G</t>
-  </si>
-  <si>
-    <t>20139081</t>
-  </si>
-  <si>
-    <t>REGAL CHO MARIE 64G</t>
-  </si>
-  <si>
-    <t>20130007</t>
-  </si>
-  <si>
-    <t>BETTER FUN BITES 10S</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10000132</t>
-  </si>
-  <si>
-    <t>MONDE BT.COOKIES 454</t>
-  </si>
-  <si>
-    <t>10000734</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHOCO 570</t>
-  </si>
-  <si>
-    <t>20010655</t>
-  </si>
-  <si>
-    <t>TANGO WFER CHOCO 220</t>
-  </si>
-  <si>
-    <t>10000133</t>
-  </si>
-  <si>
-    <t>KHONG GUAN MN ASS650</t>
-  </si>
-  <si>
-    <t>10000360</t>
-  </si>
-  <si>
-    <t>KHONG GUAN RED 1600G</t>
-  </si>
-  <si>
-    <t>20129572</t>
-  </si>
-  <si>
-    <t>CHCLATOS WFR VNLA90</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20127761</t>
-  </si>
-  <si>
-    <t>CHCLATOS WFR CHO 90</t>
-  </si>
-  <si>
-    <t>10000175</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHO 110G</t>
-  </si>
-  <si>
-    <t>20109917</t>
-  </si>
-  <si>
-    <t>RMA WAFELO C/BLS97.6</t>
-  </si>
-  <si>
-    <t>20069149</t>
-  </si>
-  <si>
-    <t>TANGO WFR LG VAN 100</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20138977</t>
-  </si>
-  <si>
-    <t>TANGO WFR LG CHES100</t>
-  </si>
-  <si>
-    <t>20132881</t>
-  </si>
-  <si>
-    <t>TANGO WFR SSY STR100</t>
-  </si>
-  <si>
-    <t>20071746</t>
-  </si>
-  <si>
-    <t>SPRSTAR TRPL.CHO 6'S</t>
-  </si>
-  <si>
-    <t>20027448</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOC 100G</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20055311</t>
-  </si>
-  <si>
-    <t>NABATI RCHSE WFR 100</t>
-  </si>
-  <si>
-    <t>20055312</t>
-  </si>
-  <si>
-    <t>NBTI RCHCO WFR CK100</t>
-  </si>
-  <si>
-    <t>20138462</t>
-  </si>
-  <si>
-    <t>NABATI WFR STRAW 122</t>
-  </si>
-  <si>
-    <t>10000726</t>
-  </si>
-  <si>
-    <t>ASTOR CHOCOLATE 150G</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20139061</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE CKLT 35</t>
-  </si>
-  <si>
-    <t>20139392</t>
-  </si>
-  <si>
-    <t>BRINGZ LMIER BTR 100</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20137570</t>
-  </si>
-  <si>
-    <t>NABATI BIG RL CHS48G</t>
-  </si>
-  <si>
-    <t>20138461</t>
-  </si>
-  <si>
-    <t>NABATI ROLL STRAW 55</t>
-  </si>
-  <si>
-    <t>20142903</t>
-  </si>
-  <si>
-    <t>CHCLTOS RCH DUBAI 54</t>
-  </si>
-  <si>
-    <t>20142904</t>
-  </si>
-  <si>
-    <t>CHCLTOS RCH MTCHA 54</t>
-  </si>
-  <si>
-    <t>10036934</t>
-  </si>
-  <si>
-    <t>ASTOR CHOCOLATE 40G</t>
-  </si>
-  <si>
-    <t>20138261</t>
-  </si>
-  <si>
-    <t>POCKY BLUEBERRY 38G</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20141134</t>
-  </si>
-  <si>
-    <t>POCKY STRAW YOGRT 38</t>
-  </si>
-  <si>
-    <t>20065180</t>
-  </si>
-  <si>
-    <t>GLICO PEJOY CHO 30G</t>
-  </si>
-  <si>
-    <t>20039648</t>
-  </si>
-  <si>
-    <t>LOTTE PEPERO ALMND32</t>
-  </si>
-  <si>
-    <t>20060710</t>
-  </si>
-  <si>
-    <t>LOTTE PEPERO WHT.C32</t>
-  </si>
-  <si>
-    <t>10038704</t>
-  </si>
-  <si>
-    <t>MEIJI H/PANDA CHOC42</t>
-  </si>
-  <si>
-    <t>10004490</t>
-  </si>
-  <si>
-    <t>HELLO PANDA STRW 42G</t>
-  </si>
-  <si>
-    <t>20134559</t>
-  </si>
-  <si>
-    <t>HLO PANDA DB.CHO 42G</t>
-  </si>
-  <si>
-    <t>20129863</t>
-  </si>
-  <si>
-    <t>NYAM2 SMILEY CKL 45G</t>
-  </si>
-  <si>
-    <t>20099762</t>
-  </si>
-  <si>
-    <t>NYAM2 POPSTIX CHO 48</t>
-  </si>
-  <si>
-    <t>20134875</t>
-  </si>
-  <si>
-    <t>CHOKI2 STIK CHOCO48G</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>10000213</t>
-  </si>
-  <si>
-    <t>GLICO POCKY CHO 40GR</t>
-  </si>
-  <si>
-    <t>10036916</t>
-  </si>
-  <si>
-    <t>GLICO POCKY.STRAW39G</t>
-  </si>
-  <si>
-    <t>20086168</t>
-  </si>
-  <si>
-    <t>GLCO POCKY COOK&amp;CR40</t>
-  </si>
-  <si>
-    <t>20138741</t>
-  </si>
-  <si>
-    <t>GLICO POCKY MILK 40G</t>
-  </si>
-  <si>
-    <t>20138740</t>
-  </si>
-  <si>
-    <t>POCKY MILK CHOCO 39G</t>
-  </si>
-  <si>
-    <t>20062839</t>
-  </si>
-  <si>
-    <t>GLCO POCKY MTCHA 35G</t>
-  </si>
-  <si>
-    <t>20057865</t>
-  </si>
-  <si>
-    <t>GLCO POCKY DOU.CHO39</t>
-  </si>
-  <si>
-    <t>20134839</t>
-  </si>
-  <si>
-    <t>POCKY CRSHD DRK.CH25</t>
-  </si>
-  <si>
-    <t>20142268</t>
-  </si>
-  <si>
-    <t>GLICO PJOY TIRAMIS30</t>
-  </si>
-  <si>
-    <t>20142267</t>
-  </si>
-  <si>
-    <t>POCKY PASION FRUIT38</t>
-  </si>
-  <si>
-    <t>10006131</t>
-  </si>
-  <si>
-    <t>AIM ROASTED CORN 180</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10000461</t>
-  </si>
-  <si>
-    <t>MONDE SERENA GOLD 50</t>
-  </si>
-  <si>
-    <t>20099687</t>
-  </si>
-  <si>
-    <t>MONDE SPCY TOMAT 50G</t>
-  </si>
-  <si>
-    <t>10000562</t>
-  </si>
-  <si>
-    <t>MONDE EGG DROPS 110G</t>
-  </si>
-  <si>
-    <t>10002258</t>
-  </si>
-  <si>
-    <t>MONDE BISC PBIS 190G</t>
-  </si>
-  <si>
-    <t>20141391</t>
-  </si>
-  <si>
-    <t>MONDE SNACK CHEESE50</t>
-  </si>
-  <si>
-    <t>20015337</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW COKL 190</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20015338</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CHSE 190</t>
-  </si>
-  <si>
-    <t>20095021</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CKLT 76G</t>
-  </si>
-  <si>
-    <t>20142943</t>
-  </si>
-  <si>
-    <t>IDM CHOCO CRACKR 100</t>
-  </si>
-  <si>
-    <t>20137569</t>
-  </si>
-  <si>
-    <t>BISKUAT GOLD.STR105G</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20085046</t>
-  </si>
-  <si>
-    <t>JULIES PNUT BTR 82.5</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20057475</t>
-  </si>
-  <si>
-    <t>SERENA TOGO CKLT 128</t>
-  </si>
-  <si>
-    <t>20131802</t>
-  </si>
-  <si>
-    <t>IMPERIAL BLUBERRY108</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20139973</t>
-  </si>
-  <si>
-    <t>IMPERIAL STRW&amp;CH 100</t>
-  </si>
-  <si>
-    <t>20125056</t>
-  </si>
-  <si>
-    <t>UNIBIS MRING TART120</t>
-  </si>
-  <si>
-    <t>20021257</t>
-  </si>
-  <si>
-    <t>U/BISC BONBON CHO200</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20008947</t>
-  </si>
-  <si>
-    <t>K/G MALKIS SPRCO 138</t>
-  </si>
-  <si>
-    <t>20091225</t>
-  </si>
-  <si>
-    <t>OVLTNE CHO BISC 104G</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20134970</t>
-  </si>
-  <si>
-    <t>MILO SANDW ORIG 96G</t>
-  </si>
-  <si>
-    <t>20134969</t>
-  </si>
-  <si>
-    <t>MILO SANDW MILK 96G</t>
-  </si>
-  <si>
-    <t>20140011</t>
-  </si>
-  <si>
-    <t>MILO BISC. CHOCO 96G</t>
-  </si>
-  <si>
-    <t>20030547</t>
-  </si>
-  <si>
-    <t>OREO ICE CRM BL 105G</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20074990</t>
-  </si>
-  <si>
-    <t>OREO DARK&amp;WHT 105G</t>
-  </si>
-  <si>
-    <t>20024644</t>
-  </si>
-  <si>
-    <t>OREO STRAW CREM1105G</t>
-  </si>
-  <si>
-    <t>20106305</t>
-  </si>
-  <si>
-    <t>OREO RED VELVET 105G</t>
-  </si>
-  <si>
-    <t>20139951</t>
-  </si>
-  <si>
-    <t>KOKOLA BLCK CKLT 110</t>
-  </si>
-  <si>
-    <t>10035165</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 105G</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20138464</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 147.2G</t>
-  </si>
-  <si>
-    <t>20142591</t>
-  </si>
-  <si>
-    <t>OREO SNDW HOTTEOK105</t>
-  </si>
-  <si>
-    <t>10016170</t>
-  </si>
-  <si>
-    <t>OREO CHOCO CRM 105G</t>
-  </si>
-  <si>
-    <t>20142670</t>
-  </si>
-  <si>
-    <t>KTST BGLN GT CHESE45</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20142669</t>
-  </si>
-  <si>
-    <t>KTST BGLN GT BUTER45</t>
-  </si>
-  <si>
-    <t>20048790</t>
-  </si>
-  <si>
-    <t>OREO MINI CHOCO 58.4</t>
-  </si>
-  <si>
-    <t>20048791</t>
-  </si>
-  <si>
-    <t>OREO MINI VANLA 58.4</t>
-  </si>
-  <si>
-    <t>20134691</t>
-  </si>
-  <si>
-    <t>TWB CRACKR RAINBOW57</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20143289</t>
-  </si>
-  <si>
-    <t>NSN COOKIES KLPN 60G</t>
-  </si>
-  <si>
-    <t>20143285</t>
-  </si>
-  <si>
-    <t>MONDE SHRTBRD BISC70</t>
-  </si>
-  <si>
-    <t>20143290</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHCLAVA 5</t>
-  </si>
-  <si>
-    <t>20133507</t>
-  </si>
-  <si>
-    <t>DELFI KRICE SWD 47.4</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20133506</t>
-  </si>
-  <si>
-    <t>DELFI KRICE SWET64.8</t>
-  </si>
-  <si>
-    <t>10008579</t>
-  </si>
-  <si>
-    <t>DELFI MINIS BLK.VN70</t>
-  </si>
-  <si>
-    <t>10008580</t>
-  </si>
-  <si>
-    <t>DELFI MINIS CHOCO 70</t>
-  </si>
-  <si>
-    <t>20076573</t>
-  </si>
-  <si>
-    <t>NEXTAR CHO.BRWNS 8'S</t>
-  </si>
-  <si>
-    <t>20071797</t>
-  </si>
-  <si>
-    <t>NEXTAR PINEAPPLE 8'S</t>
-  </si>
-  <si>
-    <t>20130555</t>
-  </si>
-  <si>
-    <t>NEXTAR RICHOCO 8'S</t>
-  </si>
-  <si>
-    <t>10032077</t>
-  </si>
-  <si>
-    <t>NSSIN LG.STK BISC 90</t>
-  </si>
-  <si>
-    <t>20122072</t>
-  </si>
-  <si>
-    <t>NUTELLA B-READY/F 22</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>10000731</t>
-  </si>
-  <si>
-    <t>KHONG GUAN BISC 300G</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>10036921</t>
-  </si>
-  <si>
-    <t>K/G CRACKERS CRM 350</t>
-  </si>
-  <si>
-    <t>20126401</t>
-  </si>
-  <si>
-    <t>KOKOLA KKS VANLA 218</t>
-  </si>
-  <si>
-    <t>20013332</t>
-  </si>
-  <si>
-    <t>K/G SALTCH CMBO10X17</t>
-  </si>
-  <si>
-    <t>20008887</t>
-  </si>
-  <si>
-    <t>MONDE SERENA EGG 168</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>10036931</t>
-  </si>
-  <si>
-    <t>MONDE BT.COOKIES 150</t>
-  </si>
-  <si>
-    <t>10038628</t>
-  </si>
-  <si>
-    <t>HATARI BIS.PEANUT225</t>
-  </si>
-  <si>
-    <t>20135148</t>
-  </si>
-  <si>
-    <t>MONDE SHRTBRD MTG115</t>
-  </si>
-  <si>
-    <t>10033424</t>
-  </si>
-  <si>
-    <t>NISSIN COCONUT 200GR</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20142677</t>
-  </si>
-  <si>
-    <t>MONDE BRBON GNDM 140</t>
-  </si>
-  <si>
-    <t>10003144</t>
-  </si>
-  <si>
-    <t>MONDE BOURBON CHO140</t>
-  </si>
-  <si>
-    <t>10036938</t>
-  </si>
-  <si>
-    <t>SRENA S.CAKE CHO 225</t>
-  </si>
-  <si>
-    <t>20062816</t>
-  </si>
-  <si>
-    <t>GT COOKIES RNBOW 72</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>10008554</t>
-  </si>
-  <si>
-    <t>G/T CHOCOCHP CLSC 72</t>
-  </si>
-  <si>
-    <t>10008550</t>
-  </si>
-  <si>
-    <t>G/T CHOCHP DB.CHO 72</t>
-  </si>
-  <si>
-    <t>20124895</t>
-  </si>
-  <si>
-    <t>G/T COKIES CHOCDIP71</t>
-  </si>
-  <si>
-    <t>20098494</t>
-  </si>
-  <si>
-    <t>NISSIN COK.SG KJU110</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20045139</t>
-  </si>
-  <si>
-    <t>NISSIN BLBRY SOES100</t>
-  </si>
-  <si>
-    <t>20098498</t>
-  </si>
-  <si>
-    <t>NISSIN CHESE SOES100</t>
-  </si>
-  <si>
-    <t>20003910</t>
-  </si>
-  <si>
-    <t>NISSIN CHOCO SOES100</t>
-  </si>
-  <si>
-    <t>20142902</t>
-  </si>
-  <si>
-    <t>DILAN CKIES CHOCP 69</t>
-  </si>
-  <si>
-    <t>20111641</t>
-  </si>
-  <si>
-    <t>BETTER VANILLA 100G</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20063488</t>
-  </si>
-  <si>
-    <t>ROMA ARDEN CHOCO 72G</t>
-  </si>
-  <si>
-    <t>10002246</t>
-  </si>
-  <si>
-    <t>NISSIN LEMONIA 130GR</t>
-  </si>
-  <si>
-    <t>20033519</t>
-  </si>
-  <si>
-    <t>SLAI O'LAI STRW 128G</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20097406</t>
-  </si>
-  <si>
-    <t>SLAI O'LAI BLUBR 128</t>
-  </si>
-  <si>
-    <t>20073409</t>
-  </si>
-  <si>
-    <t>ROMA SANDW CKLT 157G</t>
-  </si>
-  <si>
-    <t>20098059</t>
-  </si>
-  <si>
-    <t>ROMA SNDW PEANUT 157</t>
-  </si>
-  <si>
-    <t>20025741</t>
-  </si>
-  <si>
-    <t>ROMA SARI GANDUM 149</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20105102</t>
-  </si>
-  <si>
-    <t>ROMA KELAPA CRM 174</t>
-  </si>
-  <si>
-    <t>20113989</t>
-  </si>
-  <si>
-    <t>ROMA KLP CRM CKL 186</t>
-  </si>
-  <si>
-    <t>20109904</t>
-  </si>
-  <si>
-    <t>ROMA SANDW LMN 120G</t>
-  </si>
-  <si>
-    <t>20045132</t>
-  </si>
-  <si>
-    <t>ROMA GNDM SAND. 108G</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20052934</t>
-  </si>
-  <si>
-    <t>ROMA GNDM/S PNUT 108</t>
-  </si>
-  <si>
-    <t>10031595</t>
-  </si>
-  <si>
-    <t>ROMA BISC.KELAPA 300</t>
-  </si>
-  <si>
-    <t>20113383</t>
-  </si>
-  <si>
-    <t>ROMA KLPA FRSH 6'S</t>
-  </si>
-  <si>
-    <t>20124289</t>
-  </si>
-  <si>
-    <t>CHO CHO JOY JMB 40G</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20120798</t>
-  </si>
-  <si>
-    <t>CHO CHO JOY SPR 30G</t>
-  </si>
-  <si>
-    <t>10034901</t>
-  </si>
-  <si>
-    <t>CHO-CHO WFR CRISPY33</t>
-  </si>
-  <si>
-    <t>10034899</t>
-  </si>
-  <si>
-    <t>CHO-CHO WFR STRAW 35</t>
-  </si>
-  <si>
-    <t>10003424</t>
-  </si>
-  <si>
-    <t>NYAM2 B/PUFF CHO 18G</t>
-  </si>
-  <si>
-    <t>10036887</t>
-  </si>
-  <si>
-    <t>NYAM2 STK S/CHO 22.5</t>
-  </si>
-  <si>
-    <t>10003404</t>
-  </si>
-  <si>
-    <t>NYAM2 STICK STRAW 25</t>
-  </si>
-  <si>
-    <t>10001365</t>
-  </si>
-  <si>
-    <t>NYAM2 STICK CHOCO 25</t>
-  </si>
-  <si>
-    <t>10017675</t>
-  </si>
-  <si>
-    <t>NYAM2 STCK CHOBRY 25</t>
-  </si>
-  <si>
-    <t>20020018</t>
-  </si>
-  <si>
-    <t>HATARI S.H.PUFF 245G</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20020089</t>
-  </si>
-  <si>
-    <t>UNIBIS S.H.PUFF 247G</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20122975</t>
-  </si>
-  <si>
-    <t>CHOCOLITO RC.CHO 38G</t>
-  </si>
-  <si>
-    <t>20130543</t>
-  </si>
-  <si>
-    <t>CHOCOLITO ORGNL 38G</t>
-  </si>
-  <si>
-    <t>20020017</t>
-  </si>
-  <si>
-    <t>A.T.B MARIE SUSU 180</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>10000430</t>
-  </si>
-  <si>
-    <t>REGAL MARIE SPC. 230</t>
-  </si>
-  <si>
-    <t>10000103</t>
-  </si>
-  <si>
-    <t>REGAL MARIE 230GR</t>
-  </si>
-  <si>
-    <t>10000104</t>
-  </si>
-  <si>
-    <t>REGAL MARIE 120GR</t>
-  </si>
-  <si>
-    <t>20091350</t>
-  </si>
-  <si>
-    <t>ROMA MARIE GOLD 220G</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>20014537</t>
-  </si>
-  <si>
-    <t>BISKUAT ORIGNAL121.6</t>
-  </si>
-  <si>
-    <t>20013662</t>
-  </si>
-  <si>
-    <t>BISKUAT COKLAT121.6G</t>
-  </si>
-  <si>
-    <t>20053216</t>
-  </si>
-  <si>
-    <t>NSIN BSC KLP IJO 280</t>
+    <t>41</t>
+  </si>
+  <si>
+    <t>10000052</t>
+  </si>
+  <si>
+    <t>AIM CRACK CRISPY 150</t>
+  </si>
+  <si>
+    <t>20133020</t>
+  </si>
+  <si>
+    <t>NISSIN CRACK.LMON200</t>
+  </si>
+  <si>
+    <t>10001826</t>
+  </si>
+  <si>
+    <t>K/G SALTCHEESE RG200</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>20118424</t>
+  </si>
+  <si>
+    <t>KG SALTCHEESE S&amp;S200</t>
   </si>
   <si>
     <t>10000206</t>
@@ -1297,64 +1390,37 @@
     <t>NISSIN CR.CRISPY 225</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>20133020</t>
-  </si>
-  <si>
-    <t>NISSIN CRACK.LMON200</t>
-  </si>
-  <si>
-    <t>20118424</t>
-  </si>
-  <si>
-    <t>KG SALTCHEESE S&amp;S200</t>
-  </si>
-  <si>
-    <t>10001826</t>
-  </si>
-  <si>
-    <t>K/G SALTCHEESE RG200</t>
-  </si>
-  <si>
-    <t>10000052</t>
-  </si>
-  <si>
-    <t>AIM CRACK CRISPY 150</t>
-  </si>
-  <si>
-    <t>20142807</t>
-  </si>
-  <si>
-    <t>GERY BISC.KNTG BBQ55</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>20137760</t>
-  </si>
-  <si>
-    <t>BRIO POTATO ORI 104G</t>
-  </si>
-  <si>
-    <t>20139772</t>
-  </si>
-  <si>
-    <t>BRIO POTATO BBQ 49G</t>
-  </si>
-  <si>
-    <t>20046434</t>
-  </si>
-  <si>
-    <t>BRIO POTATO BISC 56G</t>
-  </si>
-  <si>
-    <t>20142222</t>
-  </si>
-  <si>
-    <t>RITZ CRCKS KYA BUT91</t>
+    <t>10001017</t>
+  </si>
+  <si>
+    <t>ROMA CREAM CRAC 107G</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>20063359</t>
+  </si>
+  <si>
+    <t>ROMA MLKST BLG/COK90</t>
+  </si>
+  <si>
+    <t>20103341</t>
+  </si>
+  <si>
+    <t>ROMA MLKS COK KLP 95</t>
+  </si>
+  <si>
+    <t>20065096</t>
+  </si>
+  <si>
+    <t>GERY MLKS SLT KJU100</t>
+  </si>
+  <si>
+    <t>20091799</t>
+  </si>
+  <si>
+    <t>GERY S.MLKS MTCH 100</t>
   </si>
   <si>
     <t>20095220</t>
@@ -1363,70 +1429,10 @@
     <t>GERY MLK COK CNUT105</t>
   </si>
   <si>
-    <t>42</t>
-  </si>
-  <si>
     <t>20049190</t>
   </si>
   <si>
     <t>GERY MLKS SLT COK100</t>
-  </si>
-  <si>
-    <t>20134984</t>
-  </si>
-  <si>
-    <t>RITZ CRCKRS CHOC 91G</t>
-  </si>
-  <si>
-    <t>20134983</t>
-  </si>
-  <si>
-    <t>RITZ CRCKRS CHSE 91G</t>
-  </si>
-  <si>
-    <t>20141506</t>
-  </si>
-  <si>
-    <t>RITZ CRACKER ORI 100</t>
-  </si>
-  <si>
-    <t>20063359</t>
-  </si>
-  <si>
-    <t>ROMA MLKST BLG/COK90</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>20103341</t>
-  </si>
-  <si>
-    <t>ROMA MLKS COK KLP 95</t>
-  </si>
-  <si>
-    <t>10000310</t>
-  </si>
-  <si>
-    <t>ROMA SWT MALKIST 105</t>
-  </si>
-  <si>
-    <t>10001017</t>
-  </si>
-  <si>
-    <t>ROMA CREAM CRAC 107G</t>
-  </si>
-  <si>
-    <t>20065096</t>
-  </si>
-  <si>
-    <t>GERY MLKS SLT KJU100</t>
-  </si>
-  <si>
-    <t>20091799</t>
-  </si>
-  <si>
-    <t>GERY S.MLKS MTCH 100</t>
   </si>
   <si>
     <t>10033018</t>
@@ -1858,7 +1864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F217"/>
+  <dimension ref="A1:F218"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1902,18 +1908,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -1922,18 +1928,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -1942,270 +1948,270 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2219,13 +2225,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2239,13 +2245,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2259,93 +2265,93 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2359,13 +2365,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2379,13 +2385,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2399,13 +2405,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2419,233 +2425,233 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2659,13 +2665,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2679,361 +2685,361 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="E46" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -3042,18 +3048,18 @@
         <v>133</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -3062,18 +3068,18 @@
         <v>133</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -3082,278 +3088,278 @@
         <v>133</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="E64" s="1" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -3362,18 +3368,18 @@
         <v>167</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -3382,18 +3388,18 @@
         <v>167</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3402,18 +3408,18 @@
         <v>167</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -3422,18 +3428,18 @@
         <v>167</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3442,850 +3448,850 @@
         <v>167</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>191</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>191</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>216</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>191</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4299,13 +4305,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4319,13 +4325,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4339,13 +4345,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4359,53 +4365,53 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4419,13 +4425,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4439,13 +4445,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4459,13 +4465,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4479,13 +4485,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4499,13 +4505,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4519,201 +4525,201 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>297</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -4722,18 +4728,18 @@
         <v>318</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4742,18 +4748,18 @@
         <v>318</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4762,610 +4768,610 @@
         <v>318</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F160" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5379,13 +5385,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5399,13 +5405,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5419,13 +5425,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5439,101 +5445,101 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>191</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>403</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>191</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
@@ -5542,18 +5548,18 @@
         <v>410</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
@@ -5562,18 +5568,18 @@
         <v>410</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>191</v>
+        <v>413</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
@@ -5582,290 +5588,290 @@
         <v>410</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>191</v>
+        <v>52</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="E192" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>439</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5879,53 +5885,53 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -5939,13 +5945,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5959,13 +5965,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -5985,7 +5991,7 @@
         <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6002,10 +6008,10 @@
         <v>461</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6022,10 +6028,10 @@
         <v>461</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6042,10 +6048,10 @@
         <v>461</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6062,10 +6068,10 @@
         <v>461</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6082,10 +6088,10 @@
         <v>461</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6099,33 +6105,33 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6139,13 +6145,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6159,13 +6165,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6179,13 +6185,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6199,13 +6205,33 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
